--- a/tame_output/ON/bt/strategyON_20240704.xlsx
+++ b/tame_output/ON/bt/strategyON_20240704.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>20.5%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.6%</t>
+          <t>-49.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.1%</t>
+          <t>-69.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.3%</t>
+          <t>449.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-530.9%</t>
+          <t>-531.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.3%</t>
+          <t>-37.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-41.0%</t>
+          <t>-40.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-167.0%</t>
+          <t>-167.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-31.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-171.7%</t>
+          <t>-171.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-217.0%</t>
+          <t>-217.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-84.9%</t>
+          <t>-85.4%</t>
         </is>
       </c>
     </row>
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.472828606418121</v>
+        <v>-4.47155341805472</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9460311762394618</v>
+        <v>0.9465412515848222</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2304826942513263</v>
+        <v>-0.2292075058879245</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.597229426569662</v>
+        <v>2.597994539587703</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.517218075747548</v>
+        <v>-4.515942887384147</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9301488644322917</v>
+        <v>0.9306589397776521</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.274872163580754</v>
+        <v>-0.2735969752173522</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.572469220896606</v>
+        <v>2.573234333914647</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.404546857511298</v>
+        <v>-4.403271669147897</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9702930602385147</v>
+        <v>0.9708031355838751</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1622009453445038</v>
+        <v>-0.160925756981102</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.635147660350079</v>
+        <v>2.63591277336812</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.292169856328625</v>
+        <v>-4.290894667965224</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.020735156542251</v>
+        <v>1.021245231887612</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1622009453445038</v>
+        <v>-0.160925756981102</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.640638956180747</v>
+        <v>2.641404069198788</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.319950254229978</v>
+        <v>-4.318675065866577</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.021120199150249</v>
+        <v>1.02163027449561</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1899813432458569</v>
+        <v>-0.1887061548824551</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.635467919208474</v>
+        <v>2.636233032226515</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.402951535255257</v>
+        <v>-4.401676346891856</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8262754067407909</v>
+        <v>0.8267854820861513</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2085522277730306</v>
+        <v>-0.2072770394096288</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.462681108492823</v>
+        <v>2.463446221510864</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.511565613698588</v>
+        <v>-4.510290425335187</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.902979436082664</v>
+        <v>0.9034895114280244</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2085522277730306</v>
+        <v>-0.2072770394096288</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.582830769212028</v>
+        <v>2.583595882230069</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.476156575450445</v>
+        <v>-4.474881387087044</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9316560774842442</v>
+        <v>0.9321661528296046</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2085522277730306</v>
+        <v>-0.2072770394096288</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.597343795314351</v>
+        <v>2.598108908332392</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.437772912892294</v>
+        <v>-4.436497724528893</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9444289838498734</v>
+        <v>0.9449390591952338</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1701685652148794</v>
+        <v>-0.1688933768514777</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.617793434191611</v>
+        <v>2.618558547209652</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.260656582857128</v>
+        <v>-4.259381394493727</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.012004544709242</v>
+        <v>1.012514620054602</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1701685652148794</v>
+        <v>-0.1688933768514777</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.614522463036913</v>
+        <v>2.615287576054954</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.305748827690674</v>
+        <v>-4.304473639327273</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9946510385377365</v>
+        <v>0.9951611138830969</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2320646083842692</v>
+        <v>-0.2307894200208674</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.578068228897192</v>
+        <v>2.578833341915233</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.126373406451906</v>
+        <v>-4.125098218088505</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.060188182339658</v>
+        <v>1.060698257685018</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.07528785021355056</v>
+        <v>-0.07401266185014876</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.665921259106037</v>
+        <v>2.666686372124079</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.171387619972512</v>
+        <v>-4.170112431609111</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.022989952263005</v>
+        <v>1.023500027608366</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1056367455281552</v>
+        <v>-0.1043615571647534</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.628519377248864</v>
+        <v>2.629284490266905</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.438392130244947</v>
+        <v>-4.437116941881546</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.921879710492977</v>
+        <v>0.9223897858383374</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2999997835711037</v>
+        <v>-0.2987245952077019</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.517593116762041</v>
+        <v>2.518358229780082</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.539589911682119</v>
+        <v>-4.538314723318718</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8806045198146095</v>
+        <v>0.8811145951599699</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3684085971164229</v>
+        <v>-0.3671334087530211</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.475751750531351</v>
+        <v>2.476516863549392</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.533078945067807</v>
+        <v>-4.531803756704406</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8808088680146513</v>
+        <v>0.8813189433600117</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3684085971164229</v>
+        <v>-0.3671334087530211</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.473351712085668</v>
+        <v>2.474116825103709</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.51404081736051</v>
+        <v>-4.512765628997109</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8849488383058151</v>
+        <v>0.8854589136511755</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4265922084476175</v>
+        <v>-0.4253170200842157</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.434966264495196</v>
+        <v>2.435731377513237</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.545167448511128</v>
+        <v>-4.543892260147727</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.050080054784248</v>
+        <v>1.050590130129609</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4265922084476175</v>
+        <v>-0.4253170200842157</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.612548133433877</v>
+        <v>2.613313246451918</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.559034209845046</v>
+        <v>-4.557759021481645</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.045366679236815</v>
+        <v>1.045876754582175</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4644501251814404</v>
+        <v>-0.4631749368180386</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.590666712379716</v>
+        <v>2.591431825397757</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.514230038305116</v>
+        <v>-4.512954849941715</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.069296878249713</v>
+        <v>1.069806953595073</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4644501251814404</v>
+        <v>-0.4631749368180386</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.596675242776642</v>
+        <v>2.597440355794683</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.366487068070113</v>
+        <v>-4.365211879706712</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.207546714135735</v>
+        <v>1.208056789481096</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2966427679465573</v>
+        <v>-0.2953675795831555</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.776512304909594</v>
+        <v>2.777277417927635</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.468501750601335</v>
+        <v>-4.467226562237934</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.169534462654728</v>
+        <v>1.170044538000088</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2966427679465573</v>
+        <v>-0.2953675795831555</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.779305926441075</v>
+        <v>2.780071039459116</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.46234904454855</v>
+        <v>-4.461073856185149</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.1726578934675</v>
+        <v>1.17316796881286</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.290490061893773</v>
+        <v>-0.2892148735303712</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.783659898464404</v>
+        <v>2.784425011482445</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.479158342699052</v>
+        <v>-4.477883154335651</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.16501465094741</v>
+        <v>1.16552472629277</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3072993600442746</v>
+        <v>-0.3060241716808728</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.772654796314213</v>
+        <v>2.773419909332254</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.41686034392293</v>
+        <v>-4.415585155559529</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.256269404254679</v>
+        <v>1.25677947960004</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3072993600442746</v>
+        <v>-0.3060241716808728</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.838990350111034</v>
+        <v>2.839755463129075</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.215070146257772</v>
+        <v>-4.213794957894371</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.04556635571014</v>
+        <v>1.046076431055501</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1092811678751202</v>
+        <v>-0.1080059795117184</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.666382137801925</v>
+        <v>2.667147250819966</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.141692049169036</v>
+        <v>-4.140416860805635</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.14520782686781</v>
+        <v>1.145717902213171</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.03590307078638366</v>
+        <v>-0.03462788242298187</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.780699228377342</v>
+        <v>2.781464341395383</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.23943259379401</v>
+        <v>-4.238157405430609</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.120739345133864</v>
+        <v>1.121249420479224</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.05179234891936385</v>
+        <v>-0.05051716055596206</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.785793397613598</v>
+        <v>2.786558510631639</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.41577035391694</v>
+        <v>-4.414495165553538</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.048740221909364</v>
+        <v>1.049250297254724</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2281301090422932</v>
+        <v>-0.2268549206788915</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.678526722364512</v>
+        <v>2.679291835382553</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.339348307485013</v>
+        <v>-4.338073119121612</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.077800658522063</v>
+        <v>1.078310733867424</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2281301090422932</v>
+        <v>-0.2268549206788915</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.67701834040444</v>
+        <v>2.677783453422481</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.294975175846444</v>
+        <v>-4.293699987483043</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.095412778612927</v>
+        <v>1.095922853958287</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1837569774037247</v>
+        <v>-0.1824817890403229</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.703505086823017</v>
+        <v>2.704270199841059</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.808153067403842</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.172140954959277</v>
+        <v>-4.170865766595876</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.138940261106384</v>
+        <v>1.139450336451745</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1837569774037247</v>
+        <v>-0.1824817890403229</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.697898880961608</v>
+        <v>2.698663993979649</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.814534824431647</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.124485224398221</v>
+        <v>-4.12321003603482</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.164384310358611</v>
+        <v>1.164894385703971</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.136101246842669</v>
+        <v>-0.1348260584792672</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.732874076326045</v>
+        <v>2.733639189344086</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.819427197806371</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.023967065899466</v>
+        <v>-4.022691877536065</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.209483947132838</v>
+        <v>1.209994022478198</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.03558308834391444</v>
+        <v>-0.03430789998051265</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.798077344800023</v>
+        <v>2.798842457818064</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.806181870282244</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.084633656301856</v>
+        <v>-4.083358467938455</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.171971983447754</v>
+        <v>1.172482058793114</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1172814050624481</v>
+        <v>-0.1160062166990463</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.735813027244775</v>
+        <v>2.736578140262816</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.810279572892872</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.039795254693457</v>
+        <v>-4.038520066330056</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.194005046701742</v>
+        <v>1.194515122047102</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1127379721175786</v>
+        <v>-0.1114627837541768</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.742636789622325</v>
+        <v>2.743401902640366</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.81444051252395</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.140553890450455</v>
+        <v>-4.139278702087054</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.157862532030021</v>
+        <v>1.158372607375381</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2015635408445841</v>
+        <v>-0.2002883524811823</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.6935023880172</v>
+        <v>2.694267501035241</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.820320115051787</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.096351053364555</v>
+        <v>-4.095075865001154</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.181423269392218</v>
+        <v>1.181933344737579</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1573607037586836</v>
+        <v>-0.1560855153952818</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.725903692796578</v>
+        <v>2.726668805814619</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.818730115521035</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.133330081027998</v>
+        <v>-4.132054892664597</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.165041658796089</v>
+        <v>1.165551734141449</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1203868019673531</v>
+        <v>-0.1191116136039513</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.746498034340624</v>
+        <v>2.747263147358665</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.869977880704075</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.153388159892838</v>
+        <v>-4.152112971529437</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.208266192433192</v>
+        <v>1.208776267778553</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1203868019673531</v>
+        <v>-0.1191116136039513</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.797745799523663</v>
+        <v>2.798510912541704</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.868418585298328</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.113457486714948</v>
+        <v>-4.112182298351547</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.222679166298601</v>
+        <v>1.223189241643962</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.08045612878946273</v>
+        <v>-0.07918094042606094</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.82014490802465</v>
+        <v>2.820910021042692</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.863366813536598</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.06242539399242</v>
+        <v>-4.061150205629019</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.238040231625882</v>
+        <v>1.238550306971243</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.02942403606693478</v>
+        <v>-0.02814884770353299</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.845712391896437</v>
+        <v>2.846477504914478</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.880554217629303</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.997201212865215</v>
+        <v>-3.995926024501814</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.28131730816947</v>
+        <v>1.28182738351483</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.03580014506027085</v>
+        <v>0.03707533342367264</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.902034304665465</v>
+        <v>2.902799417683506</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.876515189928583</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.959774192794081</v>
+        <v>-3.95849900443068</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.292249088497203</v>
+        <v>1.292759163842564</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.04105168308945251</v>
+        <v>0.0423268714528543</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.901146199782255</v>
+        <v>2.901911312800296</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.877771982259823</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.979885848828789</v>
+        <v>-3.978610660465388</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.28546121841456</v>
+        <v>1.285971293759921</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.0520790280868717</v>
+        <v>0.0533542164502735</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.909019399111947</v>
+        <v>2.909784512129988</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.038329753281034</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.926141034401585</v>
+        <v>-3.924865846038184</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.467516915206653</v>
+        <v>1.468026990552013</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.06214233752733367</v>
+        <v>0.06341752589073546</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.075615155797434</v>
+        <v>3.076380268815476</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.158442662498851</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.902349465795442</v>
+        <v>-3.901074277432041</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.597146451866927</v>
+        <v>1.597656527212288</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.08593390613347596</v>
+        <v>0.08720909449687775</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.210003006178937</v>
+        <v>3.210768119196978</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15015063851271</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.876265381531634</v>
+        <v>-3.874990193168233</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.599288061586309</v>
+        <v>1.59979813693167</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.08593390613347596</v>
+        <v>0.08720909449687775</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.201710982192796</v>
+        <v>3.202476095210837</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.14834383409649</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.798134200682687</v>
+        <v>-3.796859012319286</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.628733729509668</v>
+        <v>1.629243804855028</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1601107170171605</v>
+        <v>0.1613859053805623</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.244410264306786</v>
+        <v>3.245175377324828</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.165898239823281</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.789241739289404</v>
+        <v>-3.787966550926003</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.649845119793772</v>
+        <v>1.650355195139132</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1601107170171605</v>
+        <v>0.1613859053805623</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.261964670033578</v>
+        <v>3.262729783051619</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.157753287227865</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.957717856259282</v>
+        <v>-3.956442667895881</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.574309720410405</v>
+        <v>1.574819795755765</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1321628813005797</v>
+        <v>0.1334380696639815</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.237051016008213</v>
+        <v>3.237816129026254</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.139022984415727</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.259918327397699</v>
+        <v>-3.258643139034298</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.8346992291429</v>
+        <v>1.83520930448826</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.06181482193016902</v>
+        <v>0.06309001029357081</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.176111877573828</v>
+        <v>3.176876990591869</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.129687006912631</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.237197223714547</v>
+        <v>-3.235922035351146</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.834451693113066</v>
+        <v>1.834961768458426</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.06181482193016902</v>
+        <v>0.06309001029357081</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.166775900070733</v>
+        <v>3.167541013088774</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.2885931327638</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.235472180424503</v>
+        <v>-3.234196992061102</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.994047836280252</v>
+        <v>1.994557911625613</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.06353986522021277</v>
+        <v>0.06481505358361456</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.326717051895928</v>
+        <v>3.327482164913969</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.325670955257447</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.390253187202758</v>
+        <v>-3.388977998839357</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.969213256062597</v>
+        <v>1.969723331407957</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.03017219116573666</v>
+        <v>0.03144737952913845</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.34377426995689</v>
+        <v>3.344539382974931</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.322346311246992</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.338817853818098</v>
+        <v>-3.337542665454697</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.986462745406006</v>
+        <v>1.986972820751366</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.08160752455039633</v>
+        <v>0.08288271291379812</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.37131082597723</v>
+        <v>3.372075938995271</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.332352464891734</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.31186662949161</v>
+        <v>-3.310591441128209</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.007249388781343</v>
+        <v>2.007759464126703</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.09648787057811548</v>
+        <v>0.09776305894151727</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.390245187238603</v>
+        <v>3.391010300256645</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.516455597036694</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.447819637547926</v>
+        <v>-3.446544449184525</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.136971317703776</v>
+        <v>2.137481393049136</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.09648787057811548</v>
+        <v>0.09776305894151727</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.574348319383563</v>
+        <v>3.575113432401604</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.508572291939687</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.470227755352798</v>
+        <v>-3.468952566989397</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.12012476548482</v>
+        <v>2.120634840830181</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.09648787057811548</v>
+        <v>0.09776305894151727</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.566465014286556</v>
+        <v>3.567230127304597</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.510626291489324</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.618233522832198</v>
+        <v>-3.616958334468797</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.062976458042697</v>
+        <v>2.063486533388058</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.009760861714574021</v>
+        <v>0.01103605007797581</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.516482808518069</v>
+        <v>3.51724792153611</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.566880009211171</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.627674448720728</v>
+        <v>-3.626399260357327</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.115453805409133</v>
+        <v>2.115963880754493</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.1321879792579654</v>
+        <v>0.1334631676213672</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.646192796765951</v>
+        <v>3.646957909783992</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.569771103756472</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.626387685181172</v>
+        <v>-3.625112496817771</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.118859605370256</v>
+        <v>2.119369680715617</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.133474742797522</v>
+        <v>0.1347499311609238</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.649855949434985</v>
+        <v>3.650621062453027</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.567882916650247</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.627944739170463</v>
+        <v>-3.626669550807062</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.116348596668315</v>
+        <v>2.116858672013676</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.133474742797522</v>
+        <v>0.1347499311609238</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.647967762328761</v>
+        <v>3.648732875346802</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.56270314625311</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.635216624693927</v>
+        <v>-3.633941436330526</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.108260072061791</v>
+        <v>2.108770147407152</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.1262028572740573</v>
+        <v>0.1274780456374591</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.638424860617544</v>
+        <v>3.639189973635585</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.561137156463262</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.633375605635676</v>
+        <v>-3.632100417272275</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.107430489895244</v>
+        <v>2.107940565240605</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.1274710839455257</v>
+        <v>0.1287462723089275</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.637619806830577</v>
+        <v>3.638384919848618</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.574210563329181</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.640284311135357</v>
+        <v>-3.639009122771956</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.117740414561291</v>
+        <v>2.118250489906651</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.1274710839455257</v>
+        <v>0.1287462723089275</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.650693213696496</v>
+        <v>3.651458326714537</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.574210563329181</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.641845953950217</v>
+        <v>-3.640570765586816</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.117115757435347</v>
+        <v>2.117625832780707</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.1274710839455257</v>
+        <v>0.1287462723089275</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.650693213696496</v>
+        <v>3.651458326714537</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.572734604456183</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.66974674105969</v>
+        <v>-3.668471552696289</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.104479483718559</v>
+        <v>2.10498955906392</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.09287415980259089</v>
+        <v>0.09414934816599269</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.628459100337737</v>
+        <v>3.629224213355779</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.728687239625086</v>
+        <v>3.485674679777246</v>
       </c>
       <c r="C2014" t="n">
         <v>3.569499048433381</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.692893721380746</v>
+        <v>-3.700725613318211</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.091985135567335</v>
+        <v>2.08885237879235</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.0697271794815344</v>
+        <v>0.06189528754406992</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.611335356122302</v>
+        <v>3.606636220959824</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240704.xlsx
+++ b/tame_output/ON/bt/strategyON_20240704.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.5%</t>
+          <t>-73.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.7%</t>
+          <t>-49.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.6%</t>
+          <t>-69.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.2%</t>
+          <t>449.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-531.6%</t>
+          <t>-528.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>-37.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-167.3%</t>
+          <t>-166.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-21.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.4%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-217.8%</t>
+          <t>-214.9%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-85.4%</t>
+          <t>-83.6%</t>
         </is>
       </c>
     </row>
@@ -47873,16 +47873,16 @@
         <v>3.569499048433381</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.700725613318211</v>
+        <v>-3.671504550208962</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.08885237879235</v>
+        <v>2.100540804036049</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.06189528754406992</v>
+        <v>0.0911163506533188</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.606636220959824</v>
+        <v>3.624168858825373</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240704.xlsx
+++ b/tame_output/ON/bt/strategyON_20240704.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>49.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-73.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>122.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-681.4%</t>
+          <t>-674.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.6%</t>
+          <t>-49.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.3%</t>
+          <t>-68.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.3%</t>
+          <t>447.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-528.7%</t>
+          <t>-521.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-272.9%</t>
+          <t>-270.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.3%</t>
+          <t>-37.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-40.7%</t>
+          <t>-32.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-166.2%</t>
+          <t>-163.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.3%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-300.5%</t>
+          <t>-293.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-30.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-171.9%</t>
+          <t>-180.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-214.9%</t>
+          <t>-208.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-180.7%</t>
+          <t>-176.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-83.6%</t>
+          <t>-79.5%</t>
         </is>
       </c>
     </row>
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1878921395489951</v>
+        <v>0.2571933989386986</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.197370603618793</v>
+        <v>3.225091107374675</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.568940374610322</v>
+        <v>1.638241634000026</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.063934396879136</v>
+        <v>4.105515152512958</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.04923935230080001</v>
+        <v>0.02006190708890354</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.137459091376417</v>
+        <v>3.165179595132298</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.568940374610322</v>
+        <v>1.638241634000026</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.098875481376678</v>
+        <v>4.1404562370105</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.04420176157321348</v>
+        <v>0.02509949781649007</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.13805156785279</v>
+        <v>3.165772071608671</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.62458483087664</v>
+        <v>1.693886090266343</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.130839595321806</v>
+        <v>4.172420350955628</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.3013957962812702</v>
+        <v>-0.2320945368915667</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.013920335593304</v>
+        <v>3.041640839349186</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.367390796168583</v>
+        <v>1.436692055558286</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.95526955612071</v>
+        <v>3.996850311754532</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.3671631863306823</v>
+        <v>-0.2978619269409787</v>
       </c>
       <c r="E1842" t="n">
-        <v>2.988630988704009</v>
+        <v>3.016351492459891</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.367390796168583</v>
+        <v>1.436692055558286</v>
       </c>
       <c r="G1842" t="n">
-        <v>3.95628716525118</v>
+        <v>3.997867920885001</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.5724078633879268</v>
+        <v>-0.5031066039982233</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.897161149868867</v>
+        <v>2.924881653624749</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.367390796168583</v>
+        <v>1.436692055558286</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.946915197238935</v>
+        <v>3.988495952872757</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.6541797638156785</v>
+        <v>-0.584878504425975</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.854535115653005</v>
+        <v>2.882255619408886</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.394426369574719</v>
+        <v>1.463727628964423</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.953219267237856</v>
+        <v>3.994800022871678</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7213888716875563</v>
+        <v>-0.6520876122978527</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.832416789337956</v>
+        <v>2.860137293093838</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.394426369574719</v>
+        <v>1.463727628964423</v>
       </c>
       <c r="G1845" t="n">
-        <v>3.957984584071558</v>
+        <v>3.99956533970538</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.9289546560791682</v>
+        <v>-0.8596533966894646</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.747215271700552</v>
+        <v>2.774935775456433</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.186860585183108</v>
+        <v>1.256161844572811</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.831269909555831</v>
+        <v>3.872850665189653</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.346708679626005</v>
+        <v>-1.277407420236302</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.57804055378688</v>
+        <v>2.605761057542761</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.7691065616362706</v>
+        <v>0.8384078210259739</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.578544386932792</v>
+        <v>3.620125142566614</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.636840346231436</v>
+        <v>-1.567539086841733</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.461854103743629</v>
+        <v>2.48957460749951</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.7931883563764505</v>
+        <v>0.8624896157661538</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.592859680375822</v>
+        <v>3.634440436009644</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.844844404584514</v>
+        <v>-1.77554314519481</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.383544624956324</v>
+        <v>2.411265128712205</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.7931883563764505</v>
+        <v>0.8624896157661538</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.597751824929747</v>
+        <v>3.639332580563569</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.056256825472489</v>
+        <v>-1.986955566082786</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.294061112939122</v>
+        <v>2.321781616695003</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.5817759354884754</v>
+        <v>0.6510771948781787</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.46598582873495</v>
+        <v>3.507566584368772</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.422325552617142</v>
+        <v>-2.353024293227438</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.14071792138771</v>
+        <v>2.168438425143591</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.2157072083438227</v>
+        <v>0.2850084677335261</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.239428891754608</v>
+        <v>3.28100964738843</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.630816334068826</v>
+        <v>-2.561515074679123</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.077659898545804</v>
+        <v>2.105380402301686</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.007216426892138306</v>
+        <v>0.07651768628184163</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.134672712622365</v>
+        <v>3.176253468256187</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.878017518834048</v>
+        <v>-2.808716259444345</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.986878175048284</v>
+        <v>2.014598678804165</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.02736978039095073</v>
+        <v>0.09667103978065406</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.154863475130221</v>
+        <v>3.196444230764043</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.370402546858144</v>
+        <v>-3.301101287468442</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.791030555882378</v>
+        <v>1.818751059638259</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.465015247633146</v>
+        <v>-0.3957139882434427</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.860538850359495</v>
+        <v>2.902119605993317</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.755582937788217</v>
+        <v>-3.686281678398514</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.635500938323212</v>
+        <v>1.663221442079093</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.465015247633146</v>
+        <v>-0.3957139882434427</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.859081389172359</v>
+        <v>2.90066214480618</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.005453617802798</v>
+        <v>-3.936152358413096</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.537321789771996</v>
+        <v>1.565042293527877</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.4287525278026827</v>
+        <v>-0.3594512684129794</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.882608144525252</v>
+        <v>2.924188900159075</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.21196539468982</v>
+        <v>-4.142664135300117</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.450823137673445</v>
+        <v>1.478543641429326</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6352643046897042</v>
+        <v>-0.5659630453000009</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.754807137049298</v>
+        <v>2.79638789268312</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.531309469770322</v>
+        <v>-4.462008210380619</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.324858434341504</v>
+        <v>1.352578938097385</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6352643046897042</v>
+        <v>-0.5659630453000009</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.756580063749557</v>
+        <v>2.798160819383379</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.963115262920109</v>
+        <v>-4.893814003530406</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.138469004548993</v>
+        <v>1.166189508304874</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7716818011309712</v>
+        <v>-0.7023805417412678</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.661062453352201</v>
+        <v>2.702643208986023</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.197809257052661</v>
+        <v>-5.128507997662958</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.032876181898063</v>
+        <v>1.060596685653944</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.765345533901716</v>
+        <v>-0.6960442745120127</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.653148988691845</v>
+        <v>2.694729744325667</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.533471904283114</v>
+        <v>-5.464170644893411</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8971917146618469</v>
+        <v>0.9249122184177279</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8332765193906209</v>
+        <v>-0.7639752600009175</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.610970989054468</v>
+        <v>2.65255174468829</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.897098149183427</v>
+        <v>-5.827796889793724</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.758228776935963</v>
+        <v>0.7859492806918444</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9314981562577467</v>
+        <v>-0.8621968968680433</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.558525567168433</v>
+        <v>2.600106322802255</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.262225531822174</v>
+        <v>-6.192924272432471</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6114323388862957</v>
+        <v>0.6391528426421771</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.227808940556759</v>
+        <v>-1.158507681167056</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.379993611594857</v>
+        <v>2.42157436722868</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.670814309002852</v>
+        <v>-6.60151304961315</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4467583720287838</v>
+        <v>0.4744788757846643</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.567096458347734</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.133601889301209</v>
+        <v>2.175182644935032</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.947390409318684</v>
+        <v>-6.878089149928982</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3313133643739112</v>
+        <v>0.3590338681297922</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.567096458347734</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.12878732177267</v>
+        <v>2.170368077406492</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.363782283605682</v>
+        <v>-7.29448102421598</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1627506652679895</v>
+        <v>0.1904711690238705</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.567096458347734</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.126781372381547</v>
+        <v>2.16836212801537</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.608053684332751</v>
+        <v>-7.538752424943049</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.07530079564584069</v>
+        <v>0.1030212994017217</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.567096458347734</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.137040063050226</v>
+        <v>2.178620818684049</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.813304703569512</v>
+        <v>-7.74400344417981</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.01070004690316795</v>
+        <v>0.01702045685271258</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.567096458347734</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.133139628195922</v>
+        <v>2.174720383829744</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.976884581753895</v>
+        <v>-7.907583322364193</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.07772707812192037</v>
+        <v>-0.05000657436603984</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.567096458347734</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.131544548250923</v>
+        <v>2.173125303884745</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.273545923564093</v>
+        <v>-8.204244664174391</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1926126389167915</v>
+        <v>-0.1648921351609109</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.635839594081613</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.094077642739804</v>
+        <v>2.135658398373625</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.460265631873396</v>
+        <v>-8.390964372483694</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2713268267749158</v>
+        <v>-0.2436063230190353</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.635839594081613</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.0900513382054</v>
+        <v>2.131632093839222</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.843267020616027</v>
+        <v>-8.773965761226325</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4246294835935522</v>
+        <v>-0.3969089798376717</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.635839594081613</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.089949236883816</v>
+        <v>2.131529992517638</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.025136811601062</v>
+        <v>-8.95583555221136</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4948058840161362</v>
+        <v>-0.4670853802602553</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.887010644456351</v>
+        <v>-1.817709385066648</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.983398878264226</v>
+        <v>2.024979633898047</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.384667134105063</v>
+        <v>-9.315365874715361</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6332677097196866</v>
+        <v>-0.6055472059638056</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.887010644456351</v>
+        <v>-1.817709385066648</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.988749181562276</v>
+        <v>2.030329937196098</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.435016197559285</v>
+        <v>-9.365714938169583</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6454913151441981</v>
+        <v>-0.6177708113883171</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.937359707910573</v>
+        <v>-1.86805844852087</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.96645576344692</v>
+        <v>2.008036519080742</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.532635474980681</v>
+        <v>-9.463334215590979</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6814972754909876</v>
+        <v>-0.6537767717351066</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.03497898533197</v>
+        <v>-1.965677725942267</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.91092594761585</v>
+        <v>1.952506703249673</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.680161562986324</v>
+        <v>-9.610860303596622</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7376141543716725</v>
+        <v>-0.7098936506157916</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.182505073337614</v>
+        <v>-2.11320381394791</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.825303851134037</v>
+        <v>1.866884606767859</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.884419738316188</v>
+        <v>-9.815118478926486</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8138042273849755</v>
+        <v>-0.786083723629095</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.310144017951603</v>
+        <v>-2.240842758561899</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.754233681484286</v>
+        <v>1.795814437118108</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.918072576824661</v>
+        <v>-9.848771317434959</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8227828083039288</v>
+        <v>-0.7950623045480483</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.41055738586864</v>
+        <v>-2.341256126478936</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.698468215218499</v>
+        <v>1.740048970852322</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.844602745157212</v>
+        <v>-9.77530148576751</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7780231741435282</v>
+        <v>-0.7503026703876472</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.337087554201192</v>
+        <v>-2.267786294811488</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.757921815712389</v>
+        <v>1.799502571346212</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.01972716254376</v>
+        <v>-9.950425903154054</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8335177203506285</v>
+        <v>-0.805797216594748</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.512211971587735</v>
+        <v>-2.442910712198032</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.66740238602798</v>
+        <v>1.708983141661802</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410274</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.25417925655825</v>
+        <v>-10.18487799716854</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9345177228580206</v>
+        <v>-0.9067972191021396</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.512211971587735</v>
+        <v>-2.442910712198032</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.660183221126384</v>
+        <v>1.701763976760206</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.35855398758469</v>
+        <v>-10.28925272819499</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9829398060425754</v>
+        <v>-0.9552193022866944</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.616586702614181</v>
+        <v>-2.547285443224478</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.59088619173654</v>
+        <v>1.632466947370363</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.41134014318502</v>
+        <v>-10.34203888379532</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.00293847844415</v>
+        <v>-0.9752179746882685</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.712262189196578</v>
+        <v>-2.642960929806875</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.534596689625658</v>
+        <v>1.576177445259481</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.53737693655331</v>
+        <v>-10.46807567716361</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.050659467162351</v>
+        <v>-1.02293896340647</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.687010566386836</v>
+        <v>-2.617709306997132</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.552441391940618</v>
+        <v>1.594022147574441</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.48536142258449</v>
+        <v>-10.41606016319479</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.025862925888425</v>
+        <v>-0.9981424221325437</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.687010566386836</v>
+        <v>-2.617709306997132</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.556431727627019</v>
+        <v>1.598012483260842</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.62703326430861</v>
+        <v>-10.55773200491891</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.084006889476814</v>
+        <v>-1.056286385720933</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.687010566386836</v>
+        <v>-2.617709306997132</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.554956500728278</v>
+        <v>1.5965372563621</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.57744241988378</v>
+        <v>-10.50814116049408</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.049117141542009</v>
+        <v>-1.021396637786128</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.637419721962002</v>
+        <v>-2.568118462572298</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.59976441754805</v>
+        <v>1.641345173181872</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.56463502687901</v>
+        <v>-10.4953337674893</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.057045317986782</v>
+        <v>-1.029324814230901</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.686275496970903</v>
+        <v>-2.6169742375812</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.557399818896027</v>
+        <v>1.598980574529849</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.33878987415959</v>
+        <v>-10.26948861476989</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9571281838628081</v>
+        <v>-0.929407680106928</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.64434882138374</v>
+        <v>-2.575047561994036</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.592134897284533</v>
+        <v>1.633715652918356</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.214211217822</v>
+        <v>-10.1449099584323</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9061575767717129</v>
+        <v>-0.8784370730158328</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.64434882138374</v>
+        <v>-2.575047561994036</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.593274041840592</v>
+        <v>1.634854797474415</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.26710650586629</v>
+        <v>-10.19780524647659</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9246819178273196</v>
+        <v>-0.8969614140714395</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.639393475295293</v>
+        <v>-2.57009221590559</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.598881023655768</v>
+        <v>1.64046177928959</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.19497333057841</v>
+        <v>-10.12567207118871</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8900949434735308</v>
+        <v>-0.8623744397176507</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.639393475295293</v>
+        <v>-2.57009221590559</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.604614727894404</v>
+        <v>1.646195483528226</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.12360693796876</v>
+        <v>-10.05430567857906</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8712856488235374</v>
+        <v>-0.8435651450676573</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.568027082685645</v>
+        <v>-2.498725823295942</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.637697301066328</v>
+        <v>1.67927805670015</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.03014790398354</v>
+        <v>-9.960846644593836</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8437855165423547</v>
+        <v>-0.8160650127864746</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.568027082685645</v>
+        <v>-2.498725823295942</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.62781381975342</v>
+        <v>1.669394575387243</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.762906103115139</v>
+        <v>-9.693604843725439</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7387233566943694</v>
+        <v>-0.7110028529384893</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.568027082685645</v>
+        <v>-2.498725823295942</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.625979259254047</v>
+        <v>1.667560014887869</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.664999064438648</v>
+        <v>-9.595697805048948</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6998608561972341</v>
+        <v>-0.6721403524413541</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.500041332825089</v>
+        <v>-2.430740073435385</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.66647039419692</v>
+        <v>1.708051149830742</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.64104552346269</v>
+        <v>-9.57174426407299</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6896109336613572</v>
+        <v>-0.6618904299054771</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.476087791849131</v>
+        <v>-2.406786532459428</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.681511024927988</v>
+        <v>1.72309178056181</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.376985585139893</v>
+        <v>-9.307684325750193</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5972472744939905</v>
+        <v>-0.5695267707381104</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.212027853526335</v>
+        <v>-2.142726594136632</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.826686671759913</v>
+        <v>1.868267427393735</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.669905961635056</v>
+        <v>-8.600604702245356</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3172024587523565</v>
+        <v>-0.2894819549964764</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.212027853526335</v>
+        <v>-2.142726594136632</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.823899638099612</v>
+        <v>1.865480393733435</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.629721663268866</v>
+        <v>-8.560420403879165</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.300785115518039</v>
+        <v>-0.2730646117621589</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.171843555160144</v>
+        <v>-2.102542295770441</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.848353841007168</v>
+        <v>1.88993459664099</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.466321792329502</v>
+        <v>-8.397020532939802</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2360583459215366</v>
+        <v>-0.2083378421656565</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.008443684220782</v>
+        <v>-1.939142424831078</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.945760584791542</v>
+        <v>1.987341340425365</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.232840570099903</v>
+        <v>-8.163539310710203</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1347414281918446</v>
+        <v>-0.1070209244359646</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.774962461991183</v>
+        <v>-1.70566120260148</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.093773746967154</v>
+        <v>2.135354502600976</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.083174179092389</v>
+        <v>-8.013872919702688</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07776708210179795</v>
+        <v>-0.05004657834591786</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.682058970748648</v>
+        <v>-1.612757711358944</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.146623631399716</v>
+        <v>2.188204387033539</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.950898705461502</v>
+        <v>-7.881597446071802</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.02948940590241644</v>
+        <v>-0.001768902146536355</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.549783497117761</v>
+        <v>-1.480482237728057</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.221356402325275</v>
+        <v>2.262937157959098</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.79516037290176</v>
+        <v>-7.72585911351206</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.03562098780911693</v>
+        <v>0.06334149156499702</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.394045164558019</v>
+        <v>-1.324743905168316</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.317614462548757</v>
+        <v>2.359195218182579</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.546160574218179</v>
+        <v>-7.476859314828479</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1481272485062082</v>
+        <v>0.1758477522620883</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.394045164558019</v>
+        <v>-1.324743905168316</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.330520803772416</v>
+        <v>2.372101559406238</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.651750563991284</v>
+        <v>-7.582449304601584</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.02208467700225247</v>
+        <v>0.005635826753627615</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.499635154331124</v>
+        <v>-1.43033389494142</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.139190880309334</v>
+        <v>2.180771635943157</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.670485466109881</v>
+        <v>-7.60118420672018</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.01896570402739517</v>
+        <v>0.04668620778327526</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.505231163991255</v>
+        <v>-1.435929904601551</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.184377616390342</v>
+        <v>2.225958372024164</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.522545424702281</v>
+        <v>-7.453244165312581</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.04173720209773268</v>
+        <v>-0.0140166983418526</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.484910248082697</v>
+        <v>-1.415608988692994</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.076691243247309</v>
+        <v>2.118271998881131</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.469575902448293</v>
+        <v>-7.400274643058593</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.02926337944961555</v>
+        <v>-0.001542875693735457</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.431940725828709</v>
+        <v>-1.362639466439005</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.099758970346224</v>
+        <v>2.141339725980046</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.426027495677602</v>
+        <v>-7.356726236287902</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.01880462883643252</v>
+        <v>0.008915874919447564</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.431940725828709</v>
+        <v>-1.362639466439005</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.092798358251131</v>
+        <v>2.134379113884953</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.183879102223744</v>
+        <v>-7.114577842834044</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.09251708292625382</v>
+        <v>0.1202375866821339</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.431940725828709</v>
+        <v>-1.362639466439005</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.107260712632274</v>
+        <v>2.148841468266096</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.075619965101223</v>
+        <v>-7.006318705711522</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1303528582344575</v>
+        <v>0.1580733619903376</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.431940725828709</v>
+        <v>-1.362639466439005</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.101792833091469</v>
+        <v>2.143373588725291</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.952328830284092</v>
+        <v>-6.883027570894392</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1771674061718866</v>
+        <v>0.2048879099277667</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.308649591011578</v>
+        <v>-1.239348331621875</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.173265607992324</v>
+        <v>2.214846363626147</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.931179631380648</v>
+        <v>-6.861878371990948</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1933280639705894</v>
+        <v>0.2210485677264695</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.287500392108135</v>
+        <v>-1.218199132718431</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.193656105571716</v>
+        <v>2.235236861205538</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.687414189397204</v>
+        <v>-6.618112930007504</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2866149491110179</v>
+        <v>0.314335452866898</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.287500392108135</v>
+        <v>-1.218199132718431</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.189436813918766</v>
+        <v>2.231017569552588</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.585651369119909</v>
+        <v>-6.516350109730209</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3294443911419518</v>
+        <v>0.3571648948978319</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.274281323715706</v>
+        <v>-1.204980064326002</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.199492568874239</v>
+        <v>2.241073324508061</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.335800975170835</v>
+        <v>-6.266499715781134</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4221266237052839</v>
+        <v>0.449847127461164</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.274281323715706</v>
+        <v>-1.204980064326002</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.192234643857941</v>
+        <v>2.233815399491764</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.159908882703402</v>
+        <v>-6.090607623313701</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4960825842129055</v>
+        <v>0.5238030879687856</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.274281323715706</v>
+        <v>-1.204980064326002</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.19583376737859</v>
+        <v>2.237414523012412</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.988462419680938</v>
+        <v>-5.919161160291238</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5779886754764449</v>
+        <v>0.605709179232325</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.102834860693243</v>
+        <v>-1.033533601303539</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.312029151246622</v>
+        <v>2.353609906880444</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.914172853942599</v>
+        <v>-5.844871594552899</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6067249793880776</v>
+        <v>0.6344454831439577</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.028545294954904</v>
+        <v>-0.9592440355651999</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.355623368305922</v>
+        <v>2.397204123939745</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.850537111708665</v>
+        <v>-5.781235852318964</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6368740773359685</v>
+        <v>0.6645945810918485</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9649095527209691</v>
+        <v>-0.8956082933312653</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.3984996147006</v>
+        <v>2.440080370334423</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.739110352382744</v>
+        <v>-5.669809092993044</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6626390398501321</v>
+        <v>0.6903595436060121</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9649095527209691</v>
+        <v>-0.8956082933312653</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.379693873484396</v>
+        <v>2.421274629118218</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.498679855577884</v>
+        <v>-5.429378596188184</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7605543151969538</v>
+        <v>0.7882748189528339</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7244790559161088</v>
+        <v>-0.6551777965264051</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.52569524819219</v>
+        <v>2.567276003826012</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.42643728740669</v>
+        <v>-5.357136028016989</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7933806563002519</v>
+        <v>0.821101160056132</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7244790559161088</v>
+        <v>-0.6551777965264051</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.52962456202701</v>
+        <v>2.571205317660832</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.373438965125302</v>
+        <v>-5.304137705735601</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.815258569130147</v>
+        <v>0.8429790728860271</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.66914279691417</v>
+        <v>-0.5998415375244662</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.563504901345513</v>
+        <v>2.605085656979335</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.264634079645575</v>
+        <v>-5.195332820255874</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8557785945420311</v>
+        <v>0.8834990982979112</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.66914279691417</v>
+        <v>-0.5998415375244662</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.560502972565506</v>
+        <v>2.602083728199329</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.044613281608564</v>
+        <v>-4.975312022218864</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9453659507674494</v>
+        <v>0.9730864545233295</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5279229518461898</v>
+        <v>-0.458621692456486</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.646813916616909</v>
+        <v>2.688394672250731</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.911745592545286</v>
+        <v>-4.842444333155586</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.014407209194584</v>
+        <v>1.042127712950464</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5279229518461898</v>
+        <v>-0.458621692456486</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.662708099418732</v>
+        <v>2.704288855052555</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.791572509180788</v>
+        <v>-4.722271249791087</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.063622286980685</v>
+        <v>1.091342790736565</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4077498684816908</v>
+        <v>-0.338448609091987</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.735957793877733</v>
+        <v>2.777538549511556</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.64690036408105</v>
+        <v>-4.57759910469135</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.13157924758202</v>
+        <v>1.1592997513379</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2630777233819534</v>
+        <v>-0.1937764639922496</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.832849183499015</v>
+        <v>2.874429939132838</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.706775191438743</v>
+        <v>-4.637473932049042</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.093666808040369</v>
+        <v>1.121387311796249</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3229525507396455</v>
+        <v>-0.2536512913499417</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.782961778485826</v>
+        <v>2.824542534119649</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.619975693659734</v>
+        <v>-4.550674434270034</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.150787100474538</v>
+        <v>1.178507604230419</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3229525507396455</v>
+        <v>-0.2536512913499417</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.805362271808392</v>
+        <v>2.846943027442215</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.62244540012154</v>
+        <v>-4.55314414073184</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.149871619263228</v>
+        <v>1.177592123019108</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3254222572014517</v>
+        <v>-0.2561209978117479</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.803952849304721</v>
+        <v>2.845533604938543</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.690815586445551</v>
+        <v>-4.62151432705585</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.133530467208326</v>
+        <v>1.161250970964206</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.246845298775533</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.820525191201152</v>
+        <v>2.862105946834974</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.704603639292597</v>
+        <v>-4.635302379902897</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.118451954701399</v>
+        <v>1.146172458457279</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.246845298775533</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.810961899833043</v>
+        <v>2.852542655466865</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.735596798621303</v>
+        <v>-4.666295539231602</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9307642560103033</v>
+        <v>0.9584847597661834</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.246845298775533</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.63567146487343</v>
+        <v>2.677252220507252</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.560122538828834</v>
+        <v>-4.490821279439134</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.005521191919079</v>
+        <v>1.033241695674959</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.246845298775533</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.640238696865218</v>
+        <v>2.68181945249904</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.671058791470083</v>
+        <v>-4.601757532080383</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9368887196237861</v>
+        <v>0.9646092233796661</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.246845298775533</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.615980725626425</v>
+        <v>2.657561481260247</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.637395245997801</v>
+        <v>-4.5680939866081</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9534855230326045</v>
+        <v>0.9812060267884846</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2824830126929549</v>
+        <v>-0.2131817533032511</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.6393102381297</v>
+        <v>2.680890993763521</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.577542626794077</v>
+        <v>-4.508241367404377</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9875989571462263</v>
+        <v>1.015319460902106</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2824830126929549</v>
+        <v>-0.2131817533032511</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.649482624561832</v>
+        <v>2.691063380195654</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.4912991637677</v>
+        <v>-4.421997904377999</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.017042612930638</v>
+        <v>1.044763116686518</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2824830126929549</v>
+        <v>-0.2131817533032511</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.644428895135692</v>
+        <v>2.686009650769514</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.536605983166679</v>
+        <v>-4.467304723776979</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9906956606155712</v>
+        <v>1.018416164371451</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3232931757021857</v>
+        <v>-0.2539919163124819</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.611718572774679</v>
+        <v>2.653299328408501</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.565639087868981</v>
+        <v>-4.49633782847928</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9796342917677523</v>
+        <v>1.007354795523632</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3232931757021857</v>
+        <v>-0.2539919163124819</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.612270445807781</v>
+        <v>2.653851201441603</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.47155341805472</v>
+        <v>-4.403527347028421</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9465412515848222</v>
+        <v>0.9737516799953418</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2292075058879245</v>
+        <v>-0.1611814348616226</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.597994539587703</v>
+        <v>2.638810182203484</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.515942887384147</v>
+        <v>-4.447916816357848</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9306589397776521</v>
+        <v>0.9578693681881718</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2735969752173522</v>
+        <v>-0.2055709041910502</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.573234333914647</v>
+        <v>2.614049976530429</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.403271669147897</v>
+        <v>-4.335245598121598</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9708031355838751</v>
+        <v>0.9980135639943948</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.160925756981102</v>
+        <v>-0.09289968595480003</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.63591277336812</v>
+        <v>2.676728415983902</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.290894667965224</v>
+        <v>-4.222868596938925</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.021245231887612</v>
+        <v>1.048455660298131</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.160925756981102</v>
+        <v>-0.09289968595480003</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.641404069198788</v>
+        <v>2.682219711814569</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.318675065866577</v>
+        <v>-4.250648994840278</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.02163027449561</v>
+        <v>1.048840702906129</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1887061548824551</v>
+        <v>-0.1206800838561531</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.636233032226515</v>
+        <v>2.677048674842296</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.401676346891856</v>
+        <v>-4.333650275865557</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8267854820861513</v>
+        <v>0.853995910496671</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2072770394096288</v>
+        <v>-0.1392509683833268</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.463446221510864</v>
+        <v>2.504261864126645</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.510290425335187</v>
+        <v>-4.442264354308888</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9034895114280244</v>
+        <v>0.930699939838544</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2072770394096288</v>
+        <v>-0.1392509683833268</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.583595882230069</v>
+        <v>2.624411524845851</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.474881387087044</v>
+        <v>-4.406855316060745</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9321661528296046</v>
+        <v>0.9593765812401243</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2072770394096288</v>
+        <v>-0.1392509683833268</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.598108908332392</v>
+        <v>2.638924550948174</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.436497724528893</v>
+        <v>-4.368471653502594</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9449390591952338</v>
+        <v>0.9721494876057535</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1688933768514777</v>
+        <v>-0.1008673058251757</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.618558547209652</v>
+        <v>2.659374189825433</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.259381394493727</v>
+        <v>-4.191355323467428</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.012514620054602</v>
+        <v>1.039725048465122</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1688933768514777</v>
+        <v>-0.1008673058251757</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.615287576054954</v>
+        <v>2.656103218670735</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.304473639327273</v>
+        <v>-4.236447568300973</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9951611138830969</v>
+        <v>1.022371542293617</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2307894200208674</v>
+        <v>-0.1627633489945655</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.578833341915233</v>
+        <v>2.619648984531014</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.125098218088505</v>
+        <v>-4.057072147062206</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.060698257685018</v>
+        <v>1.087908686095538</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.07401266185014876</v>
+        <v>-0.005986590823846782</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.666686372124079</v>
+        <v>2.70750201473986</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.170112431609111</v>
+        <v>-4.102086360582812</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.023500027608366</v>
+        <v>1.050710456018885</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1043615571647534</v>
+        <v>-0.03633548613845139</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.629284490266905</v>
+        <v>2.670100132882687</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.437116941881546</v>
+        <v>-4.369090870855247</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9223897858383374</v>
+        <v>0.9496002142488571</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2987245952077019</v>
+        <v>-0.2306985241814</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.518358229780082</v>
+        <v>2.559173872395863</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.538314723318718</v>
+        <v>-4.470288652292419</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8811145951599699</v>
+        <v>0.9083250235704896</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3671334087530211</v>
+        <v>-0.2991073377267192</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.476516863549392</v>
+        <v>2.517332506165173</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.531803756704406</v>
+        <v>-4.463777685678107</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8813189433600117</v>
+        <v>0.9085293717705314</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3671334087530211</v>
+        <v>-0.2991073377267192</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.474116825103709</v>
+        <v>2.51493246771949</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.512765628997109</v>
+        <v>-4.444739557970809</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8854589136511755</v>
+        <v>0.9126693420616951</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4253170200842157</v>
+        <v>-0.3572909490579137</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.435731377513237</v>
+        <v>2.476547020129018</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.543892260147727</v>
+        <v>-4.475866189121428</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.050590130129609</v>
+        <v>1.077800558540128</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4253170200842157</v>
+        <v>-0.3572909490579137</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.613313246451918</v>
+        <v>2.654128889067699</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.557759021481645</v>
+        <v>-4.489732950455346</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.045876754582175</v>
+        <v>1.073087182992695</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4631749368180386</v>
+        <v>-0.3951488657917366</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.591431825397757</v>
+        <v>2.632247468013539</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.512954849941715</v>
+        <v>-4.444928778915416</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.069806953595073</v>
+        <v>1.097017382005593</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4631749368180386</v>
+        <v>-0.3951488657917366</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.597440355794683</v>
+        <v>2.638255998410465</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.365211879706712</v>
+        <v>-4.297185808680413</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.208056789481096</v>
+        <v>1.235267217891616</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2953675795831555</v>
+        <v>-0.2273415085568535</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.777277417927635</v>
+        <v>2.818093060543416</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.467226562237934</v>
+        <v>-4.399200491211634</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.170044538000088</v>
+        <v>1.197254966410608</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2953675795831555</v>
+        <v>-0.2273415085568535</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.780071039459116</v>
+        <v>2.820886682074897</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.461073856185149</v>
+        <v>-4.39304778515885</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.17316796881286</v>
+        <v>1.20037839722338</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2892148735303712</v>
+        <v>-0.2211888025040692</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.784425011482445</v>
+        <v>2.825240654098226</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.477883154335651</v>
+        <v>-4.409857083309352</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.16552472629277</v>
+        <v>1.19273515470329</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3060241716808728</v>
+        <v>-0.2379981006545708</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.773419909332254</v>
+        <v>2.814235551948035</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.415585155559529</v>
+        <v>-4.34755908453323</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.25677947960004</v>
+        <v>1.283989908010559</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3060241716808728</v>
+        <v>-0.2379981006545708</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.839755463129075</v>
+        <v>2.880571105744856</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.213794957894371</v>
+        <v>-4.145768886868072</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.046076431055501</v>
+        <v>1.073286859466021</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1080059795117184</v>
+        <v>-0.03997990848541644</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.667147250819966</v>
+        <v>2.707962893435747</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.140416860805635</v>
+        <v>-4.072390789779336</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.145717902213171</v>
+        <v>1.17292833062369</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.03462788242298187</v>
+        <v>0.03339818860332011</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.781464341395383</v>
+        <v>2.822279984011164</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.238157405430609</v>
+        <v>-4.17013133440431</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.121249420479224</v>
+        <v>1.148459848889744</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.05051716055596206</v>
+        <v>0.01750891047033992</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.786558510631639</v>
+        <v>2.827374153247419</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.414495165553538</v>
+        <v>-4.346469094527239</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.049250297254724</v>
+        <v>1.076460725665244</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2268549206788915</v>
+        <v>-0.1588288496525895</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.679291835382553</v>
+        <v>2.720107477998334</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.338073119121612</v>
+        <v>-4.270047048095313</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.078310733867424</v>
+        <v>1.105521162277944</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2268549206788915</v>
+        <v>-0.1588288496525895</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.677783453422481</v>
+        <v>2.718599096038262</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.293699987483043</v>
+        <v>-4.225673916456744</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.095922853958287</v>
+        <v>1.123133282368807</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1824817890403229</v>
+        <v>-0.1144557180140209</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.704270199841059</v>
+        <v>2.74508584245684</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.808153067403842</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.170865766595876</v>
+        <v>-4.102839695569577</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.139450336451745</v>
+        <v>1.166660764862264</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1824817890403229</v>
+        <v>-0.1144557180140209</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.698663993979649</v>
+        <v>2.73947963659543</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.814534824431647</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.12321003603482</v>
+        <v>-4.055183965008521</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.164894385703971</v>
+        <v>1.192104814114491</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1348260584792672</v>
+        <v>-0.06679998745296523</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.733639189344086</v>
+        <v>2.774454831959868</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.819427197806371</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.022691877536065</v>
+        <v>-3.954665806509766</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.209994022478198</v>
+        <v>1.237204450888718</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.03430789998051265</v>
+        <v>0.03371817104578934</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.798842457818064</v>
+        <v>2.839658100433845</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.806181870282244</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.083358467938455</v>
+        <v>-4.015332396912155</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.172482058793114</v>
+        <v>1.199692487203634</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1160062166990463</v>
+        <v>-0.04798014567274433</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.736578140262816</v>
+        <v>2.777393782878598</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.810279572892872</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.038520066330056</v>
+        <v>-3.970493995303757</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.194515122047102</v>
+        <v>1.221725550457622</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1114627837541768</v>
+        <v>-0.04343671272787486</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.743401902640366</v>
+        <v>2.784217545256148</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.81444051252395</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.139278702087054</v>
+        <v>-4.071252631060756</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.158372607375381</v>
+        <v>1.185583035785901</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2002883524811823</v>
+        <v>-0.1322622814548803</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.694267501035241</v>
+        <v>2.735083143651022</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.820320115051787</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.095075865001154</v>
+        <v>-4.027049793974856</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.181933344737579</v>
+        <v>1.209143773148098</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1560855153952818</v>
+        <v>-0.08805944436897983</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.726668805814619</v>
+        <v>2.7674844484304</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.818730115521035</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.132054892664597</v>
+        <v>-4.064028821638299</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.165551734141449</v>
+        <v>1.192762162551968</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1191116136039513</v>
+        <v>-0.0510855425776493</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.747263147358665</v>
+        <v>2.788078789974445</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.869977880704075</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.152112971529437</v>
+        <v>-4.08408690050314</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.208776267778553</v>
+        <v>1.235986696189071</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1191116136039513</v>
+        <v>-0.0510855425776493</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.798510912541704</v>
+        <v>2.839326555157485</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.868418585298328</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.112182298351547</v>
+        <v>-4.044156227325249</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.223189241643962</v>
+        <v>1.250399670054481</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.07918094042606094</v>
+        <v>-0.01115486939975896</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.820910021042692</v>
+        <v>2.861725663658472</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.863366813536598</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.061150205629019</v>
+        <v>-3.993124134602721</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.238550306971243</v>
+        <v>1.265760735381762</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.02814884770353299</v>
+        <v>0.039877223322769</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.846477504914478</v>
+        <v>2.887293147530259</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.880554217629303</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.995926024501814</v>
+        <v>-3.927899953475515</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.28182738351483</v>
+        <v>1.309037811925349</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.03707533342367264</v>
+        <v>0.1051014044499746</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.902799417683506</v>
+        <v>2.943615060299288</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.876515189928583</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.95849900443068</v>
+        <v>-3.890472933404382</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.292759163842564</v>
+        <v>1.319969592253083</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.0423268714528543</v>
+        <v>0.1103529424791563</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.901911312800296</v>
+        <v>2.942726955416077</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.877771982259823</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.978610660465388</v>
+        <v>-3.91058458943909</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.285971293759921</v>
+        <v>1.31318172217044</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.0533542164502735</v>
+        <v>0.1213802874765755</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.909784512129988</v>
+        <v>2.950600154745769</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.038329753281034</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.924865846038184</v>
+        <v>-3.856839775011885</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.468026990552013</v>
+        <v>1.495237418962533</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.06341752589073546</v>
+        <v>0.1314435969170374</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.076380268815476</v>
+        <v>3.117195911431257</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.158442662498851</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.901074277432041</v>
+        <v>-3.833048206405743</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.597656527212288</v>
+        <v>1.624866955622807</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.08720909449687775</v>
+        <v>0.1552351655231797</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.210768119196978</v>
+        <v>3.251583761812759</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15015063851271</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.874990193168233</v>
+        <v>-3.806964122141935</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.59979813693167</v>
+        <v>1.627008565342189</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.08720909449687775</v>
+        <v>0.1552351655231797</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.202476095210837</v>
+        <v>3.243291737826618</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.14834383409649</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.796859012319286</v>
+        <v>-3.728832941292988</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.629243804855028</v>
+        <v>1.656454233265547</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1613859053805623</v>
+        <v>0.2294119764068643</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.245175377324828</v>
+        <v>3.285991019940608</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.165898239823281</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.787966550926003</v>
+        <v>-3.719940479899705</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.650355195139132</v>
+        <v>1.677565623549652</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1613859053805623</v>
+        <v>0.2294119764068643</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.262729783051619</v>
+        <v>3.3035454256674</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.157753287227865</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.956442667895881</v>
+        <v>-3.888416596869583</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.574819795755765</v>
+        <v>1.602030224166285</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1334380696639815</v>
+        <v>0.2014641406902835</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.237816129026254</v>
+        <v>3.278631771642035</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.139022984415727</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.258643139034298</v>
+        <v>-3.190617068008</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.83520930448826</v>
+        <v>1.86241973289878</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.06309001029357081</v>
+        <v>0.1311160813198728</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.176876990591869</v>
+        <v>3.217692633207651</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.129687006912631</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.235922035351146</v>
+        <v>-3.167895964324847</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.834961768458426</v>
+        <v>1.862172196868945</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.06309001029357081</v>
+        <v>0.1311160813198728</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.167541013088774</v>
+        <v>3.208356655704555</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.2885931327638</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.234196992061102</v>
+        <v>-3.166170921034803</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.994557911625613</v>
+        <v>2.021768340036132</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.06481505358361456</v>
+        <v>0.1328411246099165</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.327482164913969</v>
+        <v>3.368297807529751</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.325670955257447</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.388977998839357</v>
+        <v>-3.320951927813058</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.969723331407957</v>
+        <v>1.996933759818476</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.03144737952913845</v>
+        <v>0.09947345055544043</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.344539382974931</v>
+        <v>3.385355025590711</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.322346311246992</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.337542665454697</v>
+        <v>-3.269516594428399</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.986972820751366</v>
+        <v>2.014183249161885</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.08288271291379812</v>
+        <v>0.1509087839401001</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.372075938995271</v>
+        <v>3.412891581611052</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.332352464891734</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.310591441128209</v>
+        <v>-3.242565370101911</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.007759464126703</v>
+        <v>2.034969892537222</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.09776305894151727</v>
+        <v>0.1657891299678192</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.391010300256645</v>
+        <v>3.431825942872425</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.516455597036694</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.446544449184525</v>
+        <v>-3.378518378158227</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.137481393049136</v>
+        <v>2.164691821459655</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.09776305894151727</v>
+        <v>0.1657891299678192</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.575113432401604</v>
+        <v>3.615929075017385</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.508572291939687</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.468952566989397</v>
+        <v>-3.400926495963099</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.120634840830181</v>
+        <v>2.1478452692407</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.09776305894151727</v>
+        <v>0.1657891299678192</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.567230127304597</v>
+        <v>3.608045769920378</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.510626291489324</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.616958334468797</v>
+        <v>-3.548932263442499</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.063486533388058</v>
+        <v>2.090696961798577</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.01103605007797581</v>
+        <v>0.07906212110427779</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.51724792153611</v>
+        <v>3.558063564151891</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.566880009211171</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.626399260357327</v>
+        <v>-3.558373189331029</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.115963880754493</v>
+        <v>2.143174309165012</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.1334631676213672</v>
+        <v>0.2014892386476692</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.646957909783992</v>
+        <v>3.687773552399773</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.569771103756472</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.625112496817771</v>
+        <v>-3.557086425791472</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.119369680715617</v>
+        <v>2.146580109126136</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.1347499311609238</v>
+        <v>0.2027760021872258</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.650621062453027</v>
+        <v>3.691436705068808</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.567882916650247</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.626669550807062</v>
+        <v>-3.558643479780764</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.116858672013676</v>
+        <v>2.144069100424194</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.1347499311609238</v>
+        <v>0.2027760021872258</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.648732875346802</v>
+        <v>3.689548517962583</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.56270314625311</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.633941436330526</v>
+        <v>-3.565915365304228</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.108770147407152</v>
+        <v>2.135980575817671</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.1274780456374591</v>
+        <v>0.1955041166637611</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.639189973635585</v>
+        <v>3.680005616251366</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.561137156463262</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.632100417272275</v>
+        <v>-3.564074346245977</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.107940565240605</v>
+        <v>2.135150993651124</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.1287462723089275</v>
+        <v>0.1967723433352295</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.638384919848618</v>
+        <v>3.6792005624644</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.574210563329181</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.639009122771956</v>
+        <v>-3.570983051745658</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.118250489906651</v>
+        <v>2.14546091831717</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.1287462723089275</v>
+        <v>0.1967723433352295</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.651458326714537</v>
+        <v>3.692273969330318</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.574210563329181</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.640570765586816</v>
+        <v>-3.572544694560517</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.117625832780707</v>
+        <v>2.144836261191227</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.1287462723089275</v>
+        <v>0.1967723433352295</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.651458326714537</v>
+        <v>3.692273969330318</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.572734604456183</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.668471552696289</v>
+        <v>-3.60044548166999</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.10498955906392</v>
+        <v>2.132199987474439</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.09414934816599269</v>
+        <v>0.1621754191922947</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.629224213355779</v>
+        <v>3.670039855971559</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.485674679777246</v>
+        <v>3.779485757366279</v>
       </c>
       <c r="C2014" t="n">
         <v>3.569499048433381</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.671504550208962</v>
+        <v>-3.603478479182664</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.100540804036049</v>
+        <v>2.127751232446569</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.0911163506533188</v>
+        <v>0.1591424216796208</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.624168858825373</v>
+        <v>3.664984501441154</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240704.xlsx
+++ b/tame_output/ON/bt/strategyON_20240704.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>55.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,37 +834,37 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>70.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.0%</t>
+          <t>-72.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.8%</t>
+          <t>122.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,31 +973,31 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-674.4%</t>
+          <t>-655.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-49.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.4%</t>
+          <t>-67.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.2%</t>
+          <t>423.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-521.9%</t>
+          <t>-507.2%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,26 +1131,26 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-270.2%</t>
+          <t>-262.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-32.7%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-163.4%</t>
+          <t>-157.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-293.6%</t>
+          <t>-300.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-32.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-180.3%</t>
+          <t>-228.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-208.1%</t>
+          <t>-222.9%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,11 +1447,11 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-176.6%</t>
+          <t>-180.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-65.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2014"/>
+  <dimension ref="A1:G2015"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.2571933989386986</v>
+        <v>0.1878921395489951</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.225091107374675</v>
+        <v>3.197370603618793</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.638241634000026</v>
+        <v>1.568940374610322</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.105515152512958</v>
+        <v>4.063934396879136</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386092</v>
+        <v>3.376932391386093</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.02006190708890354</v>
+        <v>0.2097835746314828</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.165179595132298</v>
+        <v>3.24106826214933</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.638241634000026</v>
+        <v>1.568940374610322</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.1404562370105</v>
+        <v>4.098875481376678</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998559</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.02509949781649007</v>
+        <v>0.2148211653590694</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.165772071608671</v>
+        <v>3.241660738625703</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.693886090266343</v>
+        <v>1.62458483087664</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.172420350955628</v>
+        <v>4.130839595321806</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082124</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2320945368915667</v>
+        <v>-0.04237286934898737</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.041640839349186</v>
+        <v>3.117529506366217</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.436692055558286</v>
+        <v>1.367390796168583</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.996850311754532</v>
+        <v>3.95526955612071</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.293490533757923</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.2978619269409787</v>
+        <v>-0.1081402593983994</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.016351492459891</v>
+        <v>3.092240159476923</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.436692055558286</v>
+        <v>1.367390796168583</v>
       </c>
       <c r="G1842" t="n">
-        <v>3.997867920885001</v>
+        <v>3.95628716525118</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.293766719760741</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.5031066039982233</v>
+        <v>-0.313384936455644</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.924881653624749</v>
+        <v>3.00077032064178</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.436692055558286</v>
+        <v>1.367390796168583</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.988495952872757</v>
+        <v>3.946915197238935</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706668</v>
+        <v>3.298730590706669</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.584878504425975</v>
+        <v>-0.3951568368833957</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.882255619408886</v>
+        <v>2.958144286425918</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.463727628964423</v>
+        <v>1.394426369574719</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.994800022871678</v>
+        <v>3.953219267237856</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6520876122978527</v>
+        <v>-0.4623659447552734</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.860137293093838</v>
+        <v>2.936025960110869</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.463727628964423</v>
+        <v>1.394426369574719</v>
       </c>
       <c r="G1845" t="n">
-        <v>3.99956533970538</v>
+        <v>3.957984584071558</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.8596533966894646</v>
+        <v>-0.6699317291468853</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.774935775456433</v>
+        <v>2.850824442473465</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.256161844572811</v>
+        <v>1.186860585183108</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.872850665189653</v>
+        <v>3.831269909555831</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.277407420236302</v>
+        <v>-1.087685752693722</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.605761057542761</v>
+        <v>2.681649724559793</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.8384078210259739</v>
+        <v>0.7691065616362706</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.620125142566614</v>
+        <v>3.578544386932792</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.567539086841733</v>
+        <v>-1.377817419299154</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.48957460749951</v>
+        <v>2.565463274516542</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.8624896157661538</v>
+        <v>0.7931883563764505</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.634440436009644</v>
+        <v>3.592859680375822</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.77554314519481</v>
+        <v>-1.585821477652231</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.411265128712205</v>
+        <v>2.487153795729236</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.8624896157661538</v>
+        <v>0.7931883563764505</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.639332580563569</v>
+        <v>3.597751824929747</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.986955566082786</v>
+        <v>-1.797233898540206</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.321781616695003</v>
+        <v>2.397670283712035</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6510771948781787</v>
+        <v>0.5817759354884754</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.507566584368772</v>
+        <v>3.46598582873495</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.353024293227438</v>
+        <v>-2.163302625684858</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.168438425143591</v>
+        <v>2.244327092160623</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.2850084677335261</v>
+        <v>0.2157072083438227</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.28100964738843</v>
+        <v>3.239428891754608</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.561515074679123</v>
+        <v>-2.371793407136543</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.105380402301686</v>
+        <v>2.181269069318717</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.07651768628184163</v>
+        <v>0.007216426892138306</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.176253468256187</v>
+        <v>3.134672712622365</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.808716259444345</v>
+        <v>-2.618994591901764</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.014598678804165</v>
+        <v>2.090487345821197</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.09667103978065406</v>
+        <v>0.02736978039095073</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.196444230764043</v>
+        <v>3.154863475130221</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.301101287468442</v>
+        <v>-3.111379619925861</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.818751059638259</v>
+        <v>1.894639726655291</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.3957139882434427</v>
+        <v>-0.465015247633146</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.902119605993317</v>
+        <v>2.860538850359495</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.686281678398514</v>
+        <v>-3.496560010855934</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.663221442079093</v>
+        <v>1.739110109096125</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.3957139882434427</v>
+        <v>-0.465015247633146</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.90066214480618</v>
+        <v>2.859081389172359</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.936152358413096</v>
+        <v>-3.746430690870515</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.565042293527877</v>
+        <v>1.640930960544909</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.3594512684129794</v>
+        <v>-0.4287525278026827</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.924188900159075</v>
+        <v>2.882608144525252</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.142664135300117</v>
+        <v>-3.952942467757536</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.478543641429326</v>
+        <v>1.554432308446358</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.5659630453000009</v>
+        <v>-0.6352643046897042</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.79638789268312</v>
+        <v>2.754807137049298</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.462008210380619</v>
+        <v>-4.272286542838039</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.352578938097385</v>
+        <v>1.428467605114417</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.5659630453000009</v>
+        <v>-0.6352643046897042</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.798160819383379</v>
+        <v>2.756580063749557</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.893814003530406</v>
+        <v>-4.704092335987826</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.166189508304874</v>
+        <v>1.242078175321906</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7023805417412678</v>
+        <v>-0.7716818011309712</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.702643208986023</v>
+        <v>2.661062453352201</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.128507997662958</v>
+        <v>-4.938786330120378</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.060596685653944</v>
+        <v>1.136485352670976</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.6960442745120127</v>
+        <v>-0.765345533901716</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.694729744325667</v>
+        <v>2.653148988691845</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.464170644893411</v>
+        <v>-5.274448977350831</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9249122184177279</v>
+        <v>1.00080088543476</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.7639752600009175</v>
+        <v>-0.8332765193906209</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.65255174468829</v>
+        <v>2.610970989054468</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.827796889793724</v>
+        <v>-5.638075222251144</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7859492806918444</v>
+        <v>0.8618379477088762</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.8621968968680433</v>
+        <v>-0.9314981562577467</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.600106322802255</v>
+        <v>2.558525567168433</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.192924272432471</v>
+        <v>-6.003202604889891</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6391528426421771</v>
+        <v>0.7150415096592089</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.158507681167056</v>
+        <v>-1.227808940556759</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.42157436722868</v>
+        <v>2.379993611594857</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.60151304961315</v>
+        <v>-6.41179138207057</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4744788757846643</v>
+        <v>0.5503675428016965</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.567096458347734</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.175182644935032</v>
+        <v>2.133601889301209</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.878089149928982</v>
+        <v>-6.688367482386402</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3590338681297922</v>
+        <v>0.434922535146824</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.567096458347734</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.170368077406492</v>
+        <v>2.12878732177267</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.29448102421598</v>
+        <v>-7.1047593566734</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1904711690238705</v>
+        <v>0.2663598360409023</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.567096458347734</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.16836212801537</v>
+        <v>2.126781372381547</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.538752424943049</v>
+        <v>-7.349030757400469</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1030212994017217</v>
+        <v>0.1789099664187535</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.567096458347734</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.178620818684049</v>
+        <v>2.137040063050226</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.74400344417981</v>
+        <v>-7.55428177663723</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.01702045685271258</v>
+        <v>0.09290912386974481</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.567096458347734</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.174720383829744</v>
+        <v>2.133139628195922</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.907583322364193</v>
+        <v>-7.717861654821613</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.05000657436603984</v>
+        <v>0.02588209265099239</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.567096458347734</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.173125303884745</v>
+        <v>2.131544548250923</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.204244664174391</v>
+        <v>-8.014522996631811</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1648921351609109</v>
+        <v>-0.08900346814387872</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.635839594081613</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.135658398373625</v>
+        <v>2.094077642739804</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.390964372483694</v>
+        <v>-8.201242704941114</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2436063230190353</v>
+        <v>-0.1677176560020031</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.635839594081613</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.131632093839222</v>
+        <v>2.0900513382054</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.773965761226325</v>
+        <v>-8.584244093683745</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.3969089798376717</v>
+        <v>-0.3210203128206395</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.635839594081613</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.131529992517638</v>
+        <v>2.089949236883816</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.95583555221136</v>
+        <v>-8.76611388466878</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4670853802602553</v>
+        <v>-0.3911967132432235</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.817709385066648</v>
+        <v>-1.887010644456351</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.024979633898047</v>
+        <v>1.983398878264226</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.315365874715361</v>
+        <v>-9.125644207172781</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6055472059638056</v>
+        <v>-0.5296585389467738</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.817709385066648</v>
+        <v>-1.887010644456351</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.030329937196098</v>
+        <v>1.988749181562276</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.365714938169583</v>
+        <v>-9.175993270627004</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6177708113883171</v>
+        <v>-0.5418821443712853</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.86805844852087</v>
+        <v>-1.937359707910573</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.008036519080742</v>
+        <v>1.96645576344692</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539466</v>
+        <v>3.501052558539464</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.463334215590979</v>
+        <v>-9.2736125480484</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6537767717351066</v>
+        <v>-0.5778881047180748</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.965677725942267</v>
+        <v>-2.03497898533197</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.952506703249673</v>
+        <v>1.91092594761585</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937501</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.610860303596622</v>
+        <v>-9.421138636054042</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7098936506157916</v>
+        <v>-0.6340049835987598</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.11320381394791</v>
+        <v>-2.182505073337614</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.866884606767859</v>
+        <v>1.825303851134037</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141704</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.815118478926486</v>
+        <v>-9.625396811383906</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.786083723629095</v>
+        <v>-0.7101950566120627</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.240842758561899</v>
+        <v>-2.310144017951603</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.795814437118108</v>
+        <v>1.754233681484286</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729893</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.848771317434959</v>
+        <v>-9.659049649892379</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.7950623045480483</v>
+        <v>-0.719173637531016</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.341256126478936</v>
+        <v>-2.41055738586864</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.740048970852322</v>
+        <v>1.698468215218499</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440636</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.77530148576751</v>
+        <v>-9.585579818224931</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7503026703876472</v>
+        <v>-0.6744140033706154</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.267786294811488</v>
+        <v>-2.337087554201192</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.799502571346212</v>
+        <v>1.757921815712389</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.950425903154054</v>
+        <v>-9.760704235611474</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.805797216594748</v>
+        <v>-0.7299085495777158</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.442910712198032</v>
+        <v>-2.512211971587735</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.708983141661802</v>
+        <v>1.66740238602798</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.18487799716854</v>
+        <v>-9.995156329625964</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9067972191021396</v>
+        <v>-0.8309085520851078</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.442910712198032</v>
+        <v>-2.512211971587735</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.701763976760206</v>
+        <v>1.660183221126384</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.28925272819499</v>
+        <v>-10.09953106065241</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9552193022866944</v>
+        <v>-0.8793306352696626</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.547285443224478</v>
+        <v>-2.616586702614181</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.632466947370363</v>
+        <v>1.59088619173654</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.34203888379532</v>
+        <v>-10.15231721625274</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.9752179746882685</v>
+        <v>-0.8993293076712368</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.642960929806875</v>
+        <v>-2.712262189196578</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.576177445259481</v>
+        <v>1.534596689625658</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.46807567716361</v>
+        <v>-10.27835400962103</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.02293896340647</v>
+        <v>-0.9470502963894378</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.617709306997132</v>
+        <v>-2.687010566386836</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.594022147574441</v>
+        <v>1.552441391940618</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322546</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.41606016319479</v>
+        <v>-10.22633849565221</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.9981424221325437</v>
+        <v>-0.9222537551155119</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.617709306997132</v>
+        <v>-2.687010566386836</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.598012483260842</v>
+        <v>1.556431727627019</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.55773200491891</v>
+        <v>-10.36801033737633</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.056286385720933</v>
+        <v>-0.9803977187039017</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.617709306997132</v>
+        <v>-2.687010566386836</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.5965372563621</v>
+        <v>1.554956500728278</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.50814116049408</v>
+        <v>-10.3184194929515</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.021396637786128</v>
+        <v>-0.9455079707690959</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.568118462572298</v>
+        <v>-2.637419721962002</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.641345173181872</v>
+        <v>1.59976441754805</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770583</v>
+        <v>3.676841549770582</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.4953337674893</v>
+        <v>-10.30561209994672</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.029324814230901</v>
+        <v>-0.953436147213869</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.6169742375812</v>
+        <v>-2.686275496970903</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.598980574529849</v>
+        <v>1.557399818896027</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615287</v>
+        <v>3.685161381615286</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.26948861476989</v>
+        <v>-10.07976694722731</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.929407680106928</v>
+        <v>-0.8535190130898953</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.575047561994036</v>
+        <v>-2.64434882138374</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.633715652918356</v>
+        <v>1.592134897284533</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812106</v>
+        <v>3.684843823812105</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.1449099584323</v>
+        <v>-9.955188290889721</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.8784370730158328</v>
+        <v>-0.8025484059988002</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.575047561994036</v>
+        <v>-2.64434882138374</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.634854797474415</v>
+        <v>1.593274041840592</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646221</v>
+        <v>3.710935533646219</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.19780524647659</v>
+        <v>-10.00808357893401</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.8969614140714395</v>
+        <v>-0.8210727470544068</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.57009221590559</v>
+        <v>-2.639393475295293</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.64046177928959</v>
+        <v>1.598881023655768</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611572</v>
+        <v>3.768951674611571</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.12567207118871</v>
+        <v>-9.935950403646126</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8623744397176507</v>
+        <v>-0.786485772700618</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.57009221590559</v>
+        <v>-2.639393475295293</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.646195483528226</v>
+        <v>1.604614727894404</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955332</v>
+        <v>3.72857792995533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.05430567857906</v>
+        <v>-9.864584011036479</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8435651450676573</v>
+        <v>-0.7676764780506242</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.498725823295942</v>
+        <v>-2.568027082685645</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.67927805670015</v>
+        <v>1.637697301066328</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232417</v>
+        <v>3.747702660232416</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.960846644593836</v>
+        <v>-9.771124977051254</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8160650127864746</v>
+        <v>-0.7401763457694419</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.498725823295942</v>
+        <v>-2.568027082685645</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.669394575387243</v>
+        <v>1.62781381975342</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436234</v>
+        <v>3.766317079436232</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.693604843725439</v>
+        <v>-9.503883176182857</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7110028529384893</v>
+        <v>-0.6351141859214566</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.498725823295942</v>
+        <v>-2.568027082685645</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.667560014887869</v>
+        <v>1.625979259254047</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311954</v>
+        <v>3.784684521311952</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.595697805048948</v>
+        <v>-9.405976137506366</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6721403524413541</v>
+        <v>-0.5962516854243214</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.430740073435385</v>
+        <v>-2.500041332825089</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.708051149830742</v>
+        <v>1.66647039419692</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409725</v>
+        <v>3.800829354097248</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.57174426407299</v>
+        <v>-9.382022596530408</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6618904299054771</v>
+        <v>-0.5860017628884444</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.406786532459428</v>
+        <v>-2.476087791849131</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.72309178056181</v>
+        <v>1.681511024927988</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017778</v>
+        <v>3.789311112017776</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.307684325750193</v>
+        <v>-9.117962658207611</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5695267707381104</v>
+        <v>-0.4936381037210777</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.142726594136632</v>
+        <v>-2.212027853526335</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.868267427393735</v>
+        <v>1.826686671759913</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83325274783973</v>
+        <v>3.833252747839729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.600604702245356</v>
+        <v>-8.410883034702774</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2894819549964764</v>
+        <v>-0.2135932879794438</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.142726594136632</v>
+        <v>-2.212027853526335</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.865480393733435</v>
+        <v>1.823899638099612</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388735</v>
+        <v>3.839374447388733</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.560420403879165</v>
+        <v>-8.370698736336584</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2730646117621589</v>
+        <v>-0.1971759447451262</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.102542295770441</v>
+        <v>-2.171843555160144</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.88993459664099</v>
+        <v>1.848353841007168</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626481</v>
+        <v>3.856161751626479</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.397020532939802</v>
+        <v>-8.20729886539722</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2083378421656565</v>
+        <v>-0.1324491751486239</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.939142424831078</v>
+        <v>-2.008443684220782</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.987341340425365</v>
+        <v>1.945760584791542</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291817</v>
+        <v>3.787330429291815</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.163539310710203</v>
+        <v>-7.973817643167622</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1070209244359646</v>
+        <v>-0.03113225741893233</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.70566120260148</v>
+        <v>-1.774962461991183</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.135354502600976</v>
+        <v>2.093773746967154</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785793</v>
+        <v>3.801637122785791</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.013872919702688</v>
+        <v>-7.824151252160107</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.05004657834591786</v>
+        <v>0.02584208867111482</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.612757711358944</v>
+        <v>-1.682058970748648</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.188204387033539</v>
+        <v>2.146623631399716</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390433</v>
+        <v>3.763182248390431</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.881597446071802</v>
+        <v>-7.69187577852922</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.001768902146536355</v>
+        <v>0.07411976487049632</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.480482237728057</v>
+        <v>-1.549783497117761</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.262937157959098</v>
+        <v>2.221356402325275</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.72585911351206</v>
+        <v>-7.536137445969478</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.06334149156499702</v>
+        <v>0.1392301585820297</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.324743905168316</v>
+        <v>-1.394045164558019</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.359195218182579</v>
+        <v>2.317614462548757</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960992</v>
+        <v>3.753882571960991</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.476859314828479</v>
+        <v>-7.287137647285897</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1758477522620883</v>
+        <v>0.2517364192791209</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.324743905168316</v>
+        <v>-1.394045164558019</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.372101559406238</v>
+        <v>2.330520803772416</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607651</v>
+        <v>3.69293185560765</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.582449304601584</v>
+        <v>-7.392727637059002</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.005635826753627615</v>
+        <v>0.08152449377066029</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.43033389494142</v>
+        <v>-1.499635154331124</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.180771635943157</v>
+        <v>2.139190880309334</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.77042258398791</v>
+        <v>3.770422583987908</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.60118420672018</v>
+        <v>-7.411462539177599</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.04668620778327526</v>
+        <v>0.1225748748003079</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.435929904601551</v>
+        <v>-1.505231163991255</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.225958372024164</v>
+        <v>2.184377616390342</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710817</v>
+        <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.453244165312581</v>
+        <v>-7.263522497769999</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.0140166983418526</v>
+        <v>0.06187196867518008</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.415608988692994</v>
+        <v>-1.484910248082697</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.118271998881131</v>
+        <v>2.076691243247309</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.72356622940921</v>
+        <v>3.723566229409208</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.400274643058593</v>
+        <v>-7.210552975516011</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.001542875693735457</v>
+        <v>0.07434579132329722</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.362639466439005</v>
+        <v>-1.431940725828709</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.141339725980046</v>
+        <v>2.099758970346224</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098115</v>
+        <v>3.729969716098113</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.356726236287902</v>
+        <v>-7.167004568745321</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.008915874919447564</v>
+        <v>0.08480454193648024</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.362639466439005</v>
+        <v>-1.431940725828709</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.134379113884953</v>
+        <v>2.092798358251131</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493426</v>
+        <v>3.782922533493424</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.114577842834044</v>
+        <v>-6.924856175291462</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1202375866821339</v>
+        <v>0.1961262536991666</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.362639466439005</v>
+        <v>-1.431940725828709</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.148841468266096</v>
+        <v>2.107260712632274</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722822</v>
+        <v>3.828551486722821</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.006318705711522</v>
+        <v>-6.816597038168941</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1580733619903376</v>
+        <v>0.2339620290073703</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.362639466439005</v>
+        <v>-1.431940725828709</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.143373588725291</v>
+        <v>2.101792833091469</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.883027570894392</v>
+        <v>-6.69330590335181</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2048879099277667</v>
+        <v>0.2807765769447994</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.239348331621875</v>
+        <v>-1.308649591011578</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.214846363626147</v>
+        <v>2.173265607992324</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919913</v>
+        <v>3.812453678919912</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.861878371990948</v>
+        <v>-6.672156704448367</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2210485677264695</v>
+        <v>0.2969372347435022</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.218199132718431</v>
+        <v>-1.287500392108135</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.235236861205538</v>
+        <v>2.193656105571716</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318099</v>
+        <v>3.748328408318097</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.618112930007504</v>
+        <v>-6.428391262464922</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.314335452866898</v>
+        <v>0.3902241198839307</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.218199132718431</v>
+        <v>-1.287500392108135</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.231017569552588</v>
+        <v>2.189436813918766</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057532</v>
+        <v>3.82431123305753</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.516350109730209</v>
+        <v>-6.326628442187627</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3571648948978319</v>
+        <v>0.4330535619148645</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.204980064326002</v>
+        <v>-1.274281323715706</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.241073324508061</v>
+        <v>2.199492568874239</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279192</v>
+        <v>3.82635497427919</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.266499715781134</v>
+        <v>-6.076778048238553</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.449847127461164</v>
+        <v>0.5257357944781966</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.204980064326002</v>
+        <v>-1.274281323715706</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.233815399491764</v>
+        <v>2.192234643857941</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011505</v>
+        <v>3.835957987011502</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.090607623313701</v>
+        <v>-5.90088595577112</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5238030879687856</v>
+        <v>0.5996917549858183</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.204980064326002</v>
+        <v>-1.274281323715706</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.237414523012412</v>
+        <v>2.19583376737859</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392994</v>
+        <v>3.780933911392991</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.919161160291238</v>
+        <v>-5.729439492748656</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.605709179232325</v>
+        <v>0.6815978462493577</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.033533601303539</v>
+        <v>-1.102834860693243</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.353609906880444</v>
+        <v>2.312029151246622</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632789</v>
+        <v>3.773765222632785</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.844871594552899</v>
+        <v>-5.655149927010317</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6344454831439577</v>
+        <v>0.7103341501609903</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9592440355651999</v>
+        <v>-1.028545294954904</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.397204123939745</v>
+        <v>2.355623368305922</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883081</v>
+        <v>3.764617879883078</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.781235852318964</v>
+        <v>-5.591514184776383</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6645945810918485</v>
+        <v>0.7404832481088812</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8956082933312653</v>
+        <v>-0.9649095527209691</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.440080370334423</v>
+        <v>2.3984996147006</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074792</v>
+        <v>3.798814771074788</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.669809092993044</v>
+        <v>-5.480087425450463</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6903595436060121</v>
+        <v>0.7662482106230448</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8956082933312653</v>
+        <v>-0.9649095527209691</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.421274629118218</v>
+        <v>2.379693873484396</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242303</v>
+        <v>3.7976948842423</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.429378596188184</v>
+        <v>-5.239656928645602</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7882748189528339</v>
+        <v>0.8641634859698666</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6551777965264051</v>
+        <v>-0.7244790559161088</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.567276003826012</v>
+        <v>2.52569524819219</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367694</v>
+        <v>3.82159350936769</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.357136028016989</v>
+        <v>-5.167414360474408</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.821101160056132</v>
+        <v>0.8969898270731647</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6551777965264051</v>
+        <v>-0.7244790559161088</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.571205317660832</v>
+        <v>2.52962456202701</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879975</v>
+        <v>3.822326997879971</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.304137705735601</v>
+        <v>-5.11441603819302</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8429790728860271</v>
+        <v>0.9188677399030598</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5998415375244662</v>
+        <v>-0.66914279691417</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.605085656979335</v>
+        <v>2.563504901345513</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502347</v>
+        <v>3.848616626502343</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.195332820255874</v>
+        <v>-5.005611152713293</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8834990982979112</v>
+        <v>0.9593877653149439</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5998415375244662</v>
+        <v>-0.66914279691417</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.602083728199329</v>
+        <v>2.560502972565506</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675948</v>
+        <v>3.818668951675945</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.975312022218864</v>
+        <v>-4.785590354676282</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9730864545233295</v>
+        <v>1.048975121540362</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.458621692456486</v>
+        <v>-0.5279229518461898</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.688394672250731</v>
+        <v>2.646813916616909</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539959</v>
+        <v>3.843274527539956</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.842444333155586</v>
+        <v>-4.652722665613005</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.042127712950464</v>
+        <v>1.118016379967497</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.458621692456486</v>
+        <v>-0.5279229518461898</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.704288855052555</v>
+        <v>2.662708099418732</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496267</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.722271249791087</v>
+        <v>-4.532549582248506</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.091342790736565</v>
+        <v>1.167231457753598</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.338448609091987</v>
+        <v>-0.4077498684816908</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.777538549511556</v>
+        <v>2.735957793877733</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577004</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.57759910469135</v>
+        <v>-4.387877437148768</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.1592997513379</v>
+        <v>1.235188418354933</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1937764639922496</v>
+        <v>-0.2630777233819534</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.874429939132838</v>
+        <v>2.832849183499015</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942109</v>
+        <v>3.735839222942106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.637473932049042</v>
+        <v>-4.447752264506461</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.121387311796249</v>
+        <v>1.197275978813282</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2536512913499417</v>
+        <v>-0.3229525507396455</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.824542534119649</v>
+        <v>2.782961778485826</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674521</v>
+        <v>3.762647477674518</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.550674434270034</v>
+        <v>-4.360952766727452</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.178507604230419</v>
+        <v>1.254396271247451</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2536512913499417</v>
+        <v>-0.3229525507396455</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.846943027442215</v>
+        <v>2.805362271808392</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.7291463984307</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.55314414073184</v>
+        <v>-4.363422473189258</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.177592123019108</v>
+        <v>1.253480790036141</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2561209978117479</v>
+        <v>-0.3254222572014517</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.845533604938543</v>
+        <v>2.803952849304721</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003609</v>
+        <v>3.743220196003605</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.62151432705585</v>
+        <v>-4.431792659513269</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.161250970964206</v>
+        <v>1.237139637981239</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.246845298775533</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.862105946834974</v>
+        <v>2.820525191201152</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508377</v>
+        <v>3.714179139508373</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.635302379902897</v>
+        <v>-4.445580712360315</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.146172458457279</v>
+        <v>1.222061125474311</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.246845298775533</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.852542655466865</v>
+        <v>2.810961899833043</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417712</v>
+        <v>3.710906731417708</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.666295539231602</v>
+        <v>-4.476573871689021</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9584847597661834</v>
+        <v>1.034373426783216</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.246845298775533</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.677252220507252</v>
+        <v>2.63567146487343</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205908</v>
+        <v>3.746042526205905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.490821279439134</v>
+        <v>-4.301099611896552</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.033241695674959</v>
+        <v>1.109130362691992</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.246845298775533</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.68181945249904</v>
+        <v>2.640238696865218</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225453</v>
+        <v>3.765024323225449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.601757532080383</v>
+        <v>-4.412035864537801</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9646092233796661</v>
+        <v>1.040497890396699</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.246845298775533</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.657561481260247</v>
+        <v>2.615980725626425</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111302</v>
+        <v>3.773210297111298</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.5680939866081</v>
+        <v>-4.378372319065519</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9812060267884846</v>
+        <v>1.057094693805517</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2131817533032511</v>
+        <v>-0.2824830126929549</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.680890993763521</v>
+        <v>2.6393102381297</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264171</v>
+        <v>3.784343952264168</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.508241367404377</v>
+        <v>-4.318519699861795</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.015319460902106</v>
+        <v>1.091208127919139</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2131817533032511</v>
+        <v>-0.2824830126929549</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.691063380195654</v>
+        <v>2.649482624561832</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742308</v>
+        <v>3.786949957742304</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.421997904377999</v>
+        <v>-4.232276236835418</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.044763116686518</v>
+        <v>1.12065178370355</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2131817533032511</v>
+        <v>-0.2824830126929549</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.686009650769514</v>
+        <v>2.644428895135692</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316054</v>
+        <v>3.752027499316051</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.467304723776979</v>
+        <v>-4.277583056234397</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.018416164371451</v>
+        <v>1.094304831388484</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2539919163124819</v>
+        <v>-0.3232931757021857</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.653299328408501</v>
+        <v>2.611718572774679</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.7535711658032</v>
+        <v>3.753571165803196</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.49633782847928</v>
+        <v>-4.306616160936699</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.007354795523632</v>
+        <v>1.083243462540665</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2539919163124819</v>
+        <v>-0.3232931757021857</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.653851201441603</v>
+        <v>2.612270445807781</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809507</v>
+        <v>3.733390600809503</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.403527347028421</v>
+        <v>-4.213805679485839</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9737516799953418</v>
+        <v>1.049640347012375</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1611814348616226</v>
+        <v>-0.2304826942513263</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.638810182203484</v>
+        <v>2.597229426569662</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560434</v>
+        <v>3.748285816560432</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.447916816357848</v>
+        <v>-4.258195148815267</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9578693681881718</v>
+        <v>1.033758035205204</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2055709041910502</v>
+        <v>-0.274872163580754</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.614049976530429</v>
+        <v>2.572469220896606</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472747</v>
+        <v>3.721077195472744</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.335245598121598</v>
+        <v>-4.145523930579016</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9980135639943948</v>
+        <v>1.073902231011427</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.09289968595480003</v>
+        <v>-0.1622009453445038</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.676728415983902</v>
+        <v>2.635147660350079</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798546</v>
+        <v>3.743047603798543</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.222868596938925</v>
+        <v>-4.033146929396343</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.048455660298131</v>
+        <v>1.124344327315164</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.09289968595480003</v>
+        <v>-0.1622009453445038</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.682219711814569</v>
+        <v>2.640638956180747</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498874</v>
+        <v>3.689597840498871</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.250648994840278</v>
+        <v>-4.060927327297696</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.048840702906129</v>
+        <v>1.124729369923162</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1206800838561531</v>
+        <v>-0.1899813432458569</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.677048674842296</v>
+        <v>2.635467919208474</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705335</v>
+        <v>3.643069621705331</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.333650275865557</v>
+        <v>-4.143928608322975</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.853995910496671</v>
+        <v>0.9298845775137037</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1392509683833268</v>
+        <v>-0.2085522277730306</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.504261864126645</v>
+        <v>2.462681108492823</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729279</v>
+        <v>3.682716310729276</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.442264354308888</v>
+        <v>-4.252542686766306</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.930699939838544</v>
+        <v>1.006588606855577</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1392509683833268</v>
+        <v>-0.2085522277730306</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.624411524845851</v>
+        <v>2.582830769212028</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190779</v>
+        <v>3.733012441190775</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.406855316060745</v>
+        <v>-4.217133648518163</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9593765812401243</v>
+        <v>1.035265248257157</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1392509683833268</v>
+        <v>-0.2085522277730306</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.638924550948174</v>
+        <v>2.597343795314351</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913436</v>
+        <v>3.741174069913432</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.368471653502594</v>
+        <v>-4.178749985960012</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9721494876057535</v>
+        <v>1.048038154622786</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1008673058251757</v>
+        <v>-0.1701685652148794</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.659374189825433</v>
+        <v>2.617793434191611</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532497</v>
+        <v>3.751147197532493</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.191355323467428</v>
+        <v>-4.001633655924846</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.039725048465122</v>
+        <v>1.115613715482154</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1008673058251757</v>
+        <v>-0.1701685652148794</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.656103218670735</v>
+        <v>2.614522463036913</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793914</v>
+        <v>3.741328448793911</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.236447568300973</v>
+        <v>-4.046725900758392</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.022371542293617</v>
+        <v>1.098260209310649</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1627633489945655</v>
+        <v>-0.2320646083842692</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.619648984531014</v>
+        <v>2.578068228897192</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011247</v>
+        <v>3.750729377011243</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.057072147062206</v>
+        <v>-3.867350479519624</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.087908686095538</v>
+        <v>1.163797353112571</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.005986590823846782</v>
+        <v>-0.07528785021355056</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.70750201473986</v>
+        <v>2.665921259106037</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982241</v>
+        <v>3.716991718982237</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.102086360582812</v>
+        <v>-3.91236469304023</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.050710456018885</v>
+        <v>1.126599123035918</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.03633548613845139</v>
+        <v>-0.1056367455281552</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.670100132882687</v>
+        <v>2.628519377248864</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702660850955</v>
+        <v>3.737026608509546</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.369090870855247</v>
+        <v>-4.179369203312666</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9496002142488571</v>
+        <v>1.02548888126589</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2306985241814</v>
+        <v>-0.2999997835711037</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.559173872395863</v>
+        <v>2.517593116762041</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760821</v>
+        <v>3.702309454760817</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.470288652292419</v>
+        <v>-4.280566984749838</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9083250235704896</v>
+        <v>0.9842136905875218</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2991073377267192</v>
+        <v>-0.3684085971164229</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.517332506165173</v>
+        <v>2.475751750531351</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815465</v>
+        <v>3.705571661815462</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.463777685678107</v>
+        <v>-4.274056018135526</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9085293717705314</v>
+        <v>0.9844180387875636</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2991073377267192</v>
+        <v>-0.3684085971164229</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.51493246771949</v>
+        <v>2.473351712085668</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378109</v>
+        <v>3.709510443378107</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.444739557970809</v>
+        <v>-4.255017890428229</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9126693420616951</v>
+        <v>0.9885580090787274</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3572909490579137</v>
+        <v>-0.4265922084476175</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.476547020129018</v>
+        <v>2.434966264495196</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313126</v>
+        <v>3.731064473131258</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.475866189121428</v>
+        <v>-4.286144521578847</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.077800558540128</v>
+        <v>1.153689225557161</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3572909490579137</v>
+        <v>-0.4265922084476175</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.654128889067699</v>
+        <v>2.612548133433877</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067877</v>
+        <v>3.722447362067873</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.489732950455346</v>
+        <v>-4.300011282912765</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.073087182992695</v>
+        <v>1.148975850009727</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3951488657917366</v>
+        <v>-0.4644501251814404</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.632247468013539</v>
+        <v>2.590666712379716</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789133</v>
+        <v>3.787425580789129</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.444928778915416</v>
+        <v>-4.255207111372835</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.097017382005593</v>
+        <v>1.172906049022625</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3951488657917366</v>
+        <v>-0.4644501251814404</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.638255998410465</v>
+        <v>2.596675242776642</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051992</v>
+        <v>3.781501250519916</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.297185808680413</v>
+        <v>-4.107464141137832</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.235267217891616</v>
+        <v>1.311155884908648</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2273415085568535</v>
+        <v>-0.2966427679465573</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.818093060543416</v>
+        <v>2.776512304909594</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181182</v>
+        <v>3.802245929181178</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.399200491211634</v>
+        <v>-4.209478823669054</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.197254966410608</v>
+        <v>1.27314363342764</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2273415085568535</v>
+        <v>-0.2966427679465573</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.820886682074897</v>
+        <v>2.779305926441075</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394742</v>
+        <v>3.805608985394739</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.39304778515885</v>
+        <v>-4.203326117616269</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.20037839722338</v>
+        <v>1.276267064240412</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2211888025040692</v>
+        <v>-0.290490061893773</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.825240654098226</v>
+        <v>2.783659898464404</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890619</v>
+        <v>3.798239794890618</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.409857083309352</v>
+        <v>-4.220135415766771</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.19273515470329</v>
+        <v>1.268623821720322</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2379981006545708</v>
+        <v>-0.3072993600442746</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.814235551948035</v>
+        <v>2.772654796314213</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798436</v>
+        <v>3.867362636798433</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.34755908453323</v>
+        <v>-4.157837416990649</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.283989908010559</v>
+        <v>1.359878575027592</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2379981006545708</v>
+        <v>-0.3072993600442746</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.880571105744856</v>
+        <v>2.838990350111034</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992203</v>
+        <v>3.8487291399922</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.145768886868072</v>
+        <v>-3.956047219325491</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.073286859466021</v>
+        <v>1.149175526483053</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.03997990848541644</v>
+        <v>-0.1092811678751202</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.707962893435747</v>
+        <v>2.666382137801925</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852433</v>
+        <v>3.841444817852429</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.072390789779336</v>
+        <v>-3.882669122236754</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.17292833062369</v>
+        <v>1.248816997640723</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.03339818860332011</v>
+        <v>-0.03590307078638366</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.822279984011164</v>
+        <v>2.780699228377342</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319558</v>
+        <v>3.819063300319554</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.17013133440431</v>
+        <v>-3.980409666861729</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.148459848889744</v>
+        <v>1.224348515906777</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.01750891047033992</v>
+        <v>-0.05179234891936385</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.827374153247419</v>
+        <v>2.785793397613598</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489396</v>
+        <v>3.831819032489393</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.346469094527239</v>
+        <v>-4.156747426984658</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.076460725665244</v>
+        <v>1.152349392682277</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1588288496525895</v>
+        <v>-0.2281301090422932</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.720107477998334</v>
+        <v>2.678526722364512</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397806</v>
+        <v>3.836411672397802</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.270047048095313</v>
+        <v>-4.080325380552732</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.105521162277944</v>
+        <v>1.181409829294976</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1588288496525895</v>
+        <v>-0.2281301090422932</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.718599096038262</v>
+        <v>2.67701834040444</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316261</v>
+        <v>3.833513460316257</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.225673916456744</v>
+        <v>-4.035952248914163</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.123133282368807</v>
+        <v>1.199021949385839</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1144557180140209</v>
+        <v>-0.1837569774037247</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.74508584245684</v>
+        <v>2.703505086823017</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105975</v>
+        <v>3.821562117105971</v>
       </c>
       <c r="C1977" t="n">
         <v>2.808153067403842</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.102839695569577</v>
+        <v>-3.913118028026996</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.166660764862264</v>
+        <v>1.242549431879297</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1144557180140209</v>
+        <v>-0.1837569774037247</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.73947963659543</v>
+        <v>2.697898880961608</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190333</v>
+        <v>3.833011148190329</v>
       </c>
       <c r="C1978" t="n">
         <v>2.814534824431647</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.055183965008521</v>
+        <v>-3.86546229746594</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.192104814114491</v>
+        <v>1.267993481131523</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.06679998745296523</v>
+        <v>-0.136101246842669</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.774454831959868</v>
+        <v>2.732874076326045</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569626</v>
+        <v>3.822678210569622</v>
       </c>
       <c r="C1979" t="n">
         <v>2.819427197806371</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.954665806509766</v>
+        <v>-3.764944138967185</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.237204450888718</v>
+        <v>1.31309311790575</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.03371817104578934</v>
+        <v>-0.03558308834391444</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.839658100433845</v>
+        <v>2.798077344800023</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557301</v>
+        <v>3.828808877557298</v>
       </c>
       <c r="C1980" t="n">
         <v>2.806181870282244</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.015332396912155</v>
+        <v>-3.658505874588895</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.199692487203634</v>
+        <v>1.342423096132939</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.04798014567274433</v>
+        <v>0.01276751570134105</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.777393782878598</v>
+        <v>2.813842379703049</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932776</v>
+        <v>3.816837033932774</v>
       </c>
       <c r="C1981" t="n">
         <v>2.810279572892872</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.970493995303757</v>
+        <v>-3.613667472980497</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.221725550457622</v>
+        <v>1.364456159386926</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.04343671272787486</v>
+        <v>0.01731094864621052</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.784217545256148</v>
+        <v>2.820666142080599</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491706</v>
+        <v>3.817932354917058</v>
       </c>
       <c r="C1982" t="n">
         <v>2.81444051252395</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.071252631060756</v>
+        <v>-3.714426108737495</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.185583035785901</v>
+        <v>1.328313644715205</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1322622814548803</v>
+        <v>-0.0715146200807949</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.735083143651022</v>
+        <v>2.771531740475473</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405969</v>
+        <v>3.826684745405967</v>
       </c>
       <c r="C1983" t="n">
         <v>2.820320115051787</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.027049793974856</v>
+        <v>-3.670223271651595</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.209143773148098</v>
+        <v>1.351874382077402</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.08805944436897983</v>
+        <v>-0.02731178299489445</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.7674844484304</v>
+        <v>2.803933045254851</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265654</v>
+        <v>3.838199629265652</v>
       </c>
       <c r="C1984" t="n">
         <v>2.818730115521035</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.064028821638299</v>
+        <v>-3.707202299315038</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.192762162551968</v>
+        <v>1.335492771481273</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.0510855425776493</v>
+        <v>0.009662118796436081</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.788078789974445</v>
+        <v>2.824527386798897</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284888</v>
+        <v>3.863895080284887</v>
       </c>
       <c r="C1985" t="n">
         <v>2.869977880704075</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.08408690050314</v>
+        <v>-3.727260378179878</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.235986696189071</v>
+        <v>1.378717305118376</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.0510855425776493</v>
+        <v>0.009662118796436081</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.839326555157485</v>
+        <v>2.875775151981936</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321031</v>
+        <v>3.865338681321029</v>
       </c>
       <c r="C1986" t="n">
         <v>2.868418585298328</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.044156227325249</v>
+        <v>-3.687329705001988</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.250399670054481</v>
+        <v>1.393130278983785</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.01115486939975896</v>
+        <v>0.04959279197432642</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.861725663658472</v>
+        <v>2.898174260482924</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475148</v>
+        <v>3.864489842475146</v>
       </c>
       <c r="C1987" t="n">
         <v>2.863366813536598</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.993124134602721</v>
+        <v>-3.636297612279459</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.265760735381762</v>
+        <v>1.408491344311067</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.039877223322769</v>
+        <v>0.1006248846968544</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.887293147530259</v>
+        <v>2.92374174435471</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404864</v>
+        <v>3.842547360404862</v>
       </c>
       <c r="C1988" t="n">
         <v>2.880554217629303</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.927899953475515</v>
+        <v>-3.571073431152254</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.309037811925349</v>
+        <v>1.451768420854654</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1051014044499746</v>
+        <v>0.16584906582406</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.943615060299288</v>
+        <v>2.980063657123739</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882568</v>
+        <v>3.840061186882566</v>
       </c>
       <c r="C1989" t="n">
         <v>2.876515189928583</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.890472933404382</v>
+        <v>-3.53364641108112</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.319969592253083</v>
+        <v>1.462700201182388</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1103529424791563</v>
+        <v>0.1711006038532417</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.942726955416077</v>
+        <v>2.979175552240528</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992672</v>
+        <v>3.84516980899267</v>
       </c>
       <c r="C1990" t="n">
         <v>2.877771982259823</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.91058458943909</v>
+        <v>-3.553758067115828</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.31318172217044</v>
+        <v>1.455912331099745</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1213802874765755</v>
+        <v>0.1821279488506609</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.950600154745769</v>
+        <v>2.98704875157022</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636298</v>
+        <v>3.828661445636296</v>
       </c>
       <c r="C1991" t="n">
         <v>3.038329753281034</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.856839775011885</v>
+        <v>-3.500013252688623</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.495237418962533</v>
+        <v>1.637968027891837</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.1314435969170374</v>
+        <v>0.1921912582911228</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.117195911431257</v>
+        <v>3.153644508255708</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957636</v>
+        <v>3.813222820957634</v>
       </c>
       <c r="C1992" t="n">
         <v>3.158442662498851</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.833048206405743</v>
+        <v>-3.476221684082481</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.624866955622807</v>
+        <v>1.767597564552112</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.1552351655231797</v>
+        <v>0.2159828268972651</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.251583761812759</v>
+        <v>3.28803235863721</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998762</v>
+        <v>3.81423072799876</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15015063851271</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.806964122141935</v>
+        <v>-3.450137599818673</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.627008565342189</v>
+        <v>1.769739174271494</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.1552351655231797</v>
+        <v>0.2159828268972651</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.243291737826618</v>
+        <v>3.279740334651069</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896936</v>
+        <v>3.803397818896935</v>
       </c>
       <c r="C1994" t="n">
         <v>3.14834383409649</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.728832941292988</v>
+        <v>-3.372006418969726</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.656454233265547</v>
+        <v>1.799184842194852</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2294119764068643</v>
+        <v>0.2901596377809497</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.285991019940608</v>
+        <v>3.32243961676506</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.165898239823281</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.719940479899705</v>
+        <v>-3.363113957576443</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.677565623549652</v>
+        <v>1.820296232478956</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2294119764068643</v>
+        <v>0.2901596377809497</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.3035454256674</v>
+        <v>3.339994022491851</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945374</v>
+        <v>3.794424941945373</v>
       </c>
       <c r="C1996" t="n">
         <v>3.157753287227865</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.888416596869583</v>
+        <v>-3.531590074546321</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.602030224166285</v>
+        <v>1.744760833095589</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.2014641406902835</v>
+        <v>0.2622118020643689</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.278631771642035</v>
+        <v>3.315080368466487</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.139022984415727</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.190617068008</v>
+        <v>-2.833790545684738</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.86241973289878</v>
+        <v>2.005150341828084</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1311160813198728</v>
+        <v>0.1918637426939582</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.217692633207651</v>
+        <v>3.254141230032102</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.129687006912631</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.167895964324847</v>
+        <v>-2.811069442001585</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.862172196868945</v>
+        <v>2.00490280579825</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1311160813198728</v>
+        <v>0.1918637426939582</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.208356655704555</v>
+        <v>3.244805252529007</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.2885931327638</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.166170921034803</v>
+        <v>-2.809344398711541</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.021768340036132</v>
+        <v>2.164498948965437</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.1328411246099165</v>
+        <v>0.1935887859840019</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.368297807529751</v>
+        <v>3.404746404354202</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.325670955257447</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.320951927813058</v>
+        <v>-2.964125405489797</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.996933759818476</v>
+        <v>2.139664368747781</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.09947345055544043</v>
+        <v>0.1602211119295258</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.385355025590711</v>
+        <v>3.421803622415163</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.322346311246992</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.269516594428399</v>
+        <v>-2.912690072105137</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.014183249161885</v>
+        <v>2.15691385809119</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.1509087839401001</v>
+        <v>0.2116564453141855</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.412891581611052</v>
+        <v>3.449340178435504</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.332352464891734</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.242565370101911</v>
+        <v>-2.885738847778649</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.034969892537222</v>
+        <v>2.177700501466527</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.1657891299678192</v>
+        <v>0.2265367913419046</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.431825942872425</v>
+        <v>3.468274539696877</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.516455597036694</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.378518378158227</v>
+        <v>-3.021691855834965</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.164691821459655</v>
+        <v>2.30742243038896</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.1657891299678192</v>
+        <v>0.2265367913419046</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.615929075017385</v>
+        <v>3.652377671841836</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.508572291939687</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.400926495963099</v>
+        <v>-3.044099973639837</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.1478452692407</v>
+        <v>2.290575878170005</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.1657891299678192</v>
+        <v>0.2265367913419046</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.608045769920378</v>
+        <v>3.64449436674483</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.510626291489324</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.548932263442499</v>
+        <v>-3.192105741119237</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.090696961798577</v>
+        <v>2.233427570727882</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.07906212110427779</v>
+        <v>0.1398097824783632</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.558063564151891</v>
+        <v>3.594512160976342</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.566880009211171</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.558373189331029</v>
+        <v>-3.201546667007767</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.143174309165012</v>
+        <v>2.285904918094317</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.2014892386476692</v>
+        <v>0.2622369000217546</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.687773552399773</v>
+        <v>3.724222149224224</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.569771103756472</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.557086425791472</v>
+        <v>-3.20025990346821</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.146580109126136</v>
+        <v>2.28931071805544</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.2027760021872258</v>
+        <v>0.2635236635613112</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.691436705068808</v>
+        <v>3.727885301893259</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.567882916650247</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.558643479780764</v>
+        <v>-3.201816957457502</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.144069100424194</v>
+        <v>2.286799709353499</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.2027760021872258</v>
+        <v>0.2635236635613112</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.689548517962583</v>
+        <v>3.725997114787034</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.56270314625311</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.565915365304228</v>
+        <v>-3.209088842980966</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.135980575817671</v>
+        <v>2.278711184746976</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.1955041166637611</v>
+        <v>0.2562517780378464</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.680005616251366</v>
+        <v>3.716454213075818</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.561137156463262</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.564074346245977</v>
+        <v>-3.207247823922715</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.135150993651124</v>
+        <v>2.277881602580428</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.1967723433352295</v>
+        <v>0.2575200047093149</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.6792005624644</v>
+        <v>3.715649159288851</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.574210563329181</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.570983051745658</v>
+        <v>-3.214156529422396</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.14546091831717</v>
+        <v>2.288191527246475</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.1967723433352295</v>
+        <v>0.2575200047093149</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.692273969330318</v>
+        <v>3.72872256615477</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.574210563329181</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.572544694560517</v>
+        <v>-3.215718172237255</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.144836261191227</v>
+        <v>2.287566870120531</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.1967723433352295</v>
+        <v>0.2575200047093149</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.692273969330318</v>
+        <v>3.72872256615477</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.572734604456183</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.60044548166999</v>
+        <v>-3.243618959346728</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.132199987474439</v>
+        <v>2.274930596403744</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.1621754191922947</v>
+        <v>0.22292308056638</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.670039855971559</v>
+        <v>3.706488452796011</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,45 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.779485757366279</v>
+        <v>3.684909939172536</v>
       </c>
       <c r="C2014" t="n">
         <v>3.569499048433381</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.603478479182664</v>
+        <v>-3.455988691801198</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.127751232446569</v>
+        <v>2.186747147399155</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.1591424216796208</v>
+        <v>0.01055334811191005</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.664984501441154</v>
+        <v>3.575831057300527</v>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" s="2" t="n">
+        <v>45477</v>
+      </c>
+      <c r="B2015" t="n">
+        <v>3.834879652549409</v>
+      </c>
+      <c r="C2015" t="n">
+        <v>3.817057412010405</v>
+      </c>
+      <c r="D2015" t="n">
+        <v>-3.455988691801198</v>
+      </c>
+      <c r="E2015" t="n">
+        <v>2.186747147399155</v>
+      </c>
+      <c r="F2015" t="n">
+        <v>0.01055334811191005</v>
+      </c>
+      <c r="G2015" t="n">
+        <v>3.810121208996772</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240704.xlsx
+++ b/tame_output/ON/bt/strategyON_20240704.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>48.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,27 +844,27 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.3%</t>
+          <t>-71.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.9%</t>
+          <t>122.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>94.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-655.5%</t>
+          <t>-660.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.4%</t>
+          <t>-48.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.7%</t>
+          <t>-67.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.8%</t>
+          <t>431.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-507.2%</t>
+          <t>-501.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,17 +1135,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-262.6%</t>
+          <t>-264.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.1%</t>
+          <t>-36.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.5%</t>
+          <t>-155.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-13.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-228.9%</t>
+          <t>-181.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-222.9%</t>
+          <t>-209.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-65.0%</t>
+          <t>-78.9%</t>
         </is>
       </c>
     </row>
@@ -43842,16 +43842,16 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386093</v>
+        <v>3.376932391386092</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.2097835746314828</v>
+        <v>0.1613274819982661</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.24106826214933</v>
+        <v>3.221685825096043</v>
       </c>
       <c r="F1839" t="n">
         <v>1.568940374610322</v>
@@ -43871,10 +43871,10 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.2148211653590694</v>
+        <v>0.1663650727258526</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.241660738625703</v>
+        <v>3.222278301572416</v>
       </c>
       <c r="F1840" t="n">
         <v>1.62458483087664</v>
@@ -43894,10 +43894,10 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.04237286934898737</v>
+        <v>-0.09082896198220414</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.117529506366217</v>
+        <v>3.09814706931293</v>
       </c>
       <c r="F1841" t="n">
         <v>1.367390796168583</v>
@@ -43917,10 +43917,10 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.1081402593983994</v>
+        <v>-0.1565963520316162</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.092240159476923</v>
+        <v>3.072857722423636</v>
       </c>
       <c r="F1842" t="n">
         <v>1.367390796168583</v>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.313384936455644</v>
+        <v>-0.3618410290888608</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.00077032064178</v>
+        <v>2.981387883588494</v>
       </c>
       <c r="F1843" t="n">
         <v>1.367390796168583</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.3951568368833957</v>
+        <v>-0.4436129295166125</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.958144286425918</v>
+        <v>2.938761849372631</v>
       </c>
       <c r="F1844" t="n">
         <v>1.394426369574719</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.4623659447552734</v>
+        <v>-0.5108220373884902</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.936025960110869</v>
+        <v>2.916643523057583</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.6699317291468853</v>
+        <v>-0.7183878217801021</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.850824442473465</v>
+        <v>2.831442005420178</v>
       </c>
       <c r="F1846" t="n">
         <v>1.186860585183108</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.087685752693722</v>
+        <v>-1.136141845326939</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.681649724559793</v>
+        <v>2.662267287506507</v>
       </c>
       <c r="F1847" t="n">
         <v>0.7691065616362706</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.377817419299154</v>
+        <v>-1.426273511932371</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.565463274516542</v>
+        <v>2.546080837463256</v>
       </c>
       <c r="F1848" t="n">
         <v>0.7931883563764505</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.585821477652231</v>
+        <v>-1.634277570285448</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.487153795729236</v>
+        <v>2.46777135867595</v>
       </c>
       <c r="F1849" t="n">
         <v>0.7931883563764505</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.797233898540206</v>
+        <v>-1.845689991173423</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.397670283712035</v>
+        <v>2.378287846658748</v>
       </c>
       <c r="F1850" t="n">
         <v>0.5817759354884754</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.163302625684858</v>
+        <v>-2.211758718318076</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.244327092160623</v>
+        <v>2.224944655107336</v>
       </c>
       <c r="F1851" t="n">
         <v>0.2157072083438227</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.371793407136543</v>
+        <v>-2.42024949976976</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.181269069318717</v>
+        <v>2.161886632265431</v>
       </c>
       <c r="F1852" t="n">
         <v>0.007216426892138306</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.618994591901764</v>
+        <v>-2.667450684534982</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.090487345821197</v>
+        <v>2.07110490876791</v>
       </c>
       <c r="F1853" t="n">
         <v>0.02736978039095073</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.111379619925861</v>
+        <v>-3.159835712559079</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.894639726655291</v>
+        <v>1.875257289602004</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.465015247633146</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.496560010855934</v>
+        <v>-3.545016103489151</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.739110109096125</v>
+        <v>1.719727672042838</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.465015247633146</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.746430690870515</v>
+        <v>-3.794886783503733</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.640930960544909</v>
+        <v>1.621548523491622</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.4287525278026827</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.952942467757536</v>
+        <v>-4.001398560390754</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.554432308446358</v>
+        <v>1.535049871393071</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6352643046897042</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.272286542838039</v>
+        <v>-4.320742635471256</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.428467605114417</v>
+        <v>1.40908516806113</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6352643046897042</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.704092335987826</v>
+        <v>-4.752548428621044</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.242078175321906</v>
+        <v>1.222695738268619</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7716818011309712</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.938786330120378</v>
+        <v>-4.987242422753596</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.136485352670976</v>
+        <v>1.117102915617689</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.765345533901716</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.274448977350831</v>
+        <v>-5.322905069984048</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.00080088543476</v>
+        <v>0.981418448381473</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8332765193906209</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.638075222251144</v>
+        <v>-5.686531314884362</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8618379477088762</v>
+        <v>0.8424555106555891</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9314981562577467</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.003202604889891</v>
+        <v>-6.051658697523108</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7150415096592089</v>
+        <v>0.6956590726059217</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.227808940556759</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.41179138207057</v>
+        <v>-6.460247474703786</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5503675428016965</v>
+        <v>0.5309851057484098</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.636397717737438</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.688367482386402</v>
+        <v>-6.736823575019619</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.434922535146824</v>
+        <v>0.4155400980935373</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.636397717737438</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.1047593566734</v>
+        <v>-7.153215449306616</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2663598360409023</v>
+        <v>0.2469773989876156</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.636397717737438</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.349030757400469</v>
+        <v>-7.397486850033686</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1789099664187535</v>
+        <v>0.1595275293654668</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.636397717737438</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.55428177663723</v>
+        <v>-7.602737869270446</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.09290912386974481</v>
+        <v>0.07352668681645813</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.636397717737438</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.717861654821613</v>
+        <v>-7.76631774745483</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.02588209265099239</v>
+        <v>0.006499655597705711</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.636397717737438</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.014522996631811</v>
+        <v>-8.062979089265028</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.08900346814387872</v>
+        <v>-0.1083859051971654</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.705140853471316</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.201242704941114</v>
+        <v>-8.249698797574331</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.1677176560020031</v>
+        <v>-0.1871000930552897</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.705140853471316</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.584244093683745</v>
+        <v>-8.632700186316962</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.3210203128206395</v>
+        <v>-0.3404027498739262</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.705140853471316</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.76611388466878</v>
+        <v>-8.814569977301996</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.3911967132432235</v>
+        <v>-0.4105791502965102</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.887010644456351</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.125644207172781</v>
+        <v>-9.174100299805998</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.5296585389467738</v>
+        <v>-0.5490409760000605</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.887010644456351</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.175993270627004</v>
+        <v>-9.22444936326022</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.5418821443712853</v>
+        <v>-0.5612645814245716</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.937359707910573</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.2736125480484</v>
+        <v>-9.322068640681616</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.5778881047180748</v>
+        <v>-0.5972705417713615</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.03497898533197</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.421138636054042</v>
+        <v>-9.469594728687259</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6340049835987598</v>
+        <v>-0.6533874206520465</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.182505073337614</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.625396811383906</v>
+        <v>-9.673852904017123</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7101950566120627</v>
+        <v>-0.7295774936653494</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.310144017951603</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.659049649892379</v>
+        <v>-9.707505742525596</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.719173637531016</v>
+        <v>-0.7385560745843027</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.41055738586864</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.585579818224931</v>
+        <v>-9.634035910858147</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.6744140033706154</v>
+        <v>-0.6937964404239021</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.337087554201192</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.760704235611474</v>
+        <v>-9.80916032824469</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.7299085495777158</v>
+        <v>-0.7492909866310025</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.512211971587735</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.995156329625964</v>
+        <v>-10.04361242225918</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.8309085520851078</v>
+        <v>-0.8502909891383941</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.512211971587735</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.09953106065241</v>
+        <v>-10.14798715328563</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.8793306352696626</v>
+        <v>-0.8987130723229488</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.616586702614181</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.15231721625274</v>
+        <v>-10.20077330888595</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.8993293076712368</v>
+        <v>-0.9187117447245239</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.712262189196578</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.27835400962103</v>
+        <v>-10.32681010225424</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.9470502963894378</v>
+        <v>-0.966432733442725</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.687010566386836</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.22633849565221</v>
+        <v>-10.27479458828543</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.9222537551155119</v>
+        <v>-0.9416361921687981</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.687010566386836</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.36801033737633</v>
+        <v>-10.41646643000955</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.9803977187039017</v>
+        <v>-0.9997801557571879</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.687010566386836</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.3184194929515</v>
+        <v>-10.36687558558472</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.9455079707690959</v>
+        <v>-0.9648904078223821</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.637419721962002</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.30561209994672</v>
+        <v>-10.35406819257994</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.953436147213869</v>
+        <v>-0.9728185842671553</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.686275496970903</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.07976694722731</v>
+        <v>-10.12822303986053</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.8535190130898953</v>
+        <v>-0.8729014501431824</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.64434882138374</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.955188290889721</v>
+        <v>-10.00364438352294</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.8025484059988002</v>
+        <v>-0.8219308430520864</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.64434882138374</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.00808357893401</v>
+        <v>-10.05653967156722</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.8210727470544068</v>
+        <v>-0.8404551841076939</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.639393475295293</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.935950403646126</v>
+        <v>-9.984406496279343</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.786485772700618</v>
+        <v>-0.8058682097539047</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.639393475295293</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.864584011036479</v>
+        <v>-9.913040103669696</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.7676764780506242</v>
+        <v>-0.7870589151039109</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.568027082685645</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.771124977051254</v>
+        <v>-9.819581069684471</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7401763457694419</v>
+        <v>-0.7595587828227286</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.568027082685645</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.503883176182857</v>
+        <v>-9.552339268816073</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6351141859214566</v>
+        <v>-0.6544966229747433</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.568027082685645</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.405976137506366</v>
+        <v>-9.454432230139583</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.5962516854243214</v>
+        <v>-0.6156341224776081</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.500041332825089</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.382022596530408</v>
+        <v>-9.430478689163625</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.5860017628884444</v>
+        <v>-0.6053841999417311</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.476087791849131</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.117962658207611</v>
+        <v>-9.166418750840828</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.4936381037210777</v>
+        <v>-0.5130205407743644</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.212027853526335</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.410883034702774</v>
+        <v>-8.459339127335991</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2135932879794438</v>
+        <v>-0.2329757250327305</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.212027853526335</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.370698736336584</v>
+        <v>-8.4191548289698</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.1971759447451262</v>
+        <v>-0.2165583817984129</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.171843555160144</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.20729886539722</v>
+        <v>-8.255754958030437</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1324491751486239</v>
+        <v>-0.1518316122019105</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.008443684220782</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.973817643167622</v>
+        <v>-8.022273735800837</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.03113225741893233</v>
+        <v>-0.05051469447221857</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.774962461991183</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.824151252160107</v>
+        <v>-7.872607344793322</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.02584208867111482</v>
+        <v>0.006459651617828577</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.682058970748648</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.69187577852922</v>
+        <v>-7.740331871162436</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.07411976487049632</v>
+        <v>0.05473732781721008</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.549783497117761</v>
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.536137445969478</v>
+        <v>-7.526117139945137</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1392301585820297</v>
+        <v>0.1432382809917661</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.394045164558019</v>
+        <v>-1.335568765900463</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.317614462548757</v>
+        <v>2.352700301743291</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.287137647285897</v>
+        <v>-7.277117341261556</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2517364192791209</v>
+        <v>0.2557445416888573</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.394045164558019</v>
+        <v>-1.335568765900463</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.330520803772416</v>
+        <v>2.36560664296695</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.392727637059002</v>
+        <v>-7.382707331034661</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.08152449377066029</v>
+        <v>0.08553261618039665</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.499635154331124</v>
+        <v>-1.441158755673567</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.139190880309334</v>
+        <v>2.174276719503869</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.411462539177599</v>
+        <v>-7.401442233153258</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.1225748748003079</v>
+        <v>0.1265829972100443</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.505231163991255</v>
+        <v>-1.446754765333698</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.184377616390342</v>
+        <v>2.219463455584876</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.263522497769999</v>
+        <v>-7.253502191745659</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.06187196867518008</v>
+        <v>0.06588009108491644</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.484910248082697</v>
+        <v>-1.426433849425141</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.076691243247309</v>
+        <v>2.111777082441843</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.210552975516011</v>
+        <v>-7.20053266949167</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.07434579132329722</v>
+        <v>0.07835391373303358</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.431940725828709</v>
+        <v>-1.373464327171152</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.099758970346224</v>
+        <v>2.134844809540758</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.167004568745321</v>
+        <v>-7.15698426272098</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.08480454193648024</v>
+        <v>0.0888126643462166</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.431940725828709</v>
+        <v>-1.373464327171152</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.092798358251131</v>
+        <v>2.127884197445665</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.924856175291462</v>
+        <v>-6.914835869267121</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1961262536991666</v>
+        <v>0.2001343761089029</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.431940725828709</v>
+        <v>-1.373464327171152</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.107260712632274</v>
+        <v>2.142346551826808</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.816597038168941</v>
+        <v>-6.8065767321446</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2339620290073703</v>
+        <v>0.2379701514171066</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.431940725828709</v>
+        <v>-1.373464327171152</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.101792833091469</v>
+        <v>2.136878672286003</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.69330590335181</v>
+        <v>-6.683285597327469</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2807765769447994</v>
+        <v>0.2847846993545358</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.308649591011578</v>
+        <v>-1.250173192354021</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.173265607992324</v>
+        <v>2.208351447186859</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.672156704448367</v>
+        <v>-6.662136398424026</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2969372347435022</v>
+        <v>0.3009453571532386</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.287500392108135</v>
+        <v>-1.229023993450578</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.193656105571716</v>
+        <v>2.22874194476625</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.428391262464922</v>
+        <v>-6.418370956440581</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3902241198839307</v>
+        <v>0.394232242293667</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.287500392108135</v>
+        <v>-1.229023993450578</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.189436813918766</v>
+        <v>2.2245226531133</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.326628442187627</v>
+        <v>-6.316608136163286</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4330535619148645</v>
+        <v>0.4370616843246009</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.274281323715706</v>
+        <v>-1.215804925058149</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.199492568874239</v>
+        <v>2.234578408068773</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.076778048238553</v>
+        <v>-6.066757742214212</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5257357944781966</v>
+        <v>0.529743916887933</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.274281323715706</v>
+        <v>-1.215804925058149</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.192234643857941</v>
+        <v>2.227320483052476</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.90088595577112</v>
+        <v>-5.890865649746779</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5996917549858183</v>
+        <v>0.6036998773955546</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.274281323715706</v>
+        <v>-1.215804925058149</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.19583376737859</v>
+        <v>2.230919606573124</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.729439492748656</v>
+        <v>-5.719419186724315</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6815978462493577</v>
+        <v>0.6856059686590941</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.102834860693243</v>
+        <v>-1.044358462035686</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.312029151246622</v>
+        <v>2.347114990441156</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.655149927010317</v>
+        <v>-5.645129620985976</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7103341501609903</v>
+        <v>0.7143422725707267</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.028545294954904</v>
+        <v>-0.9700688962973467</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.355623368305922</v>
+        <v>2.390709207500457</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.591514184776383</v>
+        <v>-5.581493878752042</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7404832481088812</v>
+        <v>0.7444913705186176</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9649095527209691</v>
+        <v>-0.9064331540634122</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.3984996147006</v>
+        <v>2.433585453895135</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.480087425450463</v>
+        <v>-5.470067119426122</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7662482106230448</v>
+        <v>0.7702563330327812</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9649095527209691</v>
+        <v>-0.9064331540634122</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.379693873484396</v>
+        <v>2.41477971267893</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.239656928645602</v>
+        <v>-5.229636622621261</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8641634859698666</v>
+        <v>0.8681716083796029</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7244790559161088</v>
+        <v>-0.6660026572585519</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.52569524819219</v>
+        <v>2.560781087386724</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.167414360474408</v>
+        <v>-5.157394054450067</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8969898270731647</v>
+        <v>0.900997949482901</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7244790559161088</v>
+        <v>-0.6660026572585519</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.52962456202701</v>
+        <v>2.564710401221544</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.11441603819302</v>
+        <v>-5.104395732168679</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9188677399030598</v>
+        <v>0.9228758623127962</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.66914279691417</v>
+        <v>-0.6106663982566131</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.563504901345513</v>
+        <v>2.598590740540047</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.005611152713293</v>
+        <v>-4.995590846688952</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9593877653149439</v>
+        <v>0.9633958877246802</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.66914279691417</v>
+        <v>-0.6106663982566131</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.560502972565506</v>
+        <v>2.595588811760041</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.785590354676282</v>
+        <v>-4.775570048651941</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.048975121540362</v>
+        <v>1.052983243950099</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5279229518461898</v>
+        <v>-0.4694465531886328</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.646813916616909</v>
+        <v>2.681899755811443</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.652722665613005</v>
+        <v>-4.642702359588664</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.118016379967497</v>
+        <v>1.122024502377233</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5279229518461898</v>
+        <v>-0.4694465531886328</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.662708099418732</v>
+        <v>2.697793938613266</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.532549582248506</v>
+        <v>-4.522529276224165</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.167231457753598</v>
+        <v>1.171239580163334</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4077498684816908</v>
+        <v>-0.3492734698241339</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.735957793877733</v>
+        <v>2.771043633072268</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.387877437148768</v>
+        <v>-4.377857131124427</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.235188418354933</v>
+        <v>1.239196540764669</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2630777233819534</v>
+        <v>-0.2046013247243965</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.832849183499015</v>
+        <v>2.86793502269355</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.447752264506461</v>
+        <v>-4.43773195848212</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.197275978813282</v>
+        <v>1.201284101223018</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3229525507396455</v>
+        <v>-0.2644761520820886</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.782961778485826</v>
+        <v>2.818047617680361</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.360952766727452</v>
+        <v>-4.350932460703111</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.254396271247451</v>
+        <v>1.258404393657188</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3229525507396455</v>
+        <v>-0.2644761520820886</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.805362271808392</v>
+        <v>2.840448111002927</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.363422473189258</v>
+        <v>-4.353402167164917</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.253480790036141</v>
+        <v>1.257488912445877</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3254222572014517</v>
+        <v>-0.2669458585438947</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.803952849304721</v>
+        <v>2.839038688499255</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.431792659513269</v>
+        <v>-4.421772353488928</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.237139637981239</v>
+        <v>1.241147760390975</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.2576701595076798</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.820525191201152</v>
+        <v>2.855611030395686</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.445580712360315</v>
+        <v>-4.435560406335974</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.222061125474311</v>
+        <v>1.226069247884048</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.2576701595076798</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.810961899833043</v>
+        <v>2.846047739027577</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.476573871689021</v>
+        <v>-4.46655356566468</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.034373426783216</v>
+        <v>1.038381549192952</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.2576701595076798</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.63567146487343</v>
+        <v>2.670757304067964</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.301099611896552</v>
+        <v>-4.291079305872211</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.109130362691992</v>
+        <v>1.113138485101728</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.2576701595076798</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.640238696865218</v>
+        <v>2.675324536059752</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.412035864537801</v>
+        <v>-4.40201555851346</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.040497890396699</v>
+        <v>1.044506012806435</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.2576701595076798</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.615980725626425</v>
+        <v>2.651066564820959</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.378372319065519</v>
+        <v>-4.368352013041178</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.057094693805517</v>
+        <v>1.061102816215254</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2824830126929549</v>
+        <v>-0.224006614035398</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.6393102381297</v>
+        <v>2.674396077324233</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.318519699861795</v>
+        <v>-4.308499393837455</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.091208127919139</v>
+        <v>1.095216250328875</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2824830126929549</v>
+        <v>-0.224006614035398</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.649482624561832</v>
+        <v>2.684568463756366</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.232276236835418</v>
+        <v>-4.222255930811077</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.12065178370355</v>
+        <v>1.124659906113287</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2824830126929549</v>
+        <v>-0.224006614035398</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.644428895135692</v>
+        <v>2.679514734330226</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.277583056234397</v>
+        <v>-4.267562750210057</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.094304831388484</v>
+        <v>1.09831295379822</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3232931757021857</v>
+        <v>-0.2648167770446287</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.611718572774679</v>
+        <v>2.646804411969213</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.306616160936699</v>
+        <v>-4.296595854912358</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.083243462540665</v>
+        <v>1.087251584950401</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3232931757021857</v>
+        <v>-0.2648167770446287</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.612270445807781</v>
+        <v>2.647356285002315</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.213805679485839</v>
+        <v>-4.203785373461498</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.049640347012375</v>
+        <v>1.053648469422111</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2304826942513263</v>
+        <v>-0.1720062955937694</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.597229426569662</v>
+        <v>2.632315265764196</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.258195148815267</v>
+        <v>-4.248174842790926</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.033758035205204</v>
+        <v>1.037766157614941</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.274872163580754</v>
+        <v>-0.2163957649231971</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.572469220896606</v>
+        <v>2.607555060091141</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.145523930579016</v>
+        <v>-4.135503624554675</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.073902231011427</v>
+        <v>1.077910353421164</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1622009453445038</v>
+        <v>-0.1037245466869469</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.635147660350079</v>
+        <v>2.670233499544613</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.033146929396343</v>
+        <v>-4.023126623372002</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.124344327315164</v>
+        <v>1.1283524497249</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1622009453445038</v>
+        <v>-0.1037245466869469</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.640638956180747</v>
+        <v>2.675724795375281</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.060927327297696</v>
+        <v>-4.050907021273355</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.124729369923162</v>
+        <v>1.128737492332898</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1899813432458569</v>
+        <v>-0.1315049445882999</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.635467919208474</v>
+        <v>2.670553758403008</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.143928608322975</v>
+        <v>-4.133908302298634</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9298845775137037</v>
+        <v>0.93389269992344</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2085522277730306</v>
+        <v>-0.1500758291154737</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.462681108492823</v>
+        <v>2.497766947687357</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.252542686766306</v>
+        <v>-4.242522380741965</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.006588606855577</v>
+        <v>1.010596729265313</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2085522277730306</v>
+        <v>-0.1500758291154737</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.582830769212028</v>
+        <v>2.617916608406563</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.217133648518163</v>
+        <v>-4.207113342493822</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.035265248257157</v>
+        <v>1.039273370666893</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2085522277730306</v>
+        <v>-0.1500758291154737</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.597343795314351</v>
+        <v>2.632429634508886</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.178749985960012</v>
+        <v>-4.168729679935671</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.048038154622786</v>
+        <v>1.052046277032523</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1701685652148794</v>
+        <v>-0.1116921665573225</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.617793434191611</v>
+        <v>2.652879273386145</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.001633655924846</v>
+        <v>-3.991613349900505</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.115613715482154</v>
+        <v>1.119621837891891</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1701685652148794</v>
+        <v>-0.1116921665573225</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.614522463036913</v>
+        <v>2.649608302231447</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.046725900758392</v>
+        <v>-4.036705594734051</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.098260209310649</v>
+        <v>1.102268331720386</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2320646083842692</v>
+        <v>-0.1735882097267123</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.578068228897192</v>
+        <v>2.613154068091726</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.867350479519624</v>
+        <v>-3.857330173495283</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.163797353112571</v>
+        <v>1.167805475522307</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.07528785021355056</v>
+        <v>-0.01681145155599362</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.665921259106037</v>
+        <v>2.701007098300572</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.91236469304023</v>
+        <v>-3.902344387015889</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.126599123035918</v>
+        <v>1.130607245445654</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1056367455281552</v>
+        <v>-0.04716034687059822</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.628519377248864</v>
+        <v>2.663605216443399</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.179369203312666</v>
+        <v>-4.169348897288325</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.02548888126589</v>
+        <v>1.029497003675626</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2999997835711037</v>
+        <v>-0.2415233849135468</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.517593116762041</v>
+        <v>2.552678955956575</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.280566984749838</v>
+        <v>-4.270546678725498</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9842136905875218</v>
+        <v>0.9882218129972582</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3684085971164229</v>
+        <v>-0.309932198458866</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.475751750531351</v>
+        <v>2.510837589725885</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.274056018135526</v>
+        <v>-4.264035712111185</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9844180387875636</v>
+        <v>0.9884261611973</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3684085971164229</v>
+        <v>-0.309932198458866</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.473351712085668</v>
+        <v>2.508437551280202</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.255017890428229</v>
+        <v>-4.244997584403888</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9885580090787274</v>
+        <v>0.9925661314884637</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4265922084476175</v>
+        <v>-0.3681158097900605</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.434966264495196</v>
+        <v>2.47005210368973</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.286144521578847</v>
+        <v>-4.276124215554506</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.153689225557161</v>
+        <v>1.157697347966897</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4265922084476175</v>
+        <v>-0.3681158097900605</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.612548133433877</v>
+        <v>2.647633972628411</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.300011282912765</v>
+        <v>-4.289990976888424</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.148975850009727</v>
+        <v>1.152983972419463</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4644501251814404</v>
+        <v>-0.4059737265238835</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.590666712379716</v>
+        <v>2.625752551574251</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.255207111372835</v>
+        <v>-4.245186805348494</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.172906049022625</v>
+        <v>1.176914171432361</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4644501251814404</v>
+        <v>-0.4059737265238835</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.596675242776642</v>
+        <v>2.631761081971177</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.107464141137832</v>
+        <v>-4.097443835113491</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.311155884908648</v>
+        <v>1.315164007318384</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2966427679465573</v>
+        <v>-0.2381663692890003</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.776512304909594</v>
+        <v>2.811598144104128</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.209478823669054</v>
+        <v>-4.199458517644713</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.27314363342764</v>
+        <v>1.277151755837377</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2966427679465573</v>
+        <v>-0.2381663692890003</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.779305926441075</v>
+        <v>2.814391765635609</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.203326117616269</v>
+        <v>-4.193305811591928</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.276267064240412</v>
+        <v>1.280275186650149</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.290490061893773</v>
+        <v>-0.232013663236216</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.783659898464404</v>
+        <v>2.818745737658938</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.220135415766771</v>
+        <v>-4.21011510974243</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.268623821720322</v>
+        <v>1.272631944130058</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3072993600442746</v>
+        <v>-0.2488229613867177</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.772654796314213</v>
+        <v>2.807740635508747</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.157837416990649</v>
+        <v>-4.147817110966308</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.359878575027592</v>
+        <v>1.363886697437328</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3072993600442746</v>
+        <v>-0.2488229613867177</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.838990350111034</v>
+        <v>2.874076189305568</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.956047219325491</v>
+        <v>-3.94602691330115</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.149175526483053</v>
+        <v>1.153183648892789</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1092811678751202</v>
+        <v>-0.05080476921756327</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.666382137801925</v>
+        <v>2.701467976996459</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.882669122236754</v>
+        <v>-3.872648816212414</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.248816997640723</v>
+        <v>1.252825120050459</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.03590307078638366</v>
+        <v>0.02257332787117328</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.780699228377342</v>
+        <v>2.815785067571876</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.980409666861729</v>
+        <v>-3.970389360837388</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.224348515906777</v>
+        <v>1.228356638316513</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.05179234891936385</v>
+        <v>0.006684049738193087</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.785793397613598</v>
+        <v>2.820879236808131</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.156747426984658</v>
+        <v>-4.146727120960318</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.152349392682277</v>
+        <v>1.156357515092013</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2281301090422932</v>
+        <v>-0.1696537103847363</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.678526722364512</v>
+        <v>2.713612561559045</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.080325380552732</v>
+        <v>-4.070305074528391</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.181409829294976</v>
+        <v>1.185417951704712</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2281301090422932</v>
+        <v>-0.1696537103847363</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.67701834040444</v>
+        <v>2.712104179598974</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.035952248914163</v>
+        <v>-4.025931942889822</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.199021949385839</v>
+        <v>1.203030071795576</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1837569774037247</v>
+        <v>-0.1252805787461677</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.703505086823017</v>
+        <v>2.738590926017551</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.808153067403842</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.913118028026996</v>
+        <v>-3.903097722002655</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.242549431879297</v>
+        <v>1.246557554289033</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1837569774037247</v>
+        <v>-0.1252805787461677</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.697898880961608</v>
+        <v>2.732984720156142</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.814534824431647</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.86546229746594</v>
+        <v>-3.855441991441599</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.267993481131523</v>
+        <v>1.27200160354126</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.136101246842669</v>
+        <v>-0.07762484818511206</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.732874076326045</v>
+        <v>2.76795991552058</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.819427197806371</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.764944138967185</v>
+        <v>-3.754923832942844</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.31309311790575</v>
+        <v>1.317101240315486</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.03558308834391444</v>
+        <v>0.0228933103136425</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.798077344800023</v>
+        <v>2.833163183994557</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.806181870282244</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.658505874588895</v>
+        <v>-3.815590423345233</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.342423096132939</v>
+        <v>1.279589276630403</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.01276751570134105</v>
+        <v>-0.05880500640489117</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.813842379703049</v>
+        <v>2.770898866439309</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.810279572892872</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.613667472980497</v>
+        <v>-3.770752021736835</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.364456159386926</v>
+        <v>1.301622339884391</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.01731094864621052</v>
+        <v>-0.05426157346002169</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.820666142080599</v>
+        <v>2.777722628816859</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.81444051252395</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.714426108737495</v>
+        <v>-3.871510657493834</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.328313644715205</v>
+        <v>1.265479825212669</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.0715146200807949</v>
+        <v>-0.1430871421870271</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.771531740475473</v>
+        <v>2.728588227211734</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.820320115051787</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.670223271651595</v>
+        <v>-3.827307820407933</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.351874382077402</v>
+        <v>1.289040562574867</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.02731178299489445</v>
+        <v>-0.09888430510112667</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.803933045254851</v>
+        <v>2.760989531991112</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.818730115521035</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.707202299315038</v>
+        <v>-3.864286848071377</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.335492771481273</v>
+        <v>1.272658951978737</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.009662118796436081</v>
+        <v>-0.06191040330979614</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.824527386798897</v>
+        <v>2.781583873535157</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.869977880704075</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.727260378179878</v>
+        <v>-3.884344926936217</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.378717305118376</v>
+        <v>1.315883485615841</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.009662118796436081</v>
+        <v>-0.06191040330979614</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.875775151981936</v>
+        <v>2.832831638718197</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.868418585298328</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.687329705001988</v>
+        <v>-3.844414253758326</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.393130278983785</v>
+        <v>1.33029645948125</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.04959279197432642</v>
+        <v>-0.02197973013190579</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.898174260482924</v>
+        <v>2.855230747219184</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.863366813536598</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.636297612279459</v>
+        <v>-3.793382161035798</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.408491344311067</v>
+        <v>1.345657524808531</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.1006248846968544</v>
+        <v>0.02905236259062216</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.92374174435471</v>
+        <v>2.880798231090971</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.880554217629303</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.571073431152254</v>
+        <v>-3.728157979908593</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.451768420854654</v>
+        <v>1.388934601352118</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.16584906582406</v>
+        <v>0.09427654371782779</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.980063657123739</v>
+        <v>2.93712014386</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.876515189928583</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.53364641108112</v>
+        <v>-3.690730959837459</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.462700201182388</v>
+        <v>1.399866381679852</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1711006038532417</v>
+        <v>0.09952808174700944</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.979175552240528</v>
+        <v>2.936232038976789</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.877771982259823</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.553758067115828</v>
+        <v>-3.710842615872167</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.455912331099745</v>
+        <v>1.393078511597209</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1821279488506609</v>
+        <v>0.1105554267444286</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.98704875157022</v>
+        <v>2.944105238306481</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.038329753281034</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.500013252688623</v>
+        <v>-3.657097801444963</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.637968027891837</v>
+        <v>1.575134208389302</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.1921912582911228</v>
+        <v>0.1206187361848906</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.153644508255708</v>
+        <v>3.110700994991969</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.158442662498851</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.476221684082481</v>
+        <v>-3.63330623283882</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.767597564552112</v>
+        <v>1.704763745049576</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.2159828268972651</v>
+        <v>0.1444103047910329</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.28803235863721</v>
+        <v>3.245088845373471</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15015063851271</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.450137599818673</v>
+        <v>-3.607222148575012</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.769739174271494</v>
+        <v>1.706905354768958</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.2159828268972651</v>
+        <v>0.1444103047910329</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.279740334651069</v>
+        <v>3.23679682138733</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.14834383409649</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.372006418969726</v>
+        <v>-3.529090967726066</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.799184842194852</v>
+        <v>1.736351022692316</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2901596377809497</v>
+        <v>0.2185871156747174</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.32243961676506</v>
+        <v>3.27949610350132</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.165898239823281</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.363113957576443</v>
+        <v>-3.520198506332783</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.820296232478956</v>
+        <v>1.757462412976421</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2901596377809497</v>
+        <v>0.2185871156747174</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.339994022491851</v>
+        <v>3.297050509228112</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.157753287227865</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.531590074546321</v>
+        <v>-3.68867462330266</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.744760833095589</v>
+        <v>1.681927013593054</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.2622118020643689</v>
+        <v>0.1906392799581367</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.315080368466487</v>
+        <v>3.272136855202747</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.139022984415727</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.833790545684738</v>
+        <v>-2.990875094441077</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.005150341828084</v>
+        <v>1.942316522325549</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1918637426939582</v>
+        <v>0.120291220587726</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.254141230032102</v>
+        <v>3.211197716768363</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.129687006912631</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.811069442001585</v>
+        <v>-2.968153990757925</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.00490280579825</v>
+        <v>1.942068986295714</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1918637426939582</v>
+        <v>0.120291220587726</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.244805252529007</v>
+        <v>3.201861739265267</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.2885931327638</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.809344398711541</v>
+        <v>-2.966428947467881</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.164498948965437</v>
+        <v>2.101665129462901</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.1935887859840019</v>
+        <v>0.1220162638777697</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.404746404354202</v>
+        <v>3.361802891090463</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.325670955257447</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.964125405489797</v>
+        <v>-3.121209954246136</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.139664368747781</v>
+        <v>2.076830549245245</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.1602211119295258</v>
+        <v>0.0886485898232936</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.421803622415163</v>
+        <v>3.378860109151423</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.322346311246992</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.912690072105137</v>
+        <v>-3.069774620861476</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.15691385809119</v>
+        <v>2.094080038588654</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.2116564453141855</v>
+        <v>0.1400839232079533</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.449340178435504</v>
+        <v>3.406396665171764</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.332352464891734</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.885738847778649</v>
+        <v>-3.042823396534988</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.177700501466527</v>
+        <v>2.114866681963991</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.2265367913419046</v>
+        <v>0.1549642692356724</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.468274539696877</v>
+        <v>3.425331026433137</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.516455597036694</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.021691855834965</v>
+        <v>-3.178776404591305</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.30742243038896</v>
+        <v>2.244588610886424</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.2265367913419046</v>
+        <v>0.1549642692356724</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.652377671841836</v>
+        <v>3.609434158578097</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.508572291939687</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.044099973639837</v>
+        <v>-3.201184522396177</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.290575878170005</v>
+        <v>2.227742058667469</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.2265367913419046</v>
+        <v>0.1549642692356724</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.64449436674483</v>
+        <v>3.60155085348109</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.510626291489324</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.192105741119237</v>
+        <v>-3.349190289875576</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.233427570727882</v>
+        <v>2.170593751225346</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.1398097824783632</v>
+        <v>0.06823726037213096</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.594512160976342</v>
+        <v>3.551568647712603</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.566880009211171</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.201546667007767</v>
+        <v>-3.358631215764106</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.285904918094317</v>
+        <v>2.223071098591781</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.2622369000217546</v>
+        <v>0.1906643779155224</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.724222149224224</v>
+        <v>3.681278635960485</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.569771103756472</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.20025990346821</v>
+        <v>-3.35734445222455</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.28931071805544</v>
+        <v>2.226476898552905</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.2635236635613112</v>
+        <v>0.191951141455079</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.727885301893259</v>
+        <v>3.68494178862952</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.567882916650247</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.201816957457502</v>
+        <v>-3.358901506213841</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.286799709353499</v>
+        <v>2.223965889850963</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.2635236635613112</v>
+        <v>0.191951141455079</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.725997114787034</v>
+        <v>3.683053601523295</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.56270314625311</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.209088842980966</v>
+        <v>-3.366173391737306</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.278711184746976</v>
+        <v>2.21587736524444</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.2562517780378464</v>
+        <v>0.1846792559316142</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.716454213075818</v>
+        <v>3.673510699812078</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.561137156463262</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.207247823922715</v>
+        <v>-3.364332372679054</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.277881602580428</v>
+        <v>2.215047783077893</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.2575200047093149</v>
+        <v>0.1859474826030826</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.715649159288851</v>
+        <v>3.672705646025112</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.574210563329181</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.214156529422396</v>
+        <v>-3.371241078178735</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.288191527246475</v>
+        <v>2.225357707743939</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.2575200047093149</v>
+        <v>0.1859474826030826</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.72872256615477</v>
+        <v>3.68577905289103</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.574210563329181</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.215718172237255</v>
+        <v>-3.372802720993595</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.287566870120531</v>
+        <v>2.224733050617996</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.2575200047093149</v>
+        <v>0.1859474826030826</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.72872256615477</v>
+        <v>3.68577905289103</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.572734604456183</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.243618959346728</v>
+        <v>-3.400703508103068</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.274930596403744</v>
+        <v>2.212096776901208</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.22292308056638</v>
+        <v>0.1513505584601478</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.706488452796011</v>
+        <v>3.663544939532271</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172536</v>
+        <v>3.684909939172535</v>
       </c>
       <c r="C2014" t="n">
         <v>3.569499048433381</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.455988691801198</v>
+        <v>-3.403736505615742</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.186747147399155</v>
+        <v>2.207648021873338</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.01055334811191005</v>
+        <v>0.1483175609474739</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.575831057300527</v>
+        <v>3.658489585001866</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.834879652549409</v>
+        <v>3.766459802121336</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.817057412010405</v>
+        <v>3.678133007999412</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.455988691801198</v>
+        <v>-3.403736505615742</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.186747147399155</v>
+        <v>2.207648021873338</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.01055334811191005</v>
+        <v>0.1483175609474739</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.810121208996772</v>
+        <v>3.67119680498578</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240704.xlsx
+++ b/tame_output/ON/bt/strategyON_20240704.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>19.4%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.9%</t>
+          <t>-72.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.4%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.1%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.4%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-660.3%</t>
+          <t>-681.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.8%</t>
+          <t>-49.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.2%</t>
+          <t>-68.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>431.5%</t>
+          <t>449.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-501.9%</t>
+          <t>-518.2%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-264.5%</t>
+          <t>-272.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.7%</t>
+          <t>-37.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-155.5%</t>
+          <t>-162.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.9%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-181.4%</t>
+          <t>-182.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-209.2%</t>
+          <t>-219.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-78.9%</t>
+          <t>-89.8%</t>
         </is>
       </c>
     </row>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.1613274819982661</v>
+        <v>-0.04923935230080001</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.221685825096043</v>
+        <v>3.137459091376417</v>
       </c>
       <c r="F1839" t="n">
         <v>1.568940374610322</v>
@@ -43865,16 +43865,16 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.1663650727258526</v>
+        <v>-0.04420176157321348</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.222278301572416</v>
+        <v>3.13805156785279</v>
       </c>
       <c r="F1840" t="n">
         <v>1.62458483087664</v>
@@ -43888,16 +43888,16 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082124</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.09082896198220414</v>
+        <v>-0.3013957962812702</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.09814706931293</v>
+        <v>3.013920335593304</v>
       </c>
       <c r="F1841" t="n">
         <v>1.367390796168583</v>
@@ -43911,16 +43911,16 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757923</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.1565963520316162</v>
+        <v>-0.3671631863306823</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.072857722423636</v>
+        <v>2.988630988704009</v>
       </c>
       <c r="F1842" t="n">
         <v>1.367390796168583</v>
@@ -43934,16 +43934,16 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760741</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.3618410290888608</v>
+        <v>-0.5724078633879268</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.981387883588494</v>
+        <v>2.897161149868867</v>
       </c>
       <c r="F1843" t="n">
         <v>1.367390796168583</v>
@@ -43957,16 +43957,16 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706669</v>
+        <v>3.298730590706668</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.4436129295166125</v>
+        <v>-0.6541797638156785</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.938761849372631</v>
+        <v>2.854535115653005</v>
       </c>
       <c r="F1844" t="n">
         <v>1.394426369574719</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.5108220373884902</v>
+        <v>-0.7213888716875563</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.916643523057583</v>
+        <v>2.832416789337956</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.7183878217801021</v>
+        <v>-0.9289546560791682</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.831442005420178</v>
+        <v>2.747215271700552</v>
       </c>
       <c r="F1846" t="n">
         <v>1.186860585183108</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.136141845326939</v>
+        <v>-1.346708679626005</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.662267287506507</v>
+        <v>2.57804055378688</v>
       </c>
       <c r="F1847" t="n">
         <v>0.7691065616362706</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.426273511932371</v>
+        <v>-1.636840346231436</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.546080837463256</v>
+        <v>2.461854103743629</v>
       </c>
       <c r="F1848" t="n">
         <v>0.7931883563764505</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.634277570285448</v>
+        <v>-1.844844404584514</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.46777135867595</v>
+        <v>2.383544624956324</v>
       </c>
       <c r="F1849" t="n">
         <v>0.7931883563764505</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.845689991173423</v>
+        <v>-2.056256825472489</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.378287846658748</v>
+        <v>2.294061112939122</v>
       </c>
       <c r="F1850" t="n">
         <v>0.5817759354884754</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.211758718318076</v>
+        <v>-2.422325552617142</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.224944655107336</v>
+        <v>2.14071792138771</v>
       </c>
       <c r="F1851" t="n">
         <v>0.2157072083438227</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.42024949976976</v>
+        <v>-2.630816334068826</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.161886632265431</v>
+        <v>2.077659898545804</v>
       </c>
       <c r="F1852" t="n">
         <v>0.007216426892138306</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.667450684534982</v>
+        <v>-2.878017518834048</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.07110490876791</v>
+        <v>1.986878175048284</v>
       </c>
       <c r="F1853" t="n">
         <v>0.02736978039095073</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.159835712559079</v>
+        <v>-3.370402546858144</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.875257289602004</v>
+        <v>1.791030555882378</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.465015247633146</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.545016103489151</v>
+        <v>-3.755582937788217</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.719727672042838</v>
+        <v>1.635500938323212</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.465015247633146</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.794886783503733</v>
+        <v>-4.005453617802798</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.621548523491622</v>
+        <v>1.537321789771996</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.4287525278026827</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.001398560390754</v>
+        <v>-4.21196539468982</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.535049871393071</v>
+        <v>1.450823137673445</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6352643046897042</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.320742635471256</v>
+        <v>-4.531309469770322</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.40908516806113</v>
+        <v>1.324858434341504</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6352643046897042</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.752548428621044</v>
+        <v>-4.963115262920109</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.222695738268619</v>
+        <v>1.138469004548993</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7716818011309712</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.987242422753596</v>
+        <v>-5.197809257052661</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.117102915617689</v>
+        <v>1.032876181898063</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.765345533901716</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.322905069984048</v>
+        <v>-5.533471904283114</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.981418448381473</v>
+        <v>0.8971917146618469</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8332765193906209</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.686531314884362</v>
+        <v>-5.897098149183427</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8424555106555891</v>
+        <v>0.758228776935963</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9314981562577467</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.051658697523108</v>
+        <v>-6.262225531822174</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6956590726059217</v>
+        <v>0.6114323388862957</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.227808940556759</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.460247474703786</v>
+        <v>-6.670814309002852</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5309851057484098</v>
+        <v>0.4467583720287838</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.636397717737438</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.736823575019619</v>
+        <v>-6.947390409318684</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.4155400980935373</v>
+        <v>0.3313133643739112</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.636397717737438</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.153215449306616</v>
+        <v>-7.363782283605682</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2469773989876156</v>
+        <v>0.1627506652679895</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.636397717737438</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.397486850033686</v>
+        <v>-7.608053684332751</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1595275293654668</v>
+        <v>0.07530079564584069</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.636397717737438</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.602737869270446</v>
+        <v>-7.813304703569512</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.07352668681645813</v>
+        <v>-0.01070004690316795</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.636397717737438</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.76631774745483</v>
+        <v>-7.976884581753895</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.006499655597705711</v>
+        <v>-0.07772707812192037</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.636397717737438</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.062979089265028</v>
+        <v>-8.273545923564093</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1083859051971654</v>
+        <v>-0.1926126389167915</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.705140853471316</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.249698797574331</v>
+        <v>-8.460265631873396</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.1871000930552897</v>
+        <v>-0.2713268267749158</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.705140853471316</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.632700186316962</v>
+        <v>-8.843267020616027</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.3404027498739262</v>
+        <v>-0.4246294835935522</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.705140853471316</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.814569977301996</v>
+        <v>-9.025136811601062</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4105791502965102</v>
+        <v>-0.4948058840161362</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.887010644456351</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.174100299805998</v>
+        <v>-9.384667134105063</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.5490409760000605</v>
+        <v>-0.6332677097196866</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.887010644456351</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.22444936326022</v>
+        <v>-9.435016197559285</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.5612645814245716</v>
+        <v>-0.6454913151441981</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.937359707910573</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539464</v>
+        <v>3.501052558539466</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.322068640681616</v>
+        <v>-9.532635474980681</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.5972705417713615</v>
+        <v>-0.6814972754909876</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.03497898533197</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937501</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.469594728687259</v>
+        <v>-9.680161562986324</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6533874206520465</v>
+        <v>-0.7376141543716725</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.182505073337614</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141704</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.673852904017123</v>
+        <v>-9.884419738316188</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7295774936653494</v>
+        <v>-0.8138042273849755</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.310144017951603</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729893</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.707505742525596</v>
+        <v>-9.918072576824661</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.7385560745843027</v>
+        <v>-0.8227828083039288</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.41055738586864</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440636</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.634035910858147</v>
+        <v>-9.844602745157212</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.6937964404239021</v>
+        <v>-0.7780231741435282</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.337087554201192</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.80916032824469</v>
+        <v>-10.01972716254376</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.7492909866310025</v>
+        <v>-0.8335177203506285</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.512211971587735</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410274</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.04361242225918</v>
+        <v>-10.25417925655825</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.8502909891383941</v>
+        <v>-0.9345177228580206</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.512211971587735</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.14798715328563</v>
+        <v>-10.35855398758469</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.8987130723229488</v>
+        <v>-0.9829398060425754</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.616586702614181</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.20077330888595</v>
+        <v>-10.41134014318502</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.9187117447245239</v>
+        <v>-1.00293847844415</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.712262189196578</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.32681010225424</v>
+        <v>-10.53737693655331</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.966432733442725</v>
+        <v>-1.050659467162351</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.687010566386836</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322546</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.27479458828543</v>
+        <v>-10.48536142258449</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.9416361921687981</v>
+        <v>-1.025862925888425</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.687010566386836</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.41646643000955</v>
+        <v>-10.62703326430861</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.9997801557571879</v>
+        <v>-1.084006889476814</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.687010566386836</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.36687558558472</v>
+        <v>-10.57744241988378</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.9648904078223821</v>
+        <v>-1.049117141542009</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.637419721962002</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770582</v>
+        <v>3.676841549770583</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.35406819257994</v>
+        <v>-10.56463502687901</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.9728185842671553</v>
+        <v>-1.057045317986782</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.686275496970903</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615286</v>
+        <v>3.685161381615287</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.12822303986053</v>
+        <v>-10.33878987415959</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.8729014501431824</v>
+        <v>-0.9571281838628081</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.64434882138374</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812105</v>
+        <v>3.684843823812106</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.00364438352294</v>
+        <v>-10.214211217822</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.8219308430520864</v>
+        <v>-0.9061575767717129</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.64434882138374</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646219</v>
+        <v>3.710935533646221</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.05653967156722</v>
+        <v>-10.26710650586629</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.8404551841076939</v>
+        <v>-0.9246819178273196</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.639393475295293</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611571</v>
+        <v>3.768951674611572</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.984406496279343</v>
+        <v>-10.19497333057841</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8058682097539047</v>
+        <v>-0.8900949434735308</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.639393475295293</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857792995533</v>
+        <v>3.728577929955332</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.913040103669696</v>
+        <v>-10.12360693796876</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.7870589151039109</v>
+        <v>-0.8712856488235374</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.568027082685645</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232416</v>
+        <v>3.747702660232417</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.819581069684471</v>
+        <v>-10.03014790398354</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7595587828227286</v>
+        <v>-0.8437855165423547</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.568027082685645</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436232</v>
+        <v>3.766317079436234</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.552339268816073</v>
+        <v>-9.762906103115139</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6544966229747433</v>
+        <v>-0.7387233566943694</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.568027082685645</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311952</v>
+        <v>3.784684521311954</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.454432230139583</v>
+        <v>-9.664999064438648</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6156341224776081</v>
+        <v>-0.6998608561972341</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.500041332825089</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097248</v>
+        <v>3.80082935409725</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.430478689163625</v>
+        <v>-9.64104552346269</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6053841999417311</v>
+        <v>-0.6896109336613572</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.476087791849131</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017776</v>
+        <v>3.789311112017778</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.166418750840828</v>
+        <v>-9.376985585139893</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5130205407743644</v>
+        <v>-0.5972472744939905</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.212027853526335</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839729</v>
+        <v>3.83325274783973</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.459339127335991</v>
+        <v>-8.669905961635056</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2329757250327305</v>
+        <v>-0.3172024587523565</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.212027853526335</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388733</v>
+        <v>3.839374447388735</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.4191548289698</v>
+        <v>-8.629721663268866</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2165583817984129</v>
+        <v>-0.300785115518039</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.171843555160144</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626479</v>
+        <v>3.856161751626481</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.255754958030437</v>
+        <v>-8.466321792329502</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1518316122019105</v>
+        <v>-0.2360583459215366</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.008443684220782</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291815</v>
+        <v>3.787330429291817</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.022273735800837</v>
+        <v>-8.232840570099903</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.05051469447221857</v>
+        <v>-0.1347414281918446</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.774962461991183</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785791</v>
+        <v>3.801637122785793</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.872607344793322</v>
+        <v>-8.083174179092389</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.006459651617828577</v>
+        <v>-0.07776708210179795</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.682058970748648</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390431</v>
+        <v>3.763182248390433</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.740331871162436</v>
+        <v>-7.950898705461502</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.05473732781721008</v>
+        <v>-0.02948940590241644</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.549783497117761</v>
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.526117139945137</v>
+        <v>-7.751768449116968</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1432382809917661</v>
+        <v>0.05297775732303389</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.335568765900463</v>
+        <v>-1.350653240773227</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.352700301743291</v>
+        <v>2.343649616819633</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960991</v>
+        <v>3.753882571960992</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.277117341261556</v>
+        <v>-7.502768650433387</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2557445416888573</v>
+        <v>0.1654840180201251</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.335568765900463</v>
+        <v>-1.350653240773227</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.36560664296695</v>
+        <v>2.356555958043292</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69293185560765</v>
+        <v>3.692931855607651</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.382707331034661</v>
+        <v>-7.608358640206491</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.08553261618039665</v>
+        <v>-0.004727907488335514</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.441158755673567</v>
+        <v>-1.456243230546331</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.174276719503869</v>
+        <v>2.16522603458021</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987908</v>
+        <v>3.77042258398791</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.401442233153258</v>
+        <v>-7.627093542325088</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.1265829972100443</v>
+        <v>0.03632247354131213</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.446754765333698</v>
+        <v>-1.461839240206462</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.219463455584876</v>
+        <v>2.210412770661218</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760333686710817</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.253502191745659</v>
+        <v>-7.479153500917489</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.06588009108491644</v>
+        <v>-0.02438043258381573</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.426433849425141</v>
+        <v>-1.441518324297905</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.111777082441843</v>
+        <v>2.102726397518185</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409208</v>
+        <v>3.72356622940921</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.20053266949167</v>
+        <v>-7.4261839786635</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.07835391373303358</v>
+        <v>-0.01190660993569859</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.373464327171152</v>
+        <v>-1.388548802043916</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.134844809540758</v>
+        <v>2.1257941246171</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098113</v>
+        <v>3.729969716098115</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.15698426272098</v>
+        <v>-7.38263557189281</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.0888126643462166</v>
+        <v>-0.001447859322515566</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.373464327171152</v>
+        <v>-1.388548802043916</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.127884197445665</v>
+        <v>2.118833512522007</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493424</v>
+        <v>3.782922533493426</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.914835869267121</v>
+        <v>-7.140487178438952</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.2001343761089029</v>
+        <v>0.1098738524401708</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.373464327171152</v>
+        <v>-1.388548802043916</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.142346551826808</v>
+        <v>2.13329586690315</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722821</v>
+        <v>3.828551486722822</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.8065767321446</v>
+        <v>-7.03222804131643</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2379701514171066</v>
+        <v>0.1477096277483745</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.373464327171152</v>
+        <v>-1.388548802043916</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.136878672286003</v>
+        <v>2.127827987362345</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.683285597327469</v>
+        <v>-6.908936906499299</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2847846993545358</v>
+        <v>0.1945241756858036</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.250173192354021</v>
+        <v>-1.265257667226785</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.208351447186859</v>
+        <v>2.1993007622632</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919912</v>
+        <v>3.812453678919913</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.662136398424026</v>
+        <v>-6.887787707595856</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.3009453571532386</v>
+        <v>0.2106848334845064</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.229023993450578</v>
+        <v>-1.244108468323342</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.22874194476625</v>
+        <v>2.219691259842591</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318097</v>
+        <v>3.748328408318099</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.418370956440581</v>
+        <v>-6.644022265612412</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.394232242293667</v>
+        <v>0.3039717186249349</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.229023993450578</v>
+        <v>-1.244108468323342</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.2245226531133</v>
+        <v>2.215471968189642</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.82431123305753</v>
+        <v>3.824311233057532</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.316608136163286</v>
+        <v>-6.542259445335117</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4370616843246009</v>
+        <v>0.3468011606558687</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.215804925058149</v>
+        <v>-1.230889399930913</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.234578408068773</v>
+        <v>2.225527723145115</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635497427919</v>
+        <v>3.826354974279192</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.066757742214212</v>
+        <v>-6.292409051386042</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.529743916887933</v>
+        <v>0.4394833932192008</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.215804925058149</v>
+        <v>-1.230889399930913</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.227320483052476</v>
+        <v>2.218269798128817</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011502</v>
+        <v>3.835957987011505</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.890865649746779</v>
+        <v>-6.116516958918609</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6036998773955546</v>
+        <v>0.5134393537268225</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.215804925058149</v>
+        <v>-1.230889399930913</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.230919606573124</v>
+        <v>2.221868921649466</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392991</v>
+        <v>3.780933911392994</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.719419186724315</v>
+        <v>-5.945070495896146</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6856059686590941</v>
+        <v>0.5953454449903619</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.044358462035686</v>
+        <v>-1.05944293690845</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.347114990441156</v>
+        <v>2.338064305517498</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632785</v>
+        <v>3.773765222632789</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.645129620985976</v>
+        <v>-5.870780930157807</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7143422725707267</v>
+        <v>0.6240817489019945</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9700688962973467</v>
+        <v>-0.9851533711701108</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.390709207500457</v>
+        <v>2.381658522576798</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883078</v>
+        <v>3.764617879883081</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.581493878752042</v>
+        <v>-5.807145187923872</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7444913705186176</v>
+        <v>0.6542308468498854</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9064331540634122</v>
+        <v>-0.9215176289361763</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.433585453895135</v>
+        <v>2.424534768971476</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074788</v>
+        <v>3.798814771074792</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.470067119426122</v>
+        <v>-5.695718428597952</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7702563330327812</v>
+        <v>0.679995809364049</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9064331540634122</v>
+        <v>-0.9215176289361763</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.41477971267893</v>
+        <v>2.405729027755272</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.7976948842423</v>
+        <v>3.797694884242303</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.229636622621261</v>
+        <v>-5.455287931793092</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8681716083796029</v>
+        <v>0.7779110847108708</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6660026572585519</v>
+        <v>-0.681087132131316</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.560781087386724</v>
+        <v>2.551730402463065</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936769</v>
+        <v>3.821593509367694</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.157394054450067</v>
+        <v>-5.383045363621897</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.900997949482901</v>
+        <v>0.8107374258141689</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6660026572585519</v>
+        <v>-0.681087132131316</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.564710401221544</v>
+        <v>2.555659716297885</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879971</v>
+        <v>3.822326997879975</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.104395732168679</v>
+        <v>-5.330047041340509</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9228758623127962</v>
+        <v>0.832615338644064</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6106663982566131</v>
+        <v>-0.6257508731293772</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.598590740540047</v>
+        <v>2.589540055616389</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502343</v>
+        <v>3.848616626502347</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.995590846688952</v>
+        <v>-5.221242155860782</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9633958877246802</v>
+        <v>0.873135364055948</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6106663982566131</v>
+        <v>-0.6257508731293772</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.595588811760041</v>
+        <v>2.586538126836382</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675945</v>
+        <v>3.818668951675948</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.775570048651941</v>
+        <v>-5.001221357823772</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.052983243950099</v>
+        <v>0.9627227202813664</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4694465531886328</v>
+        <v>-0.4845310280613969</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.681899755811443</v>
+        <v>2.672849070887785</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539956</v>
+        <v>3.843274527539959</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.642702359588664</v>
+        <v>-4.868353668760494</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.122024502377233</v>
+        <v>1.031763978708501</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4694465531886328</v>
+        <v>-0.4845310280613969</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.697793938613266</v>
+        <v>2.688743253689608</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496267</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.522529276224165</v>
+        <v>-4.748180585395995</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.171239580163334</v>
+        <v>1.080979056494602</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3492734698241339</v>
+        <v>-0.364357944696898</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.771043633072268</v>
+        <v>2.761992948148609</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551577004</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.377857131124427</v>
+        <v>-4.603508440296258</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.239196540764669</v>
+        <v>1.148936017095937</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2046013247243965</v>
+        <v>-0.2196857995971606</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.86793502269355</v>
+        <v>2.858884337769891</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942106</v>
+        <v>3.735839222942109</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.43773195848212</v>
+        <v>-4.66338326765395</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.201284101223018</v>
+        <v>1.111023577554286</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2644761520820886</v>
+        <v>-0.2795606269548527</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.818047617680361</v>
+        <v>2.808996932756702</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674518</v>
+        <v>3.762647477674521</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.350932460703111</v>
+        <v>-4.576583769874942</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.258404393657188</v>
+        <v>1.168143869988455</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2644761520820886</v>
+        <v>-0.2795606269548527</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.840448111002927</v>
+        <v>2.831397426079268</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.7291463984307</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.353402167164917</v>
+        <v>-4.579053476336748</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.257488912445877</v>
+        <v>1.167228388777145</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2669458585438947</v>
+        <v>-0.2820303334166588</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.839038688499255</v>
+        <v>2.829988003575596</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003605</v>
+        <v>3.743220196003609</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.421772353488928</v>
+        <v>-4.647423662660758</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.241147760390975</v>
+        <v>1.150887236722243</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2576701595076798</v>
+        <v>-0.2727546343804439</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.855611030395686</v>
+        <v>2.846560345472028</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508373</v>
+        <v>3.714179139508377</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.435560406335974</v>
+        <v>-4.661211715507805</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.226069247884048</v>
+        <v>1.135808724215316</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2576701595076798</v>
+        <v>-0.2727546343804439</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.846047739027577</v>
+        <v>2.836997054103919</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417708</v>
+        <v>3.710906731417712</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.46655356566468</v>
+        <v>-4.69220487483651</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.038381549192952</v>
+        <v>0.9481210255242203</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2576701595076798</v>
+        <v>-0.2727546343804439</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.670757304067964</v>
+        <v>2.661706619144306</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205905</v>
+        <v>3.746042526205908</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.291079305872211</v>
+        <v>-4.516730615044041</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.113138485101728</v>
+        <v>1.022877961432996</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2576701595076798</v>
+        <v>-0.2727546343804439</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.675324536059752</v>
+        <v>2.666273851136093</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225449</v>
+        <v>3.765024323225453</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.40201555851346</v>
+        <v>-4.62766686768529</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.044506012806435</v>
+        <v>0.954245489137703</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2576701595076798</v>
+        <v>-0.2727546343804439</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.651066564820959</v>
+        <v>2.642015879897301</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111298</v>
+        <v>3.773210297111302</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.368352013041178</v>
+        <v>-4.594003322213008</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.061102816215254</v>
+        <v>0.9708422925465214</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.224006614035398</v>
+        <v>-0.2390910889081621</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.674396077324233</v>
+        <v>2.665345392400575</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264168</v>
+        <v>3.784343952264171</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.308499393837455</v>
+        <v>-4.534150703009285</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.095216250328875</v>
+        <v>1.004955726660143</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.224006614035398</v>
+        <v>-0.2390910889081621</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.684568463756366</v>
+        <v>2.675517778832707</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742304</v>
+        <v>3.786949957742308</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.222255930811077</v>
+        <v>-4.447907239982907</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.124659906113287</v>
+        <v>1.034399382444555</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.224006614035398</v>
+        <v>-0.2390910889081621</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.679514734330226</v>
+        <v>2.670464049406568</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316051</v>
+        <v>3.752027499316054</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.267562750210057</v>
+        <v>-4.493214059381887</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.09831295379822</v>
+        <v>1.008052430129488</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2648167770446287</v>
+        <v>-0.2799012519173928</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.646804411969213</v>
+        <v>2.637753727045555</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803196</v>
+        <v>3.7535711658032</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.296595854912358</v>
+        <v>-4.522247164084188</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.087251584950401</v>
+        <v>0.9969910612816693</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2648167770446287</v>
+        <v>-0.2799012519173928</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.647356285002315</v>
+        <v>2.638305600078656</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809503</v>
+        <v>3.733390600809507</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.203785373461498</v>
+        <v>-4.429436682633328</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.053648469422111</v>
+        <v>0.9633879457533787</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1720062955937694</v>
+        <v>-0.1870907704665335</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.632315265764196</v>
+        <v>2.623264580840538</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560432</v>
+        <v>3.748285816560434</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.248174842790926</v>
+        <v>-4.473826151962756</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.037766157614941</v>
+        <v>0.9475056339462087</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2163957649231971</v>
+        <v>-0.2314802397959612</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.607555060091141</v>
+        <v>2.598504375167482</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472744</v>
+        <v>3.721077195472747</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.135503624554675</v>
+        <v>-4.361154933726506</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.077910353421164</v>
+        <v>0.9876498297524317</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1037245466869469</v>
+        <v>-0.118809021559711</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.670233499544613</v>
+        <v>2.661182814620955</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798543</v>
+        <v>3.743047603798546</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.023126623372002</v>
+        <v>-4.248777932543833</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.1283524497249</v>
+        <v>1.038091926056168</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1037245466869469</v>
+        <v>-0.118809021559711</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.675724795375281</v>
+        <v>2.666674110451622</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498871</v>
+        <v>3.689597840498874</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.050907021273355</v>
+        <v>-4.276558330445186</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.128737492332898</v>
+        <v>1.038476968664166</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1315049445882999</v>
+        <v>-0.146589419461064</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.670553758403008</v>
+        <v>2.661503073479349</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705331</v>
+        <v>3.643069621705335</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.133908302298634</v>
+        <v>-4.359559611470464</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.93389269992344</v>
+        <v>0.8436321762547079</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1500758291154737</v>
+        <v>-0.1651603039882378</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.497766947687357</v>
+        <v>2.488716262763699</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729276</v>
+        <v>3.682716310729279</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.242522380741965</v>
+        <v>-4.468173689913796</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.010596729265313</v>
+        <v>0.9203362055965809</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1500758291154737</v>
+        <v>-0.1651603039882378</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.617916608406563</v>
+        <v>2.608865923482904</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190775</v>
+        <v>3.733012441190779</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.207113342493822</v>
+        <v>-4.432764651665653</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.039273370666893</v>
+        <v>0.9490128469981611</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1500758291154737</v>
+        <v>-0.1651603039882378</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.632429634508886</v>
+        <v>2.623378949585227</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913432</v>
+        <v>3.741174069913436</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.168729679935671</v>
+        <v>-4.394380989107502</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.052046277032523</v>
+        <v>0.9617857533637904</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1116921665573225</v>
+        <v>-0.1267766414300866</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.652879273386145</v>
+        <v>2.643828588462486</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532493</v>
+        <v>3.751147197532497</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.991613349900505</v>
+        <v>-4.217264659072335</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.119621837891891</v>
+        <v>1.029361314223159</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1116921665573225</v>
+        <v>-0.1267766414300866</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.649608302231447</v>
+        <v>2.640557617307788</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793911</v>
+        <v>3.741328448793914</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.036705594734051</v>
+        <v>-4.262356903905881</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.102268331720386</v>
+        <v>1.012007808051653</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1735882097267123</v>
+        <v>-0.1886726845994764</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.613154068091726</v>
+        <v>2.604103383168068</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011243</v>
+        <v>3.750729377011247</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.857330173495283</v>
+        <v>-4.082981482667114</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.167805475522307</v>
+        <v>1.077544951853575</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.01681145155599362</v>
+        <v>-0.03189592642875771</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.701007098300572</v>
+        <v>2.691956413376913</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982237</v>
+        <v>3.716991718982241</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.902344387015889</v>
+        <v>-4.127995696187719</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.130607245445654</v>
+        <v>1.040346721776922</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.04716034687059822</v>
+        <v>-0.06224482174336232</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.663605216443399</v>
+        <v>2.65455453151974</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509546</v>
+        <v>3.73702660850955</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.169348897288325</v>
+        <v>-4.395000206460154</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.029497003675626</v>
+        <v>0.939236480006894</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2415233849135468</v>
+        <v>-0.2566078597863109</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.552678955956575</v>
+        <v>2.543628271032917</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760817</v>
+        <v>3.702309454760821</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.270546678725498</v>
+        <v>-4.496197987897327</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9882218129972582</v>
+        <v>0.8979612893285265</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.309932198458866</v>
+        <v>-0.3250166733316301</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.510837589725885</v>
+        <v>2.501786904802227</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815462</v>
+        <v>3.705571661815465</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.264035712111185</v>
+        <v>-4.489687021283014</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9884261611973</v>
+        <v>0.8981656375285683</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.309932198458866</v>
+        <v>-0.3250166733316301</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.508437551280202</v>
+        <v>2.499386866356543</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378107</v>
+        <v>3.709510443378109</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.244997584403888</v>
+        <v>-4.470648893575717</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9925661314884637</v>
+        <v>0.902305607819732</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3681158097900605</v>
+        <v>-0.3832002846628246</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.47005210368973</v>
+        <v>2.461001418766072</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131258</v>
+        <v>3.73106447313126</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.276124215554506</v>
+        <v>-4.501775524726336</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.157697347966897</v>
+        <v>1.067436824298165</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3681158097900605</v>
+        <v>-0.3832002846628246</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.647633972628411</v>
+        <v>2.638583287704752</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067873</v>
+        <v>3.722447362067877</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.289990976888424</v>
+        <v>-4.515642286060253</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.152983972419463</v>
+        <v>1.062723448750732</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4059737265238835</v>
+        <v>-0.4210582013966476</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.625752551574251</v>
+        <v>2.616701866650592</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789129</v>
+        <v>3.787425580789133</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.245186805348494</v>
+        <v>-4.470838114520324</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.176914171432361</v>
+        <v>1.086653647763629</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4059737265238835</v>
+        <v>-0.4210582013966476</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.631761081971177</v>
+        <v>2.622710397047518</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519916</v>
+        <v>3.78150125051992</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.097443835113491</v>
+        <v>-4.323095144285321</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.315164007318384</v>
+        <v>1.224903483649652</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2381663692890003</v>
+        <v>-0.2532508441617644</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.811598144104128</v>
+        <v>2.80254745918047</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181178</v>
+        <v>3.802245929181182</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.199458517644713</v>
+        <v>-4.425109826816542</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.277151755837377</v>
+        <v>1.186891232168645</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2381663692890003</v>
+        <v>-0.2532508441617644</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.814391765635609</v>
+        <v>2.805341080711951</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394739</v>
+        <v>3.805608985394742</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.193305811591928</v>
+        <v>-4.418957120763758</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.280275186650149</v>
+        <v>1.190014662981417</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.232013663236216</v>
+        <v>-0.2470981381089801</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.818745737658938</v>
+        <v>2.80969505273528</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890618</v>
+        <v>3.798239794890619</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.21011510974243</v>
+        <v>-4.43576641891426</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.272631944130058</v>
+        <v>1.182371420461326</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2488229613867177</v>
+        <v>-0.2639074362594818</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.807740635508747</v>
+        <v>2.798689950585089</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798433</v>
+        <v>3.867362636798436</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.147817110966308</v>
+        <v>-4.373468420138138</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.363886697437328</v>
+        <v>1.273626173768596</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2488229613867177</v>
+        <v>-0.2639074362594818</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.874076189305568</v>
+        <v>2.86502550438191</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.8487291399922</v>
+        <v>3.848729139992203</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.94602691330115</v>
+        <v>-4.17167822247298</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.153183648892789</v>
+        <v>1.062923125224057</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.05080476921756327</v>
+        <v>-0.06588924409032737</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.701467976996459</v>
+        <v>2.6924172920728</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852429</v>
+        <v>3.841444817852433</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.872648816212414</v>
+        <v>-4.098300125384243</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.252825120050459</v>
+        <v>1.162564596381727</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.02257332787117328</v>
+        <v>0.007488852998409179</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.815785067571876</v>
+        <v>2.806734382648218</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319554</v>
+        <v>3.819063300319558</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.970389360837388</v>
+        <v>-4.196040670009218</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.228356638316513</v>
+        <v>1.138096114647781</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.006684049738193087</v>
+        <v>-0.00840042513457101</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.820879236808131</v>
+        <v>2.811828551884473</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489393</v>
+        <v>3.831819032489396</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.146727120960318</v>
+        <v>-4.372378430132147</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.156357515092013</v>
+        <v>1.066096991423281</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1696537103847363</v>
+        <v>-0.1847381852575004</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.713612561559045</v>
+        <v>2.704561876635387</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397802</v>
+        <v>3.836411672397806</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.070305074528391</v>
+        <v>-4.29595638370022</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.185417951704712</v>
+        <v>1.09515742803598</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1696537103847363</v>
+        <v>-0.1847381852575004</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.712104179598974</v>
+        <v>2.703053494675316</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316257</v>
+        <v>3.833513460316261</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.025931942889822</v>
+        <v>-4.251583252061652</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.203030071795576</v>
+        <v>1.112769548126844</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1252805787461677</v>
+        <v>-0.1403650536189318</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.738590926017551</v>
+        <v>2.729540241093893</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105971</v>
+        <v>3.821562117105975</v>
       </c>
       <c r="C1977" t="n">
         <v>2.808153067403842</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.903097722002655</v>
+        <v>-4.128749031174484</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.246557554289033</v>
+        <v>1.156297030620301</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1252805787461677</v>
+        <v>-0.1403650536189318</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.732984720156142</v>
+        <v>2.723934035232483</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190329</v>
+        <v>3.833011148190333</v>
       </c>
       <c r="C1978" t="n">
         <v>2.814534824431647</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.855441991441599</v>
+        <v>-4.081093300613428</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.27200160354126</v>
+        <v>1.181741079872528</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.07762484818511206</v>
+        <v>-0.09270932305787616</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.76795991552058</v>
+        <v>2.758909230596921</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569622</v>
+        <v>3.822678210569626</v>
       </c>
       <c r="C1979" t="n">
         <v>2.819427197806371</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.754923832942844</v>
+        <v>-3.980575142114674</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.317101240315486</v>
+        <v>1.226840716646755</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.0228933103136425</v>
+        <v>0.007808835440878403</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.833163183994557</v>
+        <v>2.824112499070899</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557298</v>
+        <v>3.828808877557301</v>
       </c>
       <c r="C1980" t="n">
         <v>2.806181870282244</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.815590423345233</v>
+        <v>-4.041241732517063</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.279589276630403</v>
+        <v>1.189328752961671</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.05880500640489117</v>
+        <v>-0.07388948127765527</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.770898866439309</v>
+        <v>2.761848181515651</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932774</v>
+        <v>3.816837033932776</v>
       </c>
       <c r="C1981" t="n">
         <v>2.810279572892872</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.770752021736835</v>
+        <v>-3.996403330908665</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.301622339884391</v>
+        <v>1.211361816215659</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.05426157346002169</v>
+        <v>-0.06934604833278579</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.777722628816859</v>
+        <v>2.768671943893201</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917058</v>
+        <v>3.81793235491706</v>
       </c>
       <c r="C1982" t="n">
         <v>2.81444051252395</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.871510657493834</v>
+        <v>-4.097161966665664</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.265479825212669</v>
+        <v>1.175219301543937</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1430871421870271</v>
+        <v>-0.1581716170597912</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.728588227211734</v>
+        <v>2.719537542288076</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405967</v>
+        <v>3.826684745405969</v>
       </c>
       <c r="C1983" t="n">
         <v>2.820320115051787</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.827307820407933</v>
+        <v>-4.052959129579763</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.289040562574867</v>
+        <v>1.198780038906135</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.09888430510112667</v>
+        <v>-0.1139687799738908</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.760989531991112</v>
+        <v>2.751938847067453</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265652</v>
+        <v>3.838199629265654</v>
       </c>
       <c r="C1984" t="n">
         <v>2.818730115521035</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.864286848071377</v>
+        <v>-4.089938157243207</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.272658951978737</v>
+        <v>1.182398428310005</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.06191040330979614</v>
+        <v>-0.07699487818256023</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.781583873535157</v>
+        <v>2.772533188611499</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284887</v>
+        <v>3.863895080284888</v>
       </c>
       <c r="C1985" t="n">
         <v>2.869977880704075</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.884344926936217</v>
+        <v>-4.109996236108048</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.315883485615841</v>
+        <v>1.225622961947108</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.06191040330979614</v>
+        <v>-0.07699487818256023</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.832831638718197</v>
+        <v>2.823780953794539</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321029</v>
+        <v>3.865338681321031</v>
       </c>
       <c r="C1986" t="n">
         <v>2.868418585298328</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.844414253758326</v>
+        <v>-4.070065562930157</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.33029645948125</v>
+        <v>1.240035935812517</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.02197973013190579</v>
+        <v>-0.03706420500466989</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.855230747219184</v>
+        <v>2.846180062295526</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475146</v>
+        <v>3.864489842475148</v>
       </c>
       <c r="C1987" t="n">
         <v>2.863366813536598</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.793382161035798</v>
+        <v>-4.01903347020763</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.345657524808531</v>
+        <v>1.255397001139799</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.02905236259062216</v>
+        <v>0.01396788771785806</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.880798231090971</v>
+        <v>2.871747546167313</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404862</v>
+        <v>3.842547360404864</v>
       </c>
       <c r="C1988" t="n">
         <v>2.880554217629303</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.728157979908593</v>
+        <v>-3.953809289080424</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.388934601352118</v>
+        <v>1.298674077683386</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.09427654371782779</v>
+        <v>0.07919206884506369</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.93712014386</v>
+        <v>2.928069458936341</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882566</v>
+        <v>3.840061186882568</v>
       </c>
       <c r="C1989" t="n">
         <v>2.876515189928583</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.690730959837459</v>
+        <v>-3.91638226900929</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.399866381679852</v>
+        <v>1.30960585801112</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.09952808174700944</v>
+        <v>0.08444360687424535</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.936232038976789</v>
+        <v>2.92718135405313</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899267</v>
+        <v>3.845169808992672</v>
       </c>
       <c r="C1990" t="n">
         <v>2.877771982259823</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.710842615872167</v>
+        <v>-3.936493925043999</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.393078511597209</v>
+        <v>1.302817987928476</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1105554267444286</v>
+        <v>0.09547095187166454</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.944105238306481</v>
+        <v>2.935054553382822</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636296</v>
+        <v>3.828661445636298</v>
       </c>
       <c r="C1991" t="n">
         <v>3.038329753281034</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.657097801444963</v>
+        <v>-3.882749110616794</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.575134208389302</v>
+        <v>1.484873684720569</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.1206187361848906</v>
+        <v>0.1055342613121265</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.110700994991969</v>
+        <v>3.10165031006831</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957634</v>
+        <v>3.813222820957636</v>
       </c>
       <c r="C1992" t="n">
         <v>3.158442662498851</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.63330623283882</v>
+        <v>-3.858957542010652</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.704763745049576</v>
+        <v>1.614503221380843</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.1444103047910329</v>
+        <v>0.1293258299182688</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.245088845373471</v>
+        <v>3.236038160449813</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799876</v>
+        <v>3.814230727998762</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15015063851271</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.607222148575012</v>
+        <v>-3.832873457746844</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.706905354768958</v>
+        <v>1.616644831100225</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.1444103047910329</v>
+        <v>0.1293258299182688</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.23679682138733</v>
+        <v>3.227746136463672</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896935</v>
+        <v>3.803397818896936</v>
       </c>
       <c r="C1994" t="n">
         <v>3.14834383409649</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.529090967726066</v>
+        <v>-3.754742276897897</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.736351022692316</v>
+        <v>1.646090499023584</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2185871156747174</v>
+        <v>0.2035026408019533</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.27949610350132</v>
+        <v>3.270445418577662</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959865</v>
+        <v>3.796264143959866</v>
       </c>
       <c r="C1995" t="n">
         <v>3.165898239823281</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.520198506332783</v>
+        <v>-3.745849815504614</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.757462412976421</v>
+        <v>1.667201889307688</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2185871156747174</v>
+        <v>0.2035026408019533</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.297050509228112</v>
+        <v>3.287999824304453</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945373</v>
+        <v>3.794424941945376</v>
       </c>
       <c r="C1996" t="n">
         <v>3.157753287227865</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.68867462330266</v>
+        <v>-3.914325932474492</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.681927013593054</v>
+        <v>1.591666489924321</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1906392799581367</v>
+        <v>0.1755548050853726</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.272136855202747</v>
+        <v>3.263086170279089</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782716</v>
+        <v>3.795574066782718</v>
       </c>
       <c r="C1997" t="n">
         <v>3.139022984415727</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.990875094441077</v>
+        <v>-3.216526403612908</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.942316522325549</v>
+        <v>1.852055998656816</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.120291220587726</v>
+        <v>0.1052067457149619</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.211197716768363</v>
+        <v>3.202147031844704</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632646</v>
+        <v>3.784671345632648</v>
       </c>
       <c r="C1998" t="n">
         <v>3.129687006912631</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.968153990757925</v>
+        <v>-3.193805299929756</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.942068986295714</v>
+        <v>1.851808462626982</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.120291220587726</v>
+        <v>0.1052067457149619</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.201861739265267</v>
+        <v>3.192811054341609</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777684</v>
+        <v>3.783205696777686</v>
       </c>
       <c r="C1999" t="n">
         <v>3.2885931327638</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.966428947467881</v>
+        <v>-3.192080256639712</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.101665129462901</v>
+        <v>2.011404605794168</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.1220162638777697</v>
+        <v>0.1069317890050056</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.361802891090463</v>
+        <v>3.352752206166804</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644423</v>
+        <v>3.779933725644424</v>
       </c>
       <c r="C2000" t="n">
         <v>3.325670955257447</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.121209954246136</v>
+        <v>-3.346861263417967</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.076830549245245</v>
+        <v>1.986570025576513</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.0886485898232936</v>
+        <v>0.0735641149505295</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.378860109151423</v>
+        <v>3.369809424227765</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979997</v>
+        <v>3.769443619799972</v>
       </c>
       <c r="C2001" t="n">
         <v>3.322346311246992</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.069774620861476</v>
+        <v>-3.295425930033308</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.094080038588654</v>
+        <v>2.003819514919922</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.1400839232079533</v>
+        <v>0.1249994483351892</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.406396665171764</v>
+        <v>3.397345980248106</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331125</v>
+        <v>3.766673496331127</v>
       </c>
       <c r="C2002" t="n">
         <v>3.332352464891734</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.042823396534988</v>
+        <v>-3.26847470570682</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.114866681963991</v>
+        <v>2.024606158295259</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.1549642692356724</v>
+        <v>0.1398797943629083</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.425331026433137</v>
+        <v>3.416280341509479</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784119</v>
+        <v>3.76805206778412</v>
       </c>
       <c r="C2003" t="n">
         <v>3.516455597036694</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.178776404591305</v>
+        <v>-3.404427713763136</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.244588610886424</v>
+        <v>2.154328087217692</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.1549642692356724</v>
+        <v>0.1398797943629083</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.609434158578097</v>
+        <v>3.600383473654439</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714432</v>
+        <v>3.743925505714434</v>
       </c>
       <c r="C2004" t="n">
         <v>3.508572291939687</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.201184522396177</v>
+        <v>-3.426835831568008</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.227742058667469</v>
+        <v>2.137481534998736</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.1549642692356724</v>
+        <v>0.1398797943629083</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.60155085348109</v>
+        <v>3.592500168557432</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155042</v>
+        <v>3.719118627155044</v>
       </c>
       <c r="C2005" t="n">
         <v>3.510626291489324</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.349190289875576</v>
+        <v>-3.574841599047407</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.170593751225346</v>
+        <v>2.080333227556614</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.06823726037213096</v>
+        <v>0.05315278549936686</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.551568647712603</v>
+        <v>3.542517962788944</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161988</v>
+        <v>3.729452285161989</v>
       </c>
       <c r="C2006" t="n">
         <v>3.566880009211171</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.358631215764106</v>
+        <v>-3.521587350072851</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.223071098591781</v>
+        <v>2.157888644868283</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.1906643779155224</v>
+        <v>0.08300566814417887</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.681278635960485</v>
+        <v>3.616683410097679</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321645</v>
+        <v>3.714941193321646</v>
       </c>
       <c r="C2007" t="n">
         <v>3.569771103756472</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.35734445222455</v>
+        <v>-3.520300586533295</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.226476898552905</v>
+        <v>2.161294444829407</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.191951141455079</v>
+        <v>0.08429243168373546</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.68494178862952</v>
+        <v>3.620346562766714</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347713</v>
+        <v>3.727898186347715</v>
       </c>
       <c r="C2008" t="n">
         <v>3.567882916650247</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.358901506213841</v>
+        <v>-3.521857640522586</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.223965889850963</v>
+        <v>2.158783436127465</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.191951141455079</v>
+        <v>0.08429243168373546</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.683053601523295</v>
+        <v>3.618458375660489</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887757</v>
+        <v>3.710654104887759</v>
       </c>
       <c r="C2009" t="n">
         <v>3.56270314625311</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.366173391737306</v>
+        <v>-3.52912952604605</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.21587736524444</v>
+        <v>2.150694911520942</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.1846792559316142</v>
+        <v>0.07702054616027071</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.673510699812078</v>
+        <v>3.608915473949272</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343075</v>
+        <v>3.712897612343077</v>
       </c>
       <c r="C2010" t="n">
         <v>3.561137156463262</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.364332372679054</v>
+        <v>-3.527288506987799</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.215047783077893</v>
+        <v>2.149865329354395</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.1859474826030826</v>
+        <v>0.07828877283173913</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.672705646025112</v>
+        <v>3.608110420162306</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647116</v>
+        <v>3.754911907647117</v>
       </c>
       <c r="C2011" t="n">
         <v>3.574210563329181</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.371241078178735</v>
+        <v>-3.53419721248748</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.225357707743939</v>
+        <v>2.160175254020441</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.1859474826030826</v>
+        <v>0.07828877283173913</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.68577905289103</v>
+        <v>3.621183827028224</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763538</v>
+        <v>3.74989685176354</v>
       </c>
       <c r="C2012" t="n">
         <v>3.574210563329181</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.372802720993595</v>
+        <v>-3.53575885530234</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.224733050617996</v>
+        <v>2.159550596894498</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.1859474826030826</v>
+        <v>0.07828877283173913</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.68577905289103</v>
+        <v>3.621183827028224</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392122</v>
+        <v>3.715834055392124</v>
       </c>
       <c r="C2013" t="n">
         <v>3.572734604456183</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.400703508103068</v>
+        <v>-3.563659642411813</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.212096776901208</v>
+        <v>2.14691432317771</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.1513505584601478</v>
+        <v>0.04369184868880432</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.663544939532271</v>
+        <v>3.598949713669465</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172535</v>
+        <v>3.684909939172536</v>
       </c>
       <c r="C2014" t="n">
         <v>3.569499048433381</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.403736505615742</v>
+        <v>-3.566692639924486</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.207648021873338</v>
+        <v>2.14246556814984</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.1483175609474739</v>
+        <v>0.04065885117613044</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.658489585001866</v>
+        <v>3.59389435913906</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.766459802121336</v>
+        <v>3.474291009187088</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.678133007999412</v>
+        <v>3.568972619008902</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.403736505615742</v>
+        <v>-3.566692639924486</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.207648021873338</v>
+        <v>2.14246556814984</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.1483175609474739</v>
+        <v>0.04065885117613044</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.67119680498578</v>
+        <v>3.56203641599527</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240704.xlsx
+++ b/tame_output/ON/bt/strategyON_20240704.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.9%</t>
+          <t>-73.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.8%</t>
+          <t>-69.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.2%</t>
+          <t>449.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-518.2%</t>
+          <t>-525.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-34.5%</t>
+          <t>-40.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-162.0%</t>
+          <t>-165.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-182.3%</t>
+          <t>-180.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-219.9%</t>
+          <t>-226.0%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.751768449116968</v>
+        <v>-7.79516037290176</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.05297775732303389</v>
+        <v>0.03562098780911693</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.350653240773227</v>
+        <v>-1.394045164558019</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.343649616819633</v>
+        <v>2.317614462548757</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.502768650433387</v>
+        <v>-7.546160574218179</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1654840180201251</v>
+        <v>0.1481272485062082</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.350653240773227</v>
+        <v>-1.394045164558019</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.356555958043292</v>
+        <v>2.330520803772416</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.608358640206491</v>
+        <v>-7.651750563991284</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.004727907488335514</v>
+        <v>-0.02208467700225247</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.456243230546331</v>
+        <v>-1.499635154331124</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.16522603458021</v>
+        <v>2.139190880309334</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.627093542325088</v>
+        <v>-7.670485466109881</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.03632247354131213</v>
+        <v>0.01896570402739517</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.461839240206462</v>
+        <v>-1.505231163991255</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.210412770661218</v>
+        <v>2.184377616390342</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.479153500917489</v>
+        <v>-7.522545424702281</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.02438043258381573</v>
+        <v>-0.04173720209773268</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.441518324297905</v>
+        <v>-1.484910248082697</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.102726397518185</v>
+        <v>2.076691243247309</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.4261839786635</v>
+        <v>-7.469575902448293</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.01190660993569859</v>
+        <v>-0.02926337944961555</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.388548802043916</v>
+        <v>-1.431940725828709</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.1257941246171</v>
+        <v>2.099758970346224</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.38263557189281</v>
+        <v>-7.426027495677602</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.001447859322515566</v>
+        <v>-0.01880462883643252</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.388548802043916</v>
+        <v>-1.431940725828709</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.118833512522007</v>
+        <v>2.092798358251131</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.140487178438952</v>
+        <v>-7.183879102223744</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1098738524401708</v>
+        <v>0.09251708292625382</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.388548802043916</v>
+        <v>-1.431940725828709</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.13329586690315</v>
+        <v>2.107260712632274</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.03222804131643</v>
+        <v>-7.075619965101223</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1477096277483745</v>
+        <v>0.1303528582344575</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.388548802043916</v>
+        <v>-1.431940725828709</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.127827987362345</v>
+        <v>2.101792833091469</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.908936906499299</v>
+        <v>-6.952328830284092</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1945241756858036</v>
+        <v>0.1771674061718866</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.265257667226785</v>
+        <v>-1.308649591011578</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.1993007622632</v>
+        <v>2.173265607992324</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.887787707595856</v>
+        <v>-6.931179631380648</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2106848334845064</v>
+        <v>0.1933280639705894</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.244108468323342</v>
+        <v>-1.287500392108135</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.219691259842591</v>
+        <v>2.193656105571716</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.644022265612412</v>
+        <v>-6.687414189397204</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3039717186249349</v>
+        <v>0.2866149491110179</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.244108468323342</v>
+        <v>-1.287500392108135</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.215471968189642</v>
+        <v>2.189436813918766</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.542259445335117</v>
+        <v>-6.585651369119909</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3468011606558687</v>
+        <v>0.3294443911419518</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.230889399930913</v>
+        <v>-1.274281323715706</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.225527723145115</v>
+        <v>2.199492568874239</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.292409051386042</v>
+        <v>-6.335800975170835</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4394833932192008</v>
+        <v>0.4221266237052839</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.230889399930913</v>
+        <v>-1.274281323715706</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.218269798128817</v>
+        <v>2.192234643857941</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.116516958918609</v>
+        <v>-6.159908882703402</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5134393537268225</v>
+        <v>0.4960825842129055</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.230889399930913</v>
+        <v>-1.274281323715706</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.221868921649466</v>
+        <v>2.19583376737859</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.945070495896146</v>
+        <v>-5.988462419680938</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5953454449903619</v>
+        <v>0.5779886754764449</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.05944293690845</v>
+        <v>-1.102834860693243</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.338064305517498</v>
+        <v>2.312029151246622</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.870780930157807</v>
+        <v>-5.914172853942599</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6240817489019945</v>
+        <v>0.6067249793880776</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9851533711701108</v>
+        <v>-1.028545294954904</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.381658522576798</v>
+        <v>2.355623368305922</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.807145187923872</v>
+        <v>-5.850537111708665</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6542308468498854</v>
+        <v>0.6368740773359685</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9215176289361763</v>
+        <v>-0.9649095527209691</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.424534768971476</v>
+        <v>2.3984996147006</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.695718428597952</v>
+        <v>-5.739110352382744</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.679995809364049</v>
+        <v>0.6626390398501321</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9215176289361763</v>
+        <v>-0.9649095527209691</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.405729027755272</v>
+        <v>2.379693873484396</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.455287931793092</v>
+        <v>-5.498679855577884</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7779110847108708</v>
+        <v>0.7605543151969538</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.681087132131316</v>
+        <v>-0.7244790559161088</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.551730402463065</v>
+        <v>2.52569524819219</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.383045363621897</v>
+        <v>-5.42643728740669</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8107374258141689</v>
+        <v>0.7933806563002519</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.681087132131316</v>
+        <v>-0.7244790559161088</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.555659716297885</v>
+        <v>2.52962456202701</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.330047041340509</v>
+        <v>-5.373438965125302</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.832615338644064</v>
+        <v>0.815258569130147</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6257508731293772</v>
+        <v>-0.66914279691417</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.589540055616389</v>
+        <v>2.563504901345513</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.221242155860782</v>
+        <v>-5.264634079645575</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.873135364055948</v>
+        <v>0.8557785945420311</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6257508731293772</v>
+        <v>-0.66914279691417</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.586538126836382</v>
+        <v>2.560502972565506</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.001221357823772</v>
+        <v>-5.044613281608564</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9627227202813664</v>
+        <v>0.9453659507674494</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4845310280613969</v>
+        <v>-0.5279229518461898</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.672849070887785</v>
+        <v>2.646813916616909</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.868353668760494</v>
+        <v>-4.911745592545286</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.031763978708501</v>
+        <v>1.014407209194584</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4845310280613969</v>
+        <v>-0.5279229518461898</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.688743253689608</v>
+        <v>2.662708099418732</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.748180585395995</v>
+        <v>-4.791572509180788</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.080979056494602</v>
+        <v>1.063622286980685</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.364357944696898</v>
+        <v>-0.4077498684816908</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.761992948148609</v>
+        <v>2.735957793877733</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.603508440296258</v>
+        <v>-4.64690036408105</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.148936017095937</v>
+        <v>1.13157924758202</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2196857995971606</v>
+        <v>-0.2630777233819534</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.858884337769891</v>
+        <v>2.832849183499015</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.66338326765395</v>
+        <v>-4.706775191438743</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.111023577554286</v>
+        <v>1.093666808040369</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2795606269548527</v>
+        <v>-0.3229525507396455</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.808996932756702</v>
+        <v>2.782961778485826</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.576583769874942</v>
+        <v>-4.619975693659734</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.168143869988455</v>
+        <v>1.150787100474538</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2795606269548527</v>
+        <v>-0.3229525507396455</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.831397426079268</v>
+        <v>2.805362271808392</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.579053476336748</v>
+        <v>-4.62244540012154</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.167228388777145</v>
+        <v>1.149871619263228</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2820303334166588</v>
+        <v>-0.3254222572014517</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.829988003575596</v>
+        <v>2.803952849304721</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.647423662660758</v>
+        <v>-4.690815586445551</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.150887236722243</v>
+        <v>1.133530467208326</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2727546343804439</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.846560345472028</v>
+        <v>2.820525191201152</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.661211715507805</v>
+        <v>-4.704603639292597</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.135808724215316</v>
+        <v>1.118451954701399</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2727546343804439</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.836997054103919</v>
+        <v>2.810961899833043</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.69220487483651</v>
+        <v>-4.735596798621303</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9481210255242203</v>
+        <v>0.9307642560103033</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2727546343804439</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.661706619144306</v>
+        <v>2.63567146487343</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.516730615044041</v>
+        <v>-4.560122538828834</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.022877961432996</v>
+        <v>1.005521191919079</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2727546343804439</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.666273851136093</v>
+        <v>2.640238696865218</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.62766686768529</v>
+        <v>-4.671058791470083</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.954245489137703</v>
+        <v>0.9368887196237861</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2727546343804439</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.642015879897301</v>
+        <v>2.615980725626425</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.594003322213008</v>
+        <v>-4.637395245997801</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9708422925465214</v>
+        <v>0.9534855230326045</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2390910889081621</v>
+        <v>-0.2824830126929549</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.665345392400575</v>
+        <v>2.6393102381297</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.534150703009285</v>
+        <v>-4.577542626794077</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.004955726660143</v>
+        <v>0.9875989571462263</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2390910889081621</v>
+        <v>-0.2824830126929549</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.675517778832707</v>
+        <v>2.649482624561832</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.447907239982907</v>
+        <v>-4.4912991637677</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.034399382444555</v>
+        <v>1.017042612930638</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2390910889081621</v>
+        <v>-0.2824830126929549</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.670464049406568</v>
+        <v>2.644428895135692</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.493214059381887</v>
+        <v>-4.536605983166679</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.008052430129488</v>
+        <v>0.9906956606155712</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2799012519173928</v>
+        <v>-0.3232931757021857</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.637753727045555</v>
+        <v>2.611718572774679</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.522247164084188</v>
+        <v>-4.565639087868981</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9969910612816693</v>
+        <v>0.9796342917677523</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2799012519173928</v>
+        <v>-0.3232931757021857</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.638305600078656</v>
+        <v>2.612270445807781</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.429436682633328</v>
+        <v>-4.472828606418121</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9633879457533787</v>
+        <v>0.9460311762394618</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1870907704665335</v>
+        <v>-0.2304826942513263</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.623264580840538</v>
+        <v>2.597229426569662</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.473826151962756</v>
+        <v>-4.517218075747548</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9475056339462087</v>
+        <v>0.9301488644322917</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2314802397959612</v>
+        <v>-0.274872163580754</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.598504375167482</v>
+        <v>2.572469220896606</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.361154933726506</v>
+        <v>-4.404546857511298</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9876498297524317</v>
+        <v>0.9702930602385147</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.118809021559711</v>
+        <v>-0.1622009453445038</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.661182814620955</v>
+        <v>2.635147660350079</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.248777932543833</v>
+        <v>-4.292169856328625</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.038091926056168</v>
+        <v>1.020735156542251</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.118809021559711</v>
+        <v>-0.1622009453445038</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.666674110451622</v>
+        <v>2.640638956180747</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.276558330445186</v>
+        <v>-4.319950254229978</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.038476968664166</v>
+        <v>1.021120199150249</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.146589419461064</v>
+        <v>-0.1899813432458569</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.661503073479349</v>
+        <v>2.635467919208474</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.359559611470464</v>
+        <v>-4.402951535255257</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8436321762547079</v>
+        <v>0.8262754067407909</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1651603039882378</v>
+        <v>-0.2085522277730306</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.488716262763699</v>
+        <v>2.462681108492823</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.468173689913796</v>
+        <v>-4.511565613698588</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9203362055965809</v>
+        <v>0.902979436082664</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1651603039882378</v>
+        <v>-0.2085522277730306</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.608865923482904</v>
+        <v>2.582830769212028</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.432764651665653</v>
+        <v>-4.476156575450445</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9490128469981611</v>
+        <v>0.9316560774842442</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1651603039882378</v>
+        <v>-0.2085522277730306</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.623378949585227</v>
+        <v>2.597343795314351</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.394380989107502</v>
+        <v>-4.437772912892294</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9617857533637904</v>
+        <v>0.9444289838498734</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1267766414300866</v>
+        <v>-0.1701685652148794</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.643828588462486</v>
+        <v>2.617793434191611</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.217264659072335</v>
+        <v>-4.260656582857128</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.029361314223159</v>
+        <v>1.012004544709242</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1267766414300866</v>
+        <v>-0.1701685652148794</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.640557617307788</v>
+        <v>2.614522463036913</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.262356903905881</v>
+        <v>-4.305748827690674</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.012007808051653</v>
+        <v>0.9946510385377365</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1886726845994764</v>
+        <v>-0.2320646083842692</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.604103383168068</v>
+        <v>2.578068228897192</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.082981482667114</v>
+        <v>-4.126373406451906</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.077544951853575</v>
+        <v>1.060188182339658</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.03189592642875771</v>
+        <v>-0.07528785021355056</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.691956413376913</v>
+        <v>2.665921259106037</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.127995696187719</v>
+        <v>-4.171387619972512</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.040346721776922</v>
+        <v>1.022989952263005</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.06224482174336232</v>
+        <v>-0.1056367455281552</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.65455453151974</v>
+        <v>2.628519377248864</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.395000206460154</v>
+        <v>-4.438392130244947</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.939236480006894</v>
+        <v>0.921879710492977</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2566078597863109</v>
+        <v>-0.2999997835711037</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.543628271032917</v>
+        <v>2.517593116762041</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.496197987897327</v>
+        <v>-4.539589911682119</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8979612893285265</v>
+        <v>0.8806045198146095</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3250166733316301</v>
+        <v>-0.3684085971164229</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.501786904802227</v>
+        <v>2.475751750531351</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.489687021283014</v>
+        <v>-4.533078945067807</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8981656375285683</v>
+        <v>0.8808088680146513</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3250166733316301</v>
+        <v>-0.3684085971164229</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.499386866356543</v>
+        <v>2.473351712085668</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.470648893575717</v>
+        <v>-4.51404081736051</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.902305607819732</v>
+        <v>0.8849488383058151</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3832002846628246</v>
+        <v>-0.4265922084476175</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.461001418766072</v>
+        <v>2.434966264495196</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.501775524726336</v>
+        <v>-4.545167448511128</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.067436824298165</v>
+        <v>1.050080054784248</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3832002846628246</v>
+        <v>-0.4265922084476175</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.638583287704752</v>
+        <v>2.612548133433877</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.515642286060253</v>
+        <v>-4.559034209845046</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.062723448750732</v>
+        <v>1.045366679236815</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4210582013966476</v>
+        <v>-0.4644501251814404</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.616701866650592</v>
+        <v>2.590666712379716</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.470838114520324</v>
+        <v>-4.514230038305116</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.086653647763629</v>
+        <v>1.069296878249713</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4210582013966476</v>
+        <v>-0.4644501251814404</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.622710397047518</v>
+        <v>2.596675242776642</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.323095144285321</v>
+        <v>-4.366487068070113</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.224903483649652</v>
+        <v>1.207546714135735</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2532508441617644</v>
+        <v>-0.2966427679465573</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.80254745918047</v>
+        <v>2.776512304909594</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.425109826816542</v>
+        <v>-4.468501750601335</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.186891232168645</v>
+        <v>1.169534462654728</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2532508441617644</v>
+        <v>-0.2966427679465573</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.805341080711951</v>
+        <v>2.779305926441075</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.418957120763758</v>
+        <v>-4.46234904454855</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.190014662981417</v>
+        <v>1.1726578934675</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2470981381089801</v>
+        <v>-0.290490061893773</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.80969505273528</v>
+        <v>2.783659898464404</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.43576641891426</v>
+        <v>-4.479158342699052</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.182371420461326</v>
+        <v>1.16501465094741</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2639074362594818</v>
+        <v>-0.3072993600442746</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.798689950585089</v>
+        <v>2.772654796314213</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.373468420138138</v>
+        <v>-4.41686034392293</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.273626173768596</v>
+        <v>1.256269404254679</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2639074362594818</v>
+        <v>-0.3072993600442746</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.86502550438191</v>
+        <v>2.838990350111034</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.17167822247298</v>
+        <v>-4.215070146257772</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.062923125224057</v>
+        <v>1.04556635571014</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.06588924409032737</v>
+        <v>-0.1092811678751202</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.6924172920728</v>
+        <v>2.666382137801925</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.098300125384243</v>
+        <v>-4.141692049169036</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.162564596381727</v>
+        <v>1.14520782686781</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.007488852998409179</v>
+        <v>-0.03590307078638366</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.806734382648218</v>
+        <v>2.780699228377342</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.196040670009218</v>
+        <v>-4.23943259379401</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.138096114647781</v>
+        <v>1.120739345133864</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.00840042513457101</v>
+        <v>-0.05179234891936385</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.811828551884473</v>
+        <v>2.785793397613598</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.372378430132147</v>
+        <v>-4.41577035391694</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.066096991423281</v>
+        <v>1.048740221909364</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1847381852575004</v>
+        <v>-0.2281301090422932</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.704561876635387</v>
+        <v>2.678526722364512</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.29595638370022</v>
+        <v>-4.339348307485013</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.09515742803598</v>
+        <v>1.077800658522063</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1847381852575004</v>
+        <v>-0.2281301090422932</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.703053494675316</v>
+        <v>2.67701834040444</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.251583252061652</v>
+        <v>-4.294975175846444</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.112769548126844</v>
+        <v>1.095412778612927</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1403650536189318</v>
+        <v>-0.1837569774037247</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.729540241093893</v>
+        <v>2.703505086823017</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.808153067403842</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.128749031174484</v>
+        <v>-4.172140954959277</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.156297030620301</v>
+        <v>1.138940261106384</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1403650536189318</v>
+        <v>-0.1837569774037247</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.723934035232483</v>
+        <v>2.697898880961608</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.814534824431647</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.081093300613428</v>
+        <v>-4.124485224398221</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.181741079872528</v>
+        <v>1.164384310358611</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.09270932305787616</v>
+        <v>-0.136101246842669</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.758909230596921</v>
+        <v>2.732874076326045</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.819427197806371</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.980575142114674</v>
+        <v>-4.023967065899466</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.226840716646755</v>
+        <v>1.209483947132838</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.007808835440878403</v>
+        <v>-0.03558308834391444</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.824112499070899</v>
+        <v>2.798077344800023</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.806181870282244</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.041241732517063</v>
+        <v>-4.084633656301856</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.189328752961671</v>
+        <v>1.171971983447754</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.07388948127765527</v>
+        <v>-0.1172814050624481</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.761848181515651</v>
+        <v>2.735813027244775</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.810279572892872</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.996403330908665</v>
+        <v>-4.039795254693457</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.211361816215659</v>
+        <v>1.194005046701742</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.06934604833278579</v>
+        <v>-0.1127379721175786</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.768671943893201</v>
+        <v>2.742636789622325</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.81444051252395</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.097161966665664</v>
+        <v>-4.140553890450455</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.175219301543937</v>
+        <v>1.157862532030021</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1581716170597912</v>
+        <v>-0.2015635408445841</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.719537542288076</v>
+        <v>2.6935023880172</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.820320115051787</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.052959129579763</v>
+        <v>-4.096351053364555</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.198780038906135</v>
+        <v>1.181423269392218</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1139687799738908</v>
+        <v>-0.1573607037586836</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.751938847067453</v>
+        <v>2.725903692796578</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.818730115521035</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.089938157243207</v>
+        <v>-4.133330081027998</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.182398428310005</v>
+        <v>1.165041658796089</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.07699487818256023</v>
+        <v>-0.1203868019673531</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.772533188611499</v>
+        <v>2.746498034340624</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.869977880704075</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.109996236108048</v>
+        <v>-4.153388159892838</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.225622961947108</v>
+        <v>1.208266192433192</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.07699487818256023</v>
+        <v>-0.1203868019673531</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.823780953794539</v>
+        <v>2.797745799523663</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.868418585298328</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.070065562930157</v>
+        <v>-4.113457486714948</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.240035935812517</v>
+        <v>1.222679166298601</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.03706420500466989</v>
+        <v>-0.08045612878946273</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.846180062295526</v>
+        <v>2.82014490802465</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.863366813536598</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.01903347020763</v>
+        <v>-4.06242539399242</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.255397001139799</v>
+        <v>1.238040231625882</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.01396788771785806</v>
+        <v>-0.02942403606693478</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.871747546167313</v>
+        <v>2.845712391896437</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.880554217629303</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.953809289080424</v>
+        <v>-3.997201212865215</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.298674077683386</v>
+        <v>1.28131730816947</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.07919206884506369</v>
+        <v>0.03580014506027085</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.928069458936341</v>
+        <v>2.902034304665465</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.876515189928583</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.91638226900929</v>
+        <v>-3.959774192794081</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.30960585801112</v>
+        <v>1.292249088497203</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.08444360687424535</v>
+        <v>0.04105168308945251</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.92718135405313</v>
+        <v>2.901146199782255</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.877771982259823</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.936493925043999</v>
+        <v>-3.979885848828789</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.302817987928476</v>
+        <v>1.28546121841456</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.09547095187166454</v>
+        <v>0.0520790280868717</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.935054553382822</v>
+        <v>2.909019399111947</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.038329753281034</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.882749110616794</v>
+        <v>-3.926141034401585</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.484873684720569</v>
+        <v>1.467516915206653</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.1055342613121265</v>
+        <v>0.06214233752733367</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.10165031006831</v>
+        <v>3.075615155797434</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.158442662498851</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.858957542010652</v>
+        <v>-3.902349465795442</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.614503221380843</v>
+        <v>1.597146451866927</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.1293258299182688</v>
+        <v>0.08593390613347596</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.236038160449813</v>
+        <v>3.210003006178937</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15015063851271</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.832873457746844</v>
+        <v>-3.876265381531634</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.616644831100225</v>
+        <v>1.599288061586309</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.1293258299182688</v>
+        <v>0.08593390613347596</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.227746136463672</v>
+        <v>3.201710982192796</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.14834383409649</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.754742276897897</v>
+        <v>-3.798134200682687</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.646090499023584</v>
+        <v>1.628733729509668</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2035026408019533</v>
+        <v>0.1601107170171605</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.270445418577662</v>
+        <v>3.244410264306786</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.165898239823281</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.745849815504614</v>
+        <v>-3.789241739289404</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.667201889307688</v>
+        <v>1.649845119793772</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2035026408019533</v>
+        <v>0.1601107170171605</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.287999824304453</v>
+        <v>3.261964670033578</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.157753287227865</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.914325932474492</v>
+        <v>-3.957717856259282</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.591666489924321</v>
+        <v>1.574309720410405</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1755548050853726</v>
+        <v>0.1321628813005797</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.263086170279089</v>
+        <v>3.237051016008213</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.139022984415727</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.216526403612908</v>
+        <v>-3.259918327397699</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.852055998656816</v>
+        <v>1.8346992291429</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1052067457149619</v>
+        <v>0.06181482193016902</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.202147031844704</v>
+        <v>3.176111877573828</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.129687006912631</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.193805299929756</v>
+        <v>-3.237197223714547</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.851808462626982</v>
+        <v>1.834451693113066</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1052067457149619</v>
+        <v>0.06181482193016902</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.192811054341609</v>
+        <v>3.166775900070733</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.2885931327638</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.192080256639712</v>
+        <v>-3.235472180424503</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.011404605794168</v>
+        <v>1.994047836280252</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.1069317890050056</v>
+        <v>0.06353986522021277</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.352752206166804</v>
+        <v>3.326717051895928</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.325670955257447</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.346861263417967</v>
+        <v>-3.390253187202758</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.986570025576513</v>
+        <v>1.969213256062597</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.0735641149505295</v>
+        <v>0.03017219116573666</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.369809424227765</v>
+        <v>3.34377426995689</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.322346311246992</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.295425930033308</v>
+        <v>-3.338817853818098</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.003819514919922</v>
+        <v>1.986462745406006</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.1249994483351892</v>
+        <v>0.08160752455039633</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.397345980248106</v>
+        <v>3.37131082597723</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.332352464891734</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.26847470570682</v>
+        <v>-3.31186662949161</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.024606158295259</v>
+        <v>2.007249388781343</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.1398797943629083</v>
+        <v>0.09648787057811548</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.416280341509479</v>
+        <v>3.390245187238603</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.516455597036694</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.404427713763136</v>
+        <v>-3.447819637547926</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.154328087217692</v>
+        <v>2.136971317703776</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.1398797943629083</v>
+        <v>0.09648787057811548</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.600383473654439</v>
+        <v>3.574348319383563</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.508572291939687</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.426835831568008</v>
+        <v>-3.470227755352798</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.137481534998736</v>
+        <v>2.12012476548482</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.1398797943629083</v>
+        <v>0.09648787057811548</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.592500168557432</v>
+        <v>3.566465014286556</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.510626291489324</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.574841599047407</v>
+        <v>-3.618233522832198</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.080333227556614</v>
+        <v>2.062976458042697</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.05315278549936686</v>
+        <v>0.009760861714574021</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.542517962788944</v>
+        <v>3.516482808518069</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.566880009211171</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.521587350072851</v>
+        <v>-3.596666835504645</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.157888644868283</v>
+        <v>2.127856850695566</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.08300566814417887</v>
+        <v>0.02227172600557981</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.616683410097679</v>
+        <v>3.580243044814519</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.569771103756472</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.520300586533295</v>
+        <v>-3.595380071965089</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.161294444829407</v>
+        <v>2.131262650656689</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.08429243168373546</v>
+        <v>0.0235584895451364</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.620346562766714</v>
+        <v>3.583906197483554</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.567882916650247</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.521857640522586</v>
+        <v>-3.59693712595438</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.158783436127465</v>
+        <v>2.128751641954748</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.08429243168373546</v>
+        <v>0.0235584895451364</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.618458375660489</v>
+        <v>3.582018010377329</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.56270314625311</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.52912952604605</v>
+        <v>-3.604209011477844</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.150694911520942</v>
+        <v>2.120663117348224</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.07702054616027071</v>
+        <v>0.01628660402167165</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.608915473949272</v>
+        <v>3.572475108666113</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.561137156463262</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.527288506987799</v>
+        <v>-3.602367992419593</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.149865329354395</v>
+        <v>2.119833535181677</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.07828877283173913</v>
+        <v>0.01755483069314007</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.608110420162306</v>
+        <v>3.571670054879146</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.574210563329181</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.53419721248748</v>
+        <v>-3.609276697919274</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.160175254020441</v>
+        <v>2.130143459847724</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.07828877283173913</v>
+        <v>0.01755483069314007</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.621183827028224</v>
+        <v>3.584743461745065</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.574210563329181</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.53575885530234</v>
+        <v>-3.610838340734134</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.159550596894498</v>
+        <v>2.12951880272178</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.07828877283173913</v>
+        <v>0.01755483069314007</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.621183827028224</v>
+        <v>3.584743461745065</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.572734604456183</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.563659642411813</v>
+        <v>-3.638739127843607</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.14691432317771</v>
+        <v>2.116882529004993</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.04369184868880432</v>
+        <v>-0.01704209344979474</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.598949713669465</v>
+        <v>3.562509348386306</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.569499048433381</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.566692639924486</v>
+        <v>-3.64177212535628</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.14246556814984</v>
+        <v>2.112433773977122</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.04065885117613044</v>
+        <v>-0.02007509096246862</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.59389435913906</v>
+        <v>3.5574539938559</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,13 +47896,13 @@
         <v>3.568972619008902</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.566692639924486</v>
+        <v>-3.64177212535628</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.14246556814984</v>
+        <v>2.112433773977122</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.04065885117613044</v>
+        <v>-0.02007509096246862</v>
       </c>
       <c r="G2015" t="n">
         <v>3.56203641599527</v>

--- a/tame_output/ON/bt/strategyON_20240704.xlsx
+++ b/tame_output/ON/bt/strategyON_20240704.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>53.4%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>46.1%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.2%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.6%</t>
+          <t>-49.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.1%</t>
+          <t>-68.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.1%</t>
+          <t>453.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-525.7%</t>
+          <t>-532.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.3%</t>
+          <t>-37.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-40.7%</t>
+          <t>-30.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-165.0%</t>
+          <t>-166.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-180.5%</t>
+          <t>-208.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-226.0%</t>
+          <t>-232.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-89.8%</t>
+          <t>-93.4%</t>
         </is>
       </c>
     </row>
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.35855398758469</v>
+        <v>-10.26352495425213</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9829398060425754</v>
+        <v>-0.9449281927095492</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.616586702614181</v>
+        <v>-2.521557669281616</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.59088619173654</v>
+        <v>1.647903611736079</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.41134014318502</v>
+        <v>-10.31631110985245</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.00293847844415</v>
+        <v>-0.9649268651111234</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.712262189196578</v>
+        <v>-2.617233155864013</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.534596689625658</v>
+        <v>1.591614109625198</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.53737693655331</v>
+        <v>-10.44234790322074</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.050659467162351</v>
+        <v>-1.012647853829324</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.687010566386836</v>
+        <v>-2.591981533054271</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.552441391940618</v>
+        <v>1.609458811940158</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.48536142258449</v>
+        <v>-10.39033238925193</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.025862925888425</v>
+        <v>-0.9878513125553985</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.687010566386836</v>
+        <v>-2.591981533054271</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.556431727627019</v>
+        <v>1.613449147626558</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.62703326430861</v>
+        <v>-10.53200423097605</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.084006889476814</v>
+        <v>-1.045995276143788</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.687010566386836</v>
+        <v>-2.591981533054271</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.554956500728278</v>
+        <v>1.611973920727817</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.57744241988378</v>
+        <v>-10.48241338655122</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.049117141542009</v>
+        <v>-1.011105528208982</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.637419721962002</v>
+        <v>-2.542390688629437</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.59976441754805</v>
+        <v>1.656781837547589</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.56463502687901</v>
+        <v>-10.46960599354644</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.057045317986782</v>
+        <v>-1.019033704653756</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.686275496970903</v>
+        <v>-2.591246463638338</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.557399818896027</v>
+        <v>1.614417238895566</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.33878987415959</v>
+        <v>-10.24376084082703</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9571281838628081</v>
+        <v>-0.9191165705297819</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.64434882138374</v>
+        <v>-2.549319788051174</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.592134897284533</v>
+        <v>1.649152317284073</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.214211217822</v>
+        <v>-10.11918218448944</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9061575767717129</v>
+        <v>-0.8681459634386868</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.64434882138374</v>
+        <v>-2.549319788051174</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.593274041840592</v>
+        <v>1.650291461840131</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.26710650586629</v>
+        <v>-10.17207747253372</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9246819178273196</v>
+        <v>-0.8866703044942934</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.639393475295293</v>
+        <v>-2.544364441962728</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.598881023655768</v>
+        <v>1.655898443655307</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.19497333057841</v>
+        <v>-10.09994429724584</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8900949434735308</v>
+        <v>-0.8520833301405046</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.639393475295293</v>
+        <v>-2.544364441962728</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.604614727894404</v>
+        <v>1.661632147893943</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.12360693796876</v>
+        <v>-10.0285779046362</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8712856488235374</v>
+        <v>-0.8332740354905113</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.568027082685645</v>
+        <v>-2.47299804935308</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.637697301066328</v>
+        <v>1.694714721065867</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.03014790398354</v>
+        <v>-9.935118870650971</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8437855165423547</v>
+        <v>-0.8057739032093285</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.568027082685645</v>
+        <v>-2.47299804935308</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.62781381975342</v>
+        <v>1.684831239752959</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.762906103115139</v>
+        <v>-9.667877069782573</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7387233566943694</v>
+        <v>-0.7007117433613432</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.568027082685645</v>
+        <v>-2.47299804935308</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.625979259254047</v>
+        <v>1.682996679253586</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.664999064438648</v>
+        <v>-9.569970031106083</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6998608561972341</v>
+        <v>-0.661849242864208</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.500041332825089</v>
+        <v>-2.405012299492523</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.66647039419692</v>
+        <v>1.723487814196459</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.64104552346269</v>
+        <v>-9.546016490130125</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6896109336613572</v>
+        <v>-0.651599320328331</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.476087791849131</v>
+        <v>-2.381058758516566</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.681511024927988</v>
+        <v>1.738528444927527</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.376985585139893</v>
+        <v>-9.281956551807328</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5972472744939905</v>
+        <v>-0.5592356611609643</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.212027853526335</v>
+        <v>-2.11699882019377</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.826686671759913</v>
+        <v>1.883704091759452</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.669905961635056</v>
+        <v>-8.574876928302491</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3172024587523565</v>
+        <v>-0.2791908454193304</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.212027853526335</v>
+        <v>-2.11699882019377</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.823899638099612</v>
+        <v>1.880917058099151</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.629721663268866</v>
+        <v>-8.5346926299363</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.300785115518039</v>
+        <v>-0.2627735021850128</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.171843555160144</v>
+        <v>-2.076814521827579</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.848353841007168</v>
+        <v>1.905371261006707</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.466321792329502</v>
+        <v>-8.371292758996937</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2360583459215366</v>
+        <v>-0.1980467325885105</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.008443684220782</v>
+        <v>-1.913414650888217</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.945760584791542</v>
+        <v>2.002778004791081</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.232840570099903</v>
+        <v>-8.137811536767337</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1347414281918446</v>
+        <v>-0.09672981485881849</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.774962461991183</v>
+        <v>-1.679933428658618</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.093773746967154</v>
+        <v>2.150791166966693</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.083174179092389</v>
+        <v>-7.988145145759822</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07776708210179795</v>
+        <v>-0.03975546876877178</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.682058970748648</v>
+        <v>-1.587029937416082</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.146623631399716</v>
+        <v>2.203641051399256</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.950898705461502</v>
+        <v>-7.855869672128936</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.02948940590241644</v>
+        <v>0.008522207430610163</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.549783497117761</v>
+        <v>-1.454754463785195</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.221356402325275</v>
+        <v>2.278373822324815</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.79516037290176</v>
+        <v>-7.700131339569194</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.03562098780911693</v>
+        <v>0.07363260114214354</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.394045164558019</v>
+        <v>-1.299016131225454</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.317614462548757</v>
+        <v>2.374631882548296</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.546160574218179</v>
+        <v>-7.451131540885613</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1481272485062082</v>
+        <v>0.1861388618392348</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.394045164558019</v>
+        <v>-1.299016131225454</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.330520803772416</v>
+        <v>2.387538223771955</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.651750563991284</v>
+        <v>-7.556721530658717</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.02208467700225247</v>
+        <v>0.01592693633077413</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.499635154331124</v>
+        <v>-1.404606120998558</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.139190880309334</v>
+        <v>2.196208300308874</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.670485466109881</v>
+        <v>-7.575456432777314</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.01896570402739517</v>
+        <v>0.05697731736042178</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.505231163991255</v>
+        <v>-1.41020213065869</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.184377616390342</v>
+        <v>2.241395036389881</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.522545424702281</v>
+        <v>-7.427516391369715</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.04173720209773268</v>
+        <v>-0.003725588764706078</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.484910248082697</v>
+        <v>-1.389881214750132</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.076691243247309</v>
+        <v>2.133708663246848</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.469575902448293</v>
+        <v>-7.374546869115727</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.02926337944961555</v>
+        <v>0.008748233883411061</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.431940725828709</v>
+        <v>-1.336911692496143</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.099758970346224</v>
+        <v>2.156776390345764</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.426027495677602</v>
+        <v>-7.330998462345036</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.01880462883643252</v>
+        <v>0.01920698449659408</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.431940725828709</v>
+        <v>-1.336911692496143</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.092798358251131</v>
+        <v>2.14981577825067</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.183879102223744</v>
+        <v>-7.088850068891178</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.09251708292625382</v>
+        <v>0.1305286962592804</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.431940725828709</v>
+        <v>-1.336911692496143</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.107260712632274</v>
+        <v>2.164278132631813</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.075619965101223</v>
+        <v>-6.980590931768656</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1303528582344575</v>
+        <v>0.1683644715674841</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.431940725828709</v>
+        <v>-1.336911692496143</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.101792833091469</v>
+        <v>2.158810253091008</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.952328830284092</v>
+        <v>-6.857299796951525</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1771674061718866</v>
+        <v>0.2151790195049132</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.308649591011578</v>
+        <v>-1.213620557679013</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.173265607992324</v>
+        <v>2.230283027991864</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.931179631380648</v>
+        <v>-6.836150598048082</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1933280639705894</v>
+        <v>0.231339677303616</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.287500392108135</v>
+        <v>-1.19247135877557</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.193656105571716</v>
+        <v>2.250673525571255</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.687414189397204</v>
+        <v>-6.592385156064638</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2866149491110179</v>
+        <v>0.3246265624440441</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.287500392108135</v>
+        <v>-1.19247135877557</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.189436813918766</v>
+        <v>2.246454233918305</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.585651369119909</v>
+        <v>-6.490622335787343</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3294443911419518</v>
+        <v>0.3674560044749784</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.274281323715706</v>
+        <v>-1.179252290383141</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.199492568874239</v>
+        <v>2.256509988873779</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.335800975170835</v>
+        <v>-6.240771941838268</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4221266237052839</v>
+        <v>0.46013823703831</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.274281323715706</v>
+        <v>-1.179252290383141</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.192234643857941</v>
+        <v>2.24925206385748</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.159908882703402</v>
+        <v>-6.064879849370836</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4960825842129055</v>
+        <v>0.5340941975459317</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.274281323715706</v>
+        <v>-1.179252290383141</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.19583376737859</v>
+        <v>2.25285118737813</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.988462419680938</v>
+        <v>-5.893433386348373</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5779886754764449</v>
+        <v>0.6160002888094711</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.102834860693243</v>
+        <v>-1.007805827360678</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.312029151246622</v>
+        <v>2.369046571246161</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.914172853942599</v>
+        <v>-5.819143820610034</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6067249793880776</v>
+        <v>0.6447365927211037</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.028545294954904</v>
+        <v>-0.9335162616223384</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.355623368305922</v>
+        <v>2.412640788305461</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.850537111708665</v>
+        <v>-5.755508078376099</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6368740773359685</v>
+        <v>0.6748856906689946</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9649095527209691</v>
+        <v>-0.8698805193884038</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.3984996147006</v>
+        <v>2.45551703470014</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.739110352382744</v>
+        <v>-5.644081319050179</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6626390398501321</v>
+        <v>0.7006506531831582</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9649095527209691</v>
+        <v>-0.8698805193884038</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.379693873484396</v>
+        <v>2.436711293483935</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.498679855577884</v>
+        <v>-5.403650822245319</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7605543151969538</v>
+        <v>0.79856592852998</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7244790559161088</v>
+        <v>-0.6294500225835435</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.52569524819219</v>
+        <v>2.582712668191729</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.42643728740669</v>
+        <v>-5.331408254074124</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7933806563002519</v>
+        <v>0.8313922696332781</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7244790559161088</v>
+        <v>-0.6294500225835435</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.52962456202701</v>
+        <v>2.586641982026549</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.373438965125302</v>
+        <v>-5.278409931792736</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.815258569130147</v>
+        <v>0.8532701824631732</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.66914279691417</v>
+        <v>-0.5741137635816047</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.563504901345513</v>
+        <v>2.620522321345052</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.264634079645575</v>
+        <v>-5.169605046313009</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8557785945420311</v>
+        <v>0.8937902078750573</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.66914279691417</v>
+        <v>-0.5741137635816047</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.560502972565506</v>
+        <v>2.617520392565046</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.044613281608564</v>
+        <v>-4.949584248275999</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9453659507674494</v>
+        <v>0.9833775641004756</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5279229518461898</v>
+        <v>-0.4328939185136245</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.646813916616909</v>
+        <v>2.703831336616448</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.911745592545286</v>
+        <v>-4.816716559212721</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.014407209194584</v>
+        <v>1.05241882252761</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5279229518461898</v>
+        <v>-0.4328939185136245</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.662708099418732</v>
+        <v>2.719725519418271</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.791572509180788</v>
+        <v>-4.696543475848222</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.063622286980685</v>
+        <v>1.101633900313711</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4077498684816908</v>
+        <v>-0.3127208351491255</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.735957793877733</v>
+        <v>2.792975213877273</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.64690036408105</v>
+        <v>-4.551871330748485</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.13157924758202</v>
+        <v>1.169590860915046</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2630777233819534</v>
+        <v>-0.1680486900493881</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.832849183499015</v>
+        <v>2.889866603498555</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.706775191438743</v>
+        <v>-4.611746158106177</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.093666808040369</v>
+        <v>1.131678421373395</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3229525507396455</v>
+        <v>-0.2279235174070802</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.782961778485826</v>
+        <v>2.839979198485366</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.619975693659734</v>
+        <v>-4.524946660327169</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.150787100474538</v>
+        <v>1.188798713807565</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3229525507396455</v>
+        <v>-0.2279235174070802</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.805362271808392</v>
+        <v>2.862379691807932</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.62244540012154</v>
+        <v>-4.527416366788975</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.149871619263228</v>
+        <v>1.187883232596254</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3254222572014517</v>
+        <v>-0.2303932238688864</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.803952849304721</v>
+        <v>2.86097026930426</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.690815586445551</v>
+        <v>-4.595786553112985</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.133530467208326</v>
+        <v>1.171542080541352</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.2211175248326714</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.820525191201152</v>
+        <v>2.877542611200691</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.704603639292597</v>
+        <v>-4.609574605960032</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.118451954701399</v>
+        <v>1.156463568034425</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.2211175248326714</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.810961899833043</v>
+        <v>2.867979319832582</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.735596798621303</v>
+        <v>-4.640567765288737</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9307642560103033</v>
+        <v>0.9687758693433295</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.2211175248326714</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.63567146487343</v>
+        <v>2.692688884872969</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.560122538828834</v>
+        <v>-4.465093505496268</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.005521191919079</v>
+        <v>1.043532805252105</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.2211175248326714</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.640238696865218</v>
+        <v>2.697256116864757</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.671058791470083</v>
+        <v>-4.576029758137517</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9368887196237861</v>
+        <v>0.9749003329568122</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.2211175248326714</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.615980725626425</v>
+        <v>2.672998145625964</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.637395245997801</v>
+        <v>-4.542366212665235</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9534855230326045</v>
+        <v>0.9914971363656306</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2824830126929549</v>
+        <v>-0.1874539793603896</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.6393102381297</v>
+        <v>2.696327658129238</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.577542626794077</v>
+        <v>-4.482513593461512</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9875989571462263</v>
+        <v>1.025610570479252</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2824830126929549</v>
+        <v>-0.1874539793603896</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.649482624561832</v>
+        <v>2.706500044561371</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.4912991637677</v>
+        <v>-4.396270130435134</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.017042612930638</v>
+        <v>1.055054226263664</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2824830126929549</v>
+        <v>-0.1874539793603896</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.644428895135692</v>
+        <v>2.701446315135231</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.536605983166679</v>
+        <v>-4.441576949834114</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9906956606155712</v>
+        <v>1.028707273948597</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3232931757021857</v>
+        <v>-0.2282641423696204</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.611718572774679</v>
+        <v>2.668735992774218</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.565639087868981</v>
+        <v>-4.470610054536415</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9796342917677523</v>
+        <v>1.017645905100778</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3232931757021857</v>
+        <v>-0.2282641423696204</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.612270445807781</v>
+        <v>2.66928786580732</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.472828606418121</v>
+        <v>-4.377799573085555</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9460311762394618</v>
+        <v>0.9840427895724879</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2304826942513263</v>
+        <v>-0.135453660918761</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.597229426569662</v>
+        <v>2.654246846569201</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.517218075747548</v>
+        <v>-4.422189042414983</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9301488644322917</v>
+        <v>0.9681604777653179</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.274872163580754</v>
+        <v>-0.1798431302481887</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.572469220896606</v>
+        <v>2.629486640896145</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.404546857511298</v>
+        <v>-4.309517824178733</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9702930602385147</v>
+        <v>1.008304673571541</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1622009453445038</v>
+        <v>-0.06717191201193851</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.635147660350079</v>
+        <v>2.692165080349618</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.292169856328625</v>
+        <v>-4.19714082299606</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.020735156542251</v>
+        <v>1.058746769875277</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1622009453445038</v>
+        <v>-0.06717191201193851</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.640638956180747</v>
+        <v>2.697656376180285</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.319950254229978</v>
+        <v>-4.224921220897413</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.021120199150249</v>
+        <v>1.059131812483275</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1899813432458569</v>
+        <v>-0.09495230991329157</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.635467919208474</v>
+        <v>2.692485339208013</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.402951535255257</v>
+        <v>-4.307922501922691</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8262754067407909</v>
+        <v>0.8642870200738171</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2085522277730306</v>
+        <v>-0.1135231944404653</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.462681108492823</v>
+        <v>2.519698528492362</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.511565613698588</v>
+        <v>-4.416536580366023</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.902979436082664</v>
+        <v>0.9409910494156901</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2085522277730306</v>
+        <v>-0.1135231944404653</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.582830769212028</v>
+        <v>2.639848189211567</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.476156575450445</v>
+        <v>-4.38112754211788</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9316560774842442</v>
+        <v>0.9696676908172703</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2085522277730306</v>
+        <v>-0.1135231944404653</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.597343795314351</v>
+        <v>2.65436121531389</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.437772912892294</v>
+        <v>-4.342743879559729</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9444289838498734</v>
+        <v>0.9824405971828996</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1701685652148794</v>
+        <v>-0.07513953188231415</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.617793434191611</v>
+        <v>2.67481085419115</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.260656582857128</v>
+        <v>-4.165627549524562</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.012004544709242</v>
+        <v>1.050016158042268</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1701685652148794</v>
+        <v>-0.07513953188231415</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.614522463036913</v>
+        <v>2.671539883036452</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.305748827690674</v>
+        <v>-4.210719794358108</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9946510385377365</v>
+        <v>1.032662651870763</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2320646083842692</v>
+        <v>-0.1370355750517039</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.578068228897192</v>
+        <v>2.635085648896731</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.126373406451906</v>
+        <v>-4.031344373119341</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.060188182339658</v>
+        <v>1.098199795672684</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.07528785021355056</v>
+        <v>0.01974118311901474</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.665921259106037</v>
+        <v>2.722938679105577</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.171387619972512</v>
+        <v>-4.076358586639946</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.022989952263005</v>
+        <v>1.061001565596031</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1056367455281552</v>
+        <v>-0.01060771219558987</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.628519377248864</v>
+        <v>2.685536797248404</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.438392130244947</v>
+        <v>-4.343363096912381</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.921879710492977</v>
+        <v>0.9598913238260032</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2999997835711037</v>
+        <v>-0.2049707502385384</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.517593116762041</v>
+        <v>2.57461053676158</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.539589911682119</v>
+        <v>-4.444560878349554</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8806045198146095</v>
+        <v>0.9186161331476357</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3684085971164229</v>
+        <v>-0.2733795637838576</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.475751750531351</v>
+        <v>2.53276917053089</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.533078945067807</v>
+        <v>-4.438049911735241</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8808088680146513</v>
+        <v>0.9188204813476775</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3684085971164229</v>
+        <v>-0.2733795637838576</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.473351712085668</v>
+        <v>2.530369132085207</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.51404081736051</v>
+        <v>-4.419011784027944</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8849488383058151</v>
+        <v>0.9229604516388412</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4265922084476175</v>
+        <v>-0.3315631751150522</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.434966264495196</v>
+        <v>2.491983684494735</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.545167448511128</v>
+        <v>-4.450138415178563</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.050080054784248</v>
+        <v>1.088091668117274</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4265922084476175</v>
+        <v>-0.3315631751150522</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.612548133433877</v>
+        <v>2.669565553433416</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.559034209845046</v>
+        <v>-4.46400517651248</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.045366679236815</v>
+        <v>1.083378292569841</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4644501251814404</v>
+        <v>-0.3694210918488751</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.590666712379716</v>
+        <v>2.647684132379255</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.514230038305116</v>
+        <v>-4.419201004972551</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.069296878249713</v>
+        <v>1.107308491582739</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4644501251814404</v>
+        <v>-0.3694210918488751</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.596675242776642</v>
+        <v>2.653692662776181</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.366487068070113</v>
+        <v>-4.271458034737548</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.207546714135735</v>
+        <v>1.245558327468762</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2966427679465573</v>
+        <v>-0.201613734613992</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.776512304909594</v>
+        <v>2.833529724909133</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.468501750601335</v>
+        <v>-4.373472717268769</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.169534462654728</v>
+        <v>1.207546075987754</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2966427679465573</v>
+        <v>-0.201613734613992</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.779305926441075</v>
+        <v>2.836323346440614</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.46234904454855</v>
+        <v>-4.367320011215985</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.1726578934675</v>
+        <v>1.210669506800526</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.290490061893773</v>
+        <v>-0.1954610285612077</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.783659898464404</v>
+        <v>2.840677318463943</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.479158342699052</v>
+        <v>-4.384129309366487</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.16501465094741</v>
+        <v>1.203026264280436</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3072993600442746</v>
+        <v>-0.2122703267117093</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.772654796314213</v>
+        <v>2.829672216313752</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.41686034392293</v>
+        <v>-4.321831310590365</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.256269404254679</v>
+        <v>1.294281017587706</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3072993600442746</v>
+        <v>-0.2122703267117093</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.838990350111034</v>
+        <v>2.896007770110573</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.215070146257772</v>
+        <v>-4.120041112925207</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.04556635571014</v>
+        <v>1.083577969043167</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1092811678751202</v>
+        <v>-0.01425213454255492</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.666382137801925</v>
+        <v>2.723399557801464</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.141692049169036</v>
+        <v>-4.04666301583647</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.14520782686781</v>
+        <v>1.183219440200836</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.03590307078638366</v>
+        <v>0.05912596254618163</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.780699228377342</v>
+        <v>2.837716648376881</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.23943259379401</v>
+        <v>-4.144403560461445</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.120739345133864</v>
+        <v>1.15875095846689</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.05179234891936385</v>
+        <v>0.04323668441320144</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.785793397613598</v>
+        <v>2.842810817613136</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.41577035391694</v>
+        <v>-4.320741320584374</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.048740221909364</v>
+        <v>1.08675183524239</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2281301090422932</v>
+        <v>-0.133101075709728</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.678526722364512</v>
+        <v>2.735544142364051</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.339348307485013</v>
+        <v>-4.244319274152447</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.077800658522063</v>
+        <v>1.11581227185509</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2281301090422932</v>
+        <v>-0.133101075709728</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.67701834040444</v>
+        <v>2.734035760403979</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.294975175846444</v>
+        <v>-4.199946142513879</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.095412778612927</v>
+        <v>1.133424391945953</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1837569774037247</v>
+        <v>-0.08872794407115936</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.703505086823017</v>
+        <v>2.760522506822556</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.808153067403842</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.172140954959277</v>
+        <v>-4.077111921626711</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.138940261106384</v>
+        <v>1.176951874439411</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1837569774037247</v>
+        <v>-0.08872794407115936</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.697898880961608</v>
+        <v>2.754916300961147</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.814534824431647</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.124485224398221</v>
+        <v>-4.029456191065655</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.164384310358611</v>
+        <v>1.202395923691637</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.136101246842669</v>
+        <v>-0.04107221351010371</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.732874076326045</v>
+        <v>2.789891496325585</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.819427197806371</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.023967065899466</v>
+        <v>-3.928938032566901</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.209483947132838</v>
+        <v>1.247495560465864</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.03558308834391444</v>
+        <v>0.05944594498865086</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.798077344800023</v>
+        <v>2.855094764799562</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.806181870282244</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.084633656301856</v>
+        <v>-3.98960462296929</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.171971983447754</v>
+        <v>1.20998359678078</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1172814050624481</v>
+        <v>-0.02225237172988281</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.735813027244775</v>
+        <v>2.792830447244314</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.810279572892872</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.039795254693457</v>
+        <v>-3.944766221360892</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.194005046701742</v>
+        <v>1.232016660034768</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1127379721175786</v>
+        <v>-0.01770893878501334</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.742636789622325</v>
+        <v>2.799654209621865</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.81444051252395</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.140553890450455</v>
+        <v>-4.04552485711789</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.157862532030021</v>
+        <v>1.195874145363047</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2015635408445841</v>
+        <v>-0.1065345075120188</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.6935023880172</v>
+        <v>2.750519808016739</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.820320115051787</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.096351053364555</v>
+        <v>-4.001322020031989</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.181423269392218</v>
+        <v>1.219434882725244</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1573607037586836</v>
+        <v>-0.06233167042611831</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.725903692796578</v>
+        <v>2.782921112796116</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.818730115521035</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.133330081027998</v>
+        <v>-4.038301047695432</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.165041658796089</v>
+        <v>1.203053272129115</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1203868019673531</v>
+        <v>-0.02535776863478778</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.746498034340624</v>
+        <v>2.803515454340162</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.869977880704075</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.153388159892838</v>
+        <v>-4.058359126560273</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.208266192433192</v>
+        <v>1.246277805766218</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1203868019673531</v>
+        <v>-0.02535776863478778</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.797745799523663</v>
+        <v>2.854763219523202</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.868418585298328</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.113457486714948</v>
+        <v>-4.018428453382382</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.222679166298601</v>
+        <v>1.260690779631628</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.08045612878946273</v>
+        <v>0.01457290454310256</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.82014490802465</v>
+        <v>2.877162328024189</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.863366813536598</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.06242539399242</v>
+        <v>-3.967396360659854</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.238040231625882</v>
+        <v>1.276051844958909</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.02942403606693478</v>
+        <v>0.06560499726563052</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.845712391896437</v>
+        <v>2.902729811895976</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.880554217629303</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.997201212865215</v>
+        <v>-3.902172179532648</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.28131730816947</v>
+        <v>1.319328921502496</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.03580014506027085</v>
+        <v>0.1308291783928361</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.902034304665465</v>
+        <v>2.959051724665005</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.876515189928583</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.959774192794081</v>
+        <v>-3.864745159461515</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.292249088497203</v>
+        <v>1.33026070183023</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.04105168308945251</v>
+        <v>0.1360807164220178</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.901146199782255</v>
+        <v>2.958163619781794</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.877771982259823</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.979885848828789</v>
+        <v>-3.884856815496223</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.28546121841456</v>
+        <v>1.323472831747587</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.0520790280868717</v>
+        <v>0.147108061419437</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.909019399111947</v>
+        <v>2.966036819111486</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.038329753281034</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.926141034401585</v>
+        <v>-3.831112001069018</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.467516915206653</v>
+        <v>1.50552852853968</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.06214233752733367</v>
+        <v>0.157171370859899</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.075615155797434</v>
+        <v>3.132632575796974</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.158442662498851</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.902349465795442</v>
+        <v>-3.807320432462876</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.597146451866927</v>
+        <v>1.635158065199954</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.08593390613347596</v>
+        <v>0.1809629394660413</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.210003006178937</v>
+        <v>3.267020426178476</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15015063851271</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.876265381531634</v>
+        <v>-3.781236348199068</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.599288061586309</v>
+        <v>1.637299674919336</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.08593390613347596</v>
+        <v>0.1809629394660413</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.201710982192796</v>
+        <v>3.258728402192335</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.14834383409649</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.798134200682687</v>
+        <v>-3.703105167350121</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.628733729509668</v>
+        <v>1.666745342842694</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1601107170171605</v>
+        <v>0.2551397503497258</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.244410264306786</v>
+        <v>3.301427684306325</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959866</v>
+        <v>3.796264143959865</v>
       </c>
       <c r="C1995" t="n">
         <v>3.165898239823281</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.789241739289404</v>
+        <v>-3.694212705956838</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.649845119793772</v>
+        <v>1.687856733126799</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1601107170171605</v>
+        <v>0.2551397503497258</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.261964670033578</v>
+        <v>3.318982090033117</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945376</v>
+        <v>3.794424941945374</v>
       </c>
       <c r="C1996" t="n">
         <v>3.157753287227865</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.957717856259282</v>
+        <v>-3.862688822926716</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.574309720410405</v>
+        <v>1.612321333743431</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1321628813005797</v>
+        <v>0.227191914633145</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.237051016008213</v>
+        <v>3.294068436007752</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782718</v>
+        <v>3.795574066782716</v>
       </c>
       <c r="C1997" t="n">
         <v>3.139022984415727</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.259918327397699</v>
+        <v>-3.164889294065133</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.8346992291429</v>
+        <v>1.872710842475926</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.06181482193016902</v>
+        <v>0.1568438552627343</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.176111877573828</v>
+        <v>3.233129297573368</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632648</v>
+        <v>3.784671345632646</v>
       </c>
       <c r="C1998" t="n">
         <v>3.129687006912631</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.237197223714547</v>
+        <v>-3.14216819038198</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.834451693113066</v>
+        <v>1.872463306446092</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.06181482193016902</v>
+        <v>0.1568438552627343</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.166775900070733</v>
+        <v>3.223793320070272</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777686</v>
+        <v>3.783205696777684</v>
       </c>
       <c r="C1999" t="n">
         <v>3.2885931327638</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.235472180424503</v>
+        <v>-3.140443147091936</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.994047836280252</v>
+        <v>2.032059449613278</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.06353986522021277</v>
+        <v>0.1585688985527781</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.326717051895928</v>
+        <v>3.383734471895468</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644424</v>
+        <v>3.779933725644423</v>
       </c>
       <c r="C2000" t="n">
         <v>3.325670955257447</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.390253187202758</v>
+        <v>-3.295224153870191</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.969213256062597</v>
+        <v>2.007224869395623</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.03017219116573666</v>
+        <v>0.125201224498302</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.34377426995689</v>
+        <v>3.400791689956428</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799972</v>
+        <v>3.76944361979997</v>
       </c>
       <c r="C2001" t="n">
         <v>3.322346311246992</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.338817853818098</v>
+        <v>-3.243788820485532</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.986462745406006</v>
+        <v>2.024474358739032</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.08160752455039633</v>
+        <v>0.1766365578829616</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.37131082597723</v>
+        <v>3.428328245976769</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331127</v>
+        <v>3.766673496331125</v>
       </c>
       <c r="C2002" t="n">
         <v>3.332352464891734</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.31186662949161</v>
+        <v>-3.216837596159044</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.007249388781343</v>
+        <v>2.045261002114369</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.09648787057811548</v>
+        <v>0.1915169039106808</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.390245187238603</v>
+        <v>3.447262607238142</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.76805206778412</v>
+        <v>3.768052067784119</v>
       </c>
       <c r="C2003" t="n">
         <v>3.516455597036694</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.447819637547926</v>
+        <v>-3.35279060421536</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.136971317703776</v>
+        <v>2.174982931036802</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.09648787057811548</v>
+        <v>0.1915169039106808</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.574348319383563</v>
+        <v>3.631365739383102</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714434</v>
+        <v>3.743925505714432</v>
       </c>
       <c r="C2004" t="n">
         <v>3.508572291939687</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.470227755352798</v>
+        <v>-3.375198722020232</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.12012476548482</v>
+        <v>2.158136378817846</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.09648787057811548</v>
+        <v>0.1915169039106808</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.566465014286556</v>
+        <v>3.623482434286095</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155044</v>
+        <v>3.719118627155042</v>
       </c>
       <c r="C2005" t="n">
         <v>3.510626291489324</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.618233522832198</v>
+        <v>-3.523204489499632</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.062976458042697</v>
+        <v>2.100988071375724</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.009760861714574021</v>
+        <v>0.1047898950471393</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.516482808518069</v>
+        <v>3.573500228517608</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161989</v>
+        <v>3.729452285161988</v>
       </c>
       <c r="C2006" t="n">
         <v>3.566880009211171</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.596666835504645</v>
+        <v>-3.501637802172079</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.127856850695566</v>
+        <v>2.165868464028592</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.02227172600557981</v>
+        <v>0.1173007593381451</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.580243044814519</v>
+        <v>3.637260464814058</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321646</v>
+        <v>3.714941193321645</v>
       </c>
       <c r="C2007" t="n">
         <v>3.569771103756472</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.595380071965089</v>
+        <v>-3.500351038632522</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.131262650656689</v>
+        <v>2.169274263989716</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.0235584895451364</v>
+        <v>0.1185875228777017</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.583906197483554</v>
+        <v>3.640923617483093</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347715</v>
+        <v>3.727898186347713</v>
       </c>
       <c r="C2008" t="n">
         <v>3.567882916650247</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.59693712595438</v>
+        <v>-3.501908092621814</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.128751641954748</v>
+        <v>2.166763255287774</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.0235584895451364</v>
+        <v>0.1185875228777017</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.582018010377329</v>
+        <v>3.639035430376869</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887759</v>
+        <v>3.710654104887757</v>
       </c>
       <c r="C2009" t="n">
         <v>3.56270314625311</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.604209011477844</v>
+        <v>-3.509179978145278</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.120663117348224</v>
+        <v>2.158674730681251</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.01628660402167165</v>
+        <v>0.1113156373542369</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.572475108666113</v>
+        <v>3.629492528665652</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343077</v>
+        <v>3.712897612343075</v>
       </c>
       <c r="C2010" t="n">
         <v>3.561137156463262</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.602367992419593</v>
+        <v>-3.507338959087027</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.119833535181677</v>
+        <v>2.157845148514704</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.01755483069314007</v>
+        <v>0.1125838640257054</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.571670054879146</v>
+        <v>3.628687474878685</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647117</v>
+        <v>3.754911907647116</v>
       </c>
       <c r="C2011" t="n">
         <v>3.574210563329181</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.609276697919274</v>
+        <v>-3.514247664586708</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.130143459847724</v>
+        <v>2.16815507318075</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.01755483069314007</v>
+        <v>0.1125838640257054</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.584743461745065</v>
+        <v>3.641760881744604</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176354</v>
+        <v>3.749896851763538</v>
       </c>
       <c r="C2012" t="n">
         <v>3.574210563329181</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.610838340734134</v>
+        <v>-3.515809307401567</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.12951880272178</v>
+        <v>2.167530416054806</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.01755483069314007</v>
+        <v>0.1125838640257054</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.584743461745065</v>
+        <v>3.641760881744604</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392124</v>
+        <v>3.715834055392122</v>
       </c>
       <c r="C2013" t="n">
         <v>3.572734604456183</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.638739127843607</v>
+        <v>-3.54371009451104</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.116882529004993</v>
+        <v>2.154894142338019</v>
       </c>
       <c r="F2013" t="n">
-        <v>-0.01704209344979474</v>
+        <v>0.07798693988277056</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.562509348386306</v>
+        <v>3.619526768385845</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172536</v>
+        <v>3.684909939172534</v>
       </c>
       <c r="C2014" t="n">
         <v>3.569499048433381</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.64177212535628</v>
+        <v>-3.599938623522838</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.112433773977122</v>
+        <v>2.129167174710499</v>
       </c>
       <c r="F2014" t="n">
-        <v>-0.02007509096246862</v>
+        <v>0.02175841087097319</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.5574539938559</v>
+        <v>3.582554094955965</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.474291009187088</v>
+        <v>3.814702670382983</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.568972619008902</v>
+        <v>3.577473969103421</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.64177212535628</v>
+        <v>-3.706727332862719</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.112433773977122</v>
+        <v>2.094426611644586</v>
       </c>
       <c r="F2015" t="n">
-        <v>-0.02007509096246862</v>
+        <v>-0.08503029846890864</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.56203641599527</v>
+        <v>3.526455790022076</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240704.xlsx
+++ b/tame_output/ON/bt/strategyON_20240704.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>48.6%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-73.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-50.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.9%</t>
+          <t>-69.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.0%</t>
+          <t>453.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-532.2%</t>
+          <t>-534.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>-37.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-30.2%</t>
+          <t>-41.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-166.8%</t>
+          <t>-167.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-208.2%</t>
+          <t>-185.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-232.5%</t>
+          <t>-224.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-26.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-93.4%</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.26352495425213</v>
+        <v>-10.35855398758469</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9449281927095492</v>
+        <v>-0.9829398060425754</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.521557669281616</v>
+        <v>-2.616586702614181</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.647903611736079</v>
+        <v>1.59088619173654</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.31631110985245</v>
+        <v>-10.41134014318502</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.9649268651111234</v>
+        <v>-1.00293847844415</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.617233155864013</v>
+        <v>-2.712262189196578</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.591614109625198</v>
+        <v>1.534596689625658</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.44234790322074</v>
+        <v>-10.53737693655331</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.012647853829324</v>
+        <v>-1.050659467162351</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.591981533054271</v>
+        <v>-2.687010566386836</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.609458811940158</v>
+        <v>1.552441391940618</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.39033238925193</v>
+        <v>-10.48536142258449</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.9878513125553985</v>
+        <v>-1.025862925888425</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.591981533054271</v>
+        <v>-2.687010566386836</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.613449147626558</v>
+        <v>1.556431727627019</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.53200423097605</v>
+        <v>-10.62703326430861</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.045995276143788</v>
+        <v>-1.084006889476814</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.591981533054271</v>
+        <v>-2.687010566386836</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.611973920727817</v>
+        <v>1.554956500728278</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.48241338655122</v>
+        <v>-10.57744241988378</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.011105528208982</v>
+        <v>-1.049117141542009</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.542390688629437</v>
+        <v>-2.637419721962002</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.656781837547589</v>
+        <v>1.59976441754805</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.46960599354644</v>
+        <v>-10.56463502687901</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.019033704653756</v>
+        <v>-1.057045317986782</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.591246463638338</v>
+        <v>-2.686275496970903</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.614417238895566</v>
+        <v>1.557399818896027</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.24376084082703</v>
+        <v>-10.33878987415959</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9191165705297819</v>
+        <v>-0.9571281838628081</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.549319788051174</v>
+        <v>-2.64434882138374</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.649152317284073</v>
+        <v>1.592134897284533</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.11918218448944</v>
+        <v>-10.214211217822</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.8681459634386868</v>
+        <v>-0.9061575767717129</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.549319788051174</v>
+        <v>-2.64434882138374</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.650291461840131</v>
+        <v>1.593274041840592</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.17207747253372</v>
+        <v>-10.26710650586629</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.8866703044942934</v>
+        <v>-0.9246819178273196</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.544364441962728</v>
+        <v>-2.639393475295293</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.655898443655307</v>
+        <v>1.598881023655768</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.09994429724584</v>
+        <v>-10.19497333057841</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8520833301405046</v>
+        <v>-0.8900949434735308</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.544364441962728</v>
+        <v>-2.639393475295293</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.661632147893943</v>
+        <v>1.604614727894404</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.0285779046362</v>
+        <v>-10.12360693796876</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8332740354905113</v>
+        <v>-0.8712856488235374</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.47299804935308</v>
+        <v>-2.568027082685645</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.694714721065867</v>
+        <v>1.637697301066328</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.935118870650971</v>
+        <v>-10.03014790398354</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8057739032093285</v>
+        <v>-0.8437855165423547</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.47299804935308</v>
+        <v>-2.568027082685645</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.684831239752959</v>
+        <v>1.62781381975342</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.667877069782573</v>
+        <v>-9.762906103115139</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7007117433613432</v>
+        <v>-0.7387233566943694</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.47299804935308</v>
+        <v>-2.568027082685645</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.682996679253586</v>
+        <v>1.625979259254047</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.569970031106083</v>
+        <v>-9.664999064438648</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.661849242864208</v>
+        <v>-0.6998608561972341</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.405012299492523</v>
+        <v>-2.500041332825089</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.723487814196459</v>
+        <v>1.66647039419692</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.546016490130125</v>
+        <v>-9.64104552346269</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.651599320328331</v>
+        <v>-0.6896109336613572</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.381058758516566</v>
+        <v>-2.476087791849131</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.738528444927527</v>
+        <v>1.681511024927988</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.281956551807328</v>
+        <v>-9.376985585139893</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5592356611609643</v>
+        <v>-0.5972472744939905</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.11699882019377</v>
+        <v>-2.212027853526335</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.883704091759452</v>
+        <v>1.826686671759913</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.574876928302491</v>
+        <v>-8.669905961635056</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2791908454193304</v>
+        <v>-0.3172024587523565</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.11699882019377</v>
+        <v>-2.212027853526335</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.880917058099151</v>
+        <v>1.823899638099612</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.5346926299363</v>
+        <v>-8.629721663268866</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2627735021850128</v>
+        <v>-0.300785115518039</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.076814521827579</v>
+        <v>-2.171843555160144</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.905371261006707</v>
+        <v>1.848353841007168</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.371292758996937</v>
+        <v>-8.466321792329502</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1980467325885105</v>
+        <v>-0.2360583459215366</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.913414650888217</v>
+        <v>-2.008443684220782</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.002778004791081</v>
+        <v>1.945760584791542</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.137811536767337</v>
+        <v>-8.232840570099903</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.09672981485881849</v>
+        <v>-0.1347414281918446</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.679933428658618</v>
+        <v>-1.774962461991183</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.150791166966693</v>
+        <v>2.093773746967154</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.988145145759822</v>
+        <v>-8.083174179092389</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.03975546876877178</v>
+        <v>-0.07776708210179795</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.587029937416082</v>
+        <v>-1.682058970748648</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.203641051399256</v>
+        <v>2.146623631399716</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.855869672128936</v>
+        <v>-7.950898705461502</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.008522207430610163</v>
+        <v>-0.02948940590241644</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.454754463785195</v>
+        <v>-1.549783497117761</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.278373822324815</v>
+        <v>2.221356402325275</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.700131339569194</v>
+        <v>-7.79516037290176</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.07363260114214354</v>
+        <v>0.03562098780911693</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.299016131225454</v>
+        <v>-1.394045164558019</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.374631882548296</v>
+        <v>2.317614462548757</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.451131540885613</v>
+        <v>-7.546160574218179</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1861388618392348</v>
+        <v>0.1481272485062082</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.299016131225454</v>
+        <v>-1.394045164558019</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.387538223771955</v>
+        <v>2.330520803772416</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.556721530658717</v>
+        <v>-7.651750563991284</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.01592693633077413</v>
+        <v>-0.02208467700225247</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.404606120998558</v>
+        <v>-1.499635154331124</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.196208300308874</v>
+        <v>2.139190880309334</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.575456432777314</v>
+        <v>-7.670485466109881</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.05697731736042178</v>
+        <v>0.01896570402739517</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.41020213065869</v>
+        <v>-1.505231163991255</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.241395036389881</v>
+        <v>2.184377616390342</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.427516391369715</v>
+        <v>-7.522545424702281</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.003725588764706078</v>
+        <v>-0.04173720209773268</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.389881214750132</v>
+        <v>-1.484910248082697</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.133708663246848</v>
+        <v>2.076691243247309</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.374546869115727</v>
+        <v>-7.469575902448293</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.008748233883411061</v>
+        <v>-0.02926337944961555</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.336911692496143</v>
+        <v>-1.431940725828709</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.156776390345764</v>
+        <v>2.099758970346224</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.330998462345036</v>
+        <v>-7.426027495677602</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.01920698449659408</v>
+        <v>-0.01880462883643252</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.336911692496143</v>
+        <v>-1.431940725828709</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.14981577825067</v>
+        <v>2.092798358251131</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.088850068891178</v>
+        <v>-7.183879102223744</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1305286962592804</v>
+        <v>0.09251708292625382</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.336911692496143</v>
+        <v>-1.431940725828709</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.164278132631813</v>
+        <v>2.107260712632274</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.980590931768656</v>
+        <v>-7.075619965101223</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1683644715674841</v>
+        <v>0.1303528582344575</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.336911692496143</v>
+        <v>-1.431940725828709</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.158810253091008</v>
+        <v>2.101792833091469</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.857299796951525</v>
+        <v>-6.952328830284092</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2151790195049132</v>
+        <v>0.1771674061718866</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.213620557679013</v>
+        <v>-1.308649591011578</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.230283027991864</v>
+        <v>2.173265607992324</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.836150598048082</v>
+        <v>-6.931179631380648</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.231339677303616</v>
+        <v>0.1933280639705894</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.19247135877557</v>
+        <v>-1.287500392108135</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.250673525571255</v>
+        <v>2.193656105571716</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.592385156064638</v>
+        <v>-6.687414189397204</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3246265624440441</v>
+        <v>0.2866149491110179</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.19247135877557</v>
+        <v>-1.287500392108135</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.246454233918305</v>
+        <v>2.189436813918766</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.490622335787343</v>
+        <v>-6.585651369119909</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3674560044749784</v>
+        <v>0.3294443911419518</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.179252290383141</v>
+        <v>-1.274281323715706</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.256509988873779</v>
+        <v>2.199492568874239</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.240771941838268</v>
+        <v>-6.335800975170835</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.46013823703831</v>
+        <v>0.4221266237052839</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.179252290383141</v>
+        <v>-1.274281323715706</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.24925206385748</v>
+        <v>2.192234643857941</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.064879849370836</v>
+        <v>-6.159908882703402</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5340941975459317</v>
+        <v>0.4960825842129055</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.179252290383141</v>
+        <v>-1.274281323715706</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.25285118737813</v>
+        <v>2.19583376737859</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.893433386348373</v>
+        <v>-5.988462419680938</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6160002888094711</v>
+        <v>0.5779886754764449</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.007805827360678</v>
+        <v>-1.102834860693243</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.369046571246161</v>
+        <v>2.312029151246622</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.819143820610034</v>
+        <v>-5.914172853942599</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6447365927211037</v>
+        <v>0.6067249793880776</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9335162616223384</v>
+        <v>-1.028545294954904</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.412640788305461</v>
+        <v>2.355623368305922</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.755508078376099</v>
+        <v>-5.850537111708665</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6748856906689946</v>
+        <v>0.6368740773359685</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8698805193884038</v>
+        <v>-0.9649095527209691</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.45551703470014</v>
+        <v>2.3984996147006</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.644081319050179</v>
+        <v>-5.739110352382744</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7006506531831582</v>
+        <v>0.6626390398501321</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8698805193884038</v>
+        <v>-0.9649095527209691</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.436711293483935</v>
+        <v>2.379693873484396</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.403650822245319</v>
+        <v>-5.498679855577884</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.79856592852998</v>
+        <v>0.7605543151969538</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6294500225835435</v>
+        <v>-0.7244790559161088</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.582712668191729</v>
+        <v>2.52569524819219</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.331408254074124</v>
+        <v>-5.42643728740669</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8313922696332781</v>
+        <v>0.7933806563002519</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6294500225835435</v>
+        <v>-0.7244790559161088</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.586641982026549</v>
+        <v>2.52962456202701</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.278409931792736</v>
+        <v>-5.373438965125302</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8532701824631732</v>
+        <v>0.815258569130147</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5741137635816047</v>
+        <v>-0.66914279691417</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.620522321345052</v>
+        <v>2.563504901345513</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.169605046313009</v>
+        <v>-5.264634079645575</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8937902078750573</v>
+        <v>0.8557785945420311</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5741137635816047</v>
+        <v>-0.66914279691417</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.617520392565046</v>
+        <v>2.560502972565506</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.949584248275999</v>
+        <v>-5.044613281608564</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9833775641004756</v>
+        <v>0.9453659507674494</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4328939185136245</v>
+        <v>-0.5279229518461898</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.703831336616448</v>
+        <v>2.646813916616909</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.816716559212721</v>
+        <v>-4.911745592545286</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.05241882252761</v>
+        <v>1.014407209194584</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4328939185136245</v>
+        <v>-0.5279229518461898</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.719725519418271</v>
+        <v>2.662708099418732</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.696543475848222</v>
+        <v>-4.791572509180788</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.101633900313711</v>
+        <v>1.063622286980685</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3127208351491255</v>
+        <v>-0.4077498684816908</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.792975213877273</v>
+        <v>2.735957793877733</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.551871330748485</v>
+        <v>-4.64690036408105</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.169590860915046</v>
+        <v>1.13157924758202</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1680486900493881</v>
+        <v>-0.2630777233819534</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.889866603498555</v>
+        <v>2.832849183499015</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.611746158106177</v>
+        <v>-4.706775191438743</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.131678421373395</v>
+        <v>1.093666808040369</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2279235174070802</v>
+        <v>-0.3229525507396455</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.839979198485366</v>
+        <v>2.782961778485826</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.524946660327169</v>
+        <v>-4.619975693659734</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.188798713807565</v>
+        <v>1.150787100474538</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2279235174070802</v>
+        <v>-0.3229525507396455</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.862379691807932</v>
+        <v>2.805362271808392</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.527416366788975</v>
+        <v>-4.62244540012154</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.187883232596254</v>
+        <v>1.149871619263228</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2303932238688864</v>
+        <v>-0.3254222572014517</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.86097026930426</v>
+        <v>2.803952849304721</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.595786553112985</v>
+        <v>-4.690815586445551</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.171542080541352</v>
+        <v>1.133530467208326</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2211175248326714</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.877542611200691</v>
+        <v>2.820525191201152</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.609574605960032</v>
+        <v>-4.704603639292597</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.156463568034425</v>
+        <v>1.118451954701399</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2211175248326714</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.867979319832582</v>
+        <v>2.810961899833043</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.640567765288737</v>
+        <v>-4.735596798621303</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9687758693433295</v>
+        <v>0.9307642560103033</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2211175248326714</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.692688884872969</v>
+        <v>2.63567146487343</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.465093505496268</v>
+        <v>-4.560122538828834</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.043532805252105</v>
+        <v>1.005521191919079</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2211175248326714</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.697256116864757</v>
+        <v>2.640238696865218</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.576029758137517</v>
+        <v>-4.671058791470083</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9749003329568122</v>
+        <v>0.9368887196237861</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2211175248326714</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.672998145625964</v>
+        <v>2.615980725626425</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.542366212665235</v>
+        <v>-4.637395245997801</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9914971363656306</v>
+        <v>0.9534855230326045</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1874539793603896</v>
+        <v>-0.2824830126929549</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.696327658129238</v>
+        <v>2.6393102381297</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.482513593461512</v>
+        <v>-4.577542626794077</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.025610570479252</v>
+        <v>0.9875989571462263</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1874539793603896</v>
+        <v>-0.2824830126929549</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.706500044561371</v>
+        <v>2.649482624561832</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.396270130435134</v>
+        <v>-4.4912991637677</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.055054226263664</v>
+        <v>1.017042612930638</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1874539793603896</v>
+        <v>-0.2824830126929549</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.701446315135231</v>
+        <v>2.644428895135692</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.441576949834114</v>
+        <v>-4.536605983166679</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.028707273948597</v>
+        <v>0.9906956606155712</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2282641423696204</v>
+        <v>-0.3232931757021857</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.668735992774218</v>
+        <v>2.611718572774679</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.470610054536415</v>
+        <v>-4.565639087868981</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.017645905100778</v>
+        <v>0.9796342917677523</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2282641423696204</v>
+        <v>-0.3232931757021857</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.66928786580732</v>
+        <v>2.612270445807781</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.377799573085555</v>
+        <v>-4.472828606418121</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9840427895724879</v>
+        <v>0.9460311762394618</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.135453660918761</v>
+        <v>-0.2304826942513263</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.654246846569201</v>
+        <v>2.597229426569662</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.422189042414983</v>
+        <v>-4.517218075747548</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9681604777653179</v>
+        <v>0.9301488644322917</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1798431302481887</v>
+        <v>-0.274872163580754</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.629486640896145</v>
+        <v>2.572469220896606</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.309517824178733</v>
+        <v>-4.404546857511298</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.008304673571541</v>
+        <v>0.9702930602385147</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.06717191201193851</v>
+        <v>-0.1622009453445038</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.692165080349618</v>
+        <v>2.635147660350079</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.19714082299606</v>
+        <v>-4.292169856328625</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.058746769875277</v>
+        <v>1.020735156542251</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.06717191201193851</v>
+        <v>-0.1622009453445038</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.697656376180285</v>
+        <v>2.640638956180747</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.224921220897413</v>
+        <v>-4.319950254229978</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.059131812483275</v>
+        <v>1.021120199150249</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.09495230991329157</v>
+        <v>-0.1899813432458569</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.692485339208013</v>
+        <v>2.635467919208474</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.307922501922691</v>
+        <v>-4.402951535255257</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8642870200738171</v>
+        <v>0.8262754067407909</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1135231944404653</v>
+        <v>-0.2085522277730306</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.519698528492362</v>
+        <v>2.462681108492823</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.416536580366023</v>
+        <v>-4.511565613698588</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9409910494156901</v>
+        <v>0.902979436082664</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1135231944404653</v>
+        <v>-0.2085522277730306</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.639848189211567</v>
+        <v>2.582830769212028</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.38112754211788</v>
+        <v>-4.476156575450445</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9696676908172703</v>
+        <v>0.9316560774842442</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1135231944404653</v>
+        <v>-0.2085522277730306</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.65436121531389</v>
+        <v>2.597343795314351</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.342743879559729</v>
+        <v>-4.437772912892294</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9824405971828996</v>
+        <v>0.9444289838498734</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.07513953188231415</v>
+        <v>-0.1701685652148794</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.67481085419115</v>
+        <v>2.617793434191611</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.165627549524562</v>
+        <v>-4.260656582857128</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.050016158042268</v>
+        <v>1.012004544709242</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.07513953188231415</v>
+        <v>-0.1701685652148794</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.671539883036452</v>
+        <v>2.614522463036913</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.210719794358108</v>
+        <v>-4.305748827690674</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.032662651870763</v>
+        <v>0.9946510385377365</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1370355750517039</v>
+        <v>-0.2320646083842692</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.635085648896731</v>
+        <v>2.578068228897192</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.031344373119341</v>
+        <v>-4.126373406451906</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.098199795672684</v>
+        <v>1.060188182339658</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.01974118311901474</v>
+        <v>-0.07528785021355056</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.722938679105577</v>
+        <v>2.665921259106037</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.076358586639946</v>
+        <v>-4.171387619972512</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.061001565596031</v>
+        <v>1.022989952263005</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.01060771219558987</v>
+        <v>-0.1056367455281552</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.685536797248404</v>
+        <v>2.628519377248864</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.343363096912381</v>
+        <v>-4.438392130244947</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9598913238260032</v>
+        <v>0.921879710492977</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2049707502385384</v>
+        <v>-0.2999997835711037</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.57461053676158</v>
+        <v>2.517593116762041</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.444560878349554</v>
+        <v>-4.539589911682119</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9186161331476357</v>
+        <v>0.8806045198146095</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2733795637838576</v>
+        <v>-0.3684085971164229</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.53276917053089</v>
+        <v>2.475751750531351</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.438049911735241</v>
+        <v>-4.533078945067807</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9188204813476775</v>
+        <v>0.8808088680146513</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2733795637838576</v>
+        <v>-0.3684085971164229</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.530369132085207</v>
+        <v>2.473351712085668</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.419011784027944</v>
+        <v>-4.51404081736051</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9229604516388412</v>
+        <v>0.8849488383058151</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3315631751150522</v>
+        <v>-0.4265922084476175</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.491983684494735</v>
+        <v>2.434966264495196</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.450138415178563</v>
+        <v>-4.545167448511128</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.088091668117274</v>
+        <v>1.050080054784248</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3315631751150522</v>
+        <v>-0.4265922084476175</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.669565553433416</v>
+        <v>2.612548133433877</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.46400517651248</v>
+        <v>-4.559034209845046</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.083378292569841</v>
+        <v>1.045366679236815</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3694210918488751</v>
+        <v>-0.4644501251814404</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.647684132379255</v>
+        <v>2.590666712379716</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.419201004972551</v>
+        <v>-4.514230038305116</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.107308491582739</v>
+        <v>1.069296878249713</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3694210918488751</v>
+        <v>-0.4644501251814404</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.653692662776181</v>
+        <v>2.596675242776642</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.271458034737548</v>
+        <v>-4.366487068070113</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.245558327468762</v>
+        <v>1.207546714135735</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.201613734613992</v>
+        <v>-0.2966427679465573</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.833529724909133</v>
+        <v>2.776512304909594</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.373472717268769</v>
+        <v>-4.468501750601335</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.207546075987754</v>
+        <v>1.169534462654728</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.201613734613992</v>
+        <v>-0.2966427679465573</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.836323346440614</v>
+        <v>2.779305926441075</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.367320011215985</v>
+        <v>-4.46234904454855</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.210669506800526</v>
+        <v>1.1726578934675</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1954610285612077</v>
+        <v>-0.290490061893773</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.840677318463943</v>
+        <v>2.783659898464404</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.384129309366487</v>
+        <v>-4.479158342699052</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.203026264280436</v>
+        <v>1.16501465094741</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2122703267117093</v>
+        <v>-0.3072993600442746</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.829672216313752</v>
+        <v>2.772654796314213</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.321831310590365</v>
+        <v>-4.41686034392293</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.294281017587706</v>
+        <v>1.256269404254679</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2122703267117093</v>
+        <v>-0.3072993600442746</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.896007770110573</v>
+        <v>2.838990350111034</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.120041112925207</v>
+        <v>-4.215070146257772</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.083577969043167</v>
+        <v>1.04556635571014</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.01425213454255492</v>
+        <v>-0.1092811678751202</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.723399557801464</v>
+        <v>2.666382137801925</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.04666301583647</v>
+        <v>-4.141692049169036</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.183219440200836</v>
+        <v>1.14520782686781</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.05912596254618163</v>
+        <v>-0.03590307078638366</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.837716648376881</v>
+        <v>2.780699228377342</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.144403560461445</v>
+        <v>-4.23943259379401</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.15875095846689</v>
+        <v>1.120739345133864</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.04323668441320144</v>
+        <v>-0.05179234891936385</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.842810817613136</v>
+        <v>2.785793397613598</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.320741320584374</v>
+        <v>-4.41577035391694</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.08675183524239</v>
+        <v>1.048740221909364</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.133101075709728</v>
+        <v>-0.2281301090422932</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.735544142364051</v>
+        <v>2.678526722364512</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.244319274152447</v>
+        <v>-4.339348307485013</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.11581227185509</v>
+        <v>1.077800658522063</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.133101075709728</v>
+        <v>-0.2281301090422932</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.734035760403979</v>
+        <v>2.67701834040444</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.199946142513879</v>
+        <v>-4.294975175846444</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.133424391945953</v>
+        <v>1.095412778612927</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.08872794407115936</v>
+        <v>-0.1837569774037247</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.760522506822556</v>
+        <v>2.703505086823017</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.808153067403842</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.077111921626711</v>
+        <v>-4.172140954959277</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.176951874439411</v>
+        <v>1.138940261106384</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.08872794407115936</v>
+        <v>-0.1837569774037247</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.754916300961147</v>
+        <v>2.697898880961608</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.814534824431647</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.029456191065655</v>
+        <v>-4.124485224398221</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.202395923691637</v>
+        <v>1.164384310358611</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.04107221351010371</v>
+        <v>-0.136101246842669</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.789891496325585</v>
+        <v>2.732874076326045</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.819427197806371</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.928938032566901</v>
+        <v>-4.023967065899466</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.247495560465864</v>
+        <v>1.209483947132838</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.05944594498865086</v>
+        <v>-0.03558308834391444</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.855094764799562</v>
+        <v>2.798077344800023</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.806181870282244</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.98960462296929</v>
+        <v>-4.084633656301856</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.20998359678078</v>
+        <v>1.171971983447754</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.02225237172988281</v>
+        <v>-0.1172814050624481</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.792830447244314</v>
+        <v>2.735813027244775</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.810279572892872</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.944766221360892</v>
+        <v>-3.980652549536695</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.232016660034768</v>
+        <v>1.217662128764447</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.01770893878501334</v>
+        <v>-0.06270353938807061</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.799654209621865</v>
+        <v>2.77265744926003</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.81444051252395</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.04552485711789</v>
+        <v>-4.081411185293693</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.195874145363047</v>
+        <v>1.181519614092726</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1065345075120188</v>
+        <v>-0.151529108115076</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.750519808016739</v>
+        <v>2.723523047654905</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.820320115051787</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.001322020031989</v>
+        <v>-4.037208348207793</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.219434882725244</v>
+        <v>1.205080351454923</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.06233167042611831</v>
+        <v>-0.1073262710291756</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.782921112796116</v>
+        <v>2.755924352434282</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.818730115521035</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.038301047695432</v>
+        <v>-4.074187375871237</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.203053272129115</v>
+        <v>1.188698740858793</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.02535776863478778</v>
+        <v>-0.07035236923784505</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.803515454340162</v>
+        <v>2.776518693978328</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.869977880704075</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.058359126560273</v>
+        <v>-4.094245454736077</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.246277805766218</v>
+        <v>1.231923274495896</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.02535776863478778</v>
+        <v>-0.07035236923784505</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.854763219523202</v>
+        <v>2.827766459161368</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.868418585298328</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.018428453382382</v>
+        <v>-4.054314781558187</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.260690779631628</v>
+        <v>1.246336248361306</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.01457290454310256</v>
+        <v>-0.03042169605995471</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.877162328024189</v>
+        <v>2.850165567662355</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.863366813536598</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.967396360659854</v>
+        <v>-4.003282688835659</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.276051844958909</v>
+        <v>1.261697313688587</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.06560499726563052</v>
+        <v>0.02061039666257325</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.902729811895976</v>
+        <v>2.875733051534142</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.880554217629303</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.902172179532648</v>
+        <v>-3.938058507708453</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.319328921502496</v>
+        <v>1.304974390232174</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1308291783928361</v>
+        <v>0.08583457778977888</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.959051724665005</v>
+        <v>2.93205496430317</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.876515189928583</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.864745159461515</v>
+        <v>-3.90063148763732</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.33026070183023</v>
+        <v>1.315906170559908</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1360807164220178</v>
+        <v>0.09108611581896053</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.958163619781794</v>
+        <v>2.93116685941996</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.877771982259823</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.884856815496223</v>
+        <v>-3.920743143672028</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.323472831747587</v>
+        <v>1.309118300477265</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.147108061419437</v>
+        <v>0.1021134608163797</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.966036819111486</v>
+        <v>2.939040058749651</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.038329753281034</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.831112001069018</v>
+        <v>-3.866998329244823</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.50552852853968</v>
+        <v>1.491173997269358</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.157171370859899</v>
+        <v>0.1121767702568417</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.132632575796974</v>
+        <v>3.105635815435139</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.158442662498851</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.807320432462876</v>
+        <v>-3.843206760638681</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.635158065199954</v>
+        <v>1.620803533929632</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.1809629394660413</v>
+        <v>0.135968338862984</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.267020426178476</v>
+        <v>3.240023665816642</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15015063851271</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.781236348199068</v>
+        <v>-3.817122676374873</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.637299674919336</v>
+        <v>1.622945143649014</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.1809629394660413</v>
+        <v>0.135968338862984</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.258728402192335</v>
+        <v>3.231731641830501</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.14834383409649</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.703105167350121</v>
+        <v>-3.738991495525926</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.666745342842694</v>
+        <v>1.652390811572372</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2551397503497258</v>
+        <v>0.2101451497466685</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.301427684306325</v>
+        <v>3.274430923944491</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.165898239823281</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.694212705956838</v>
+        <v>-3.692848215908264</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.687856733126799</v>
+        <v>1.688402529146229</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2551397503497258</v>
+        <v>0.2101451497466685</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.318982090033117</v>
+        <v>3.291985329671283</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.157753287227865</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.862688822926716</v>
+        <v>-3.861324332878142</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.612321333743431</v>
+        <v>1.612867129762861</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.227191914633145</v>
+        <v>0.1821973140300878</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.294068436007752</v>
+        <v>3.267071675645918</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.139022984415727</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.164889294065133</v>
+        <v>-3.163524804016558</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.872710842475926</v>
+        <v>1.873256638495356</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1568438552627343</v>
+        <v>0.111849254659677</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.233129297573368</v>
+        <v>3.206132537211533</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.129687006912631</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.14216819038198</v>
+        <v>-3.140803700333406</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.872463306446092</v>
+        <v>1.873009102465522</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1568438552627343</v>
+        <v>0.111849254659677</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.223793320070272</v>
+        <v>3.196796559708438</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.2885931327638</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.140443147091936</v>
+        <v>-3.139078657043362</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.032059449613278</v>
+        <v>2.032605245632709</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.1585688985527781</v>
+        <v>0.1135742979497208</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.383734471895468</v>
+        <v>3.356737711533633</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.325670955257447</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.295224153870191</v>
+        <v>-3.293859663821617</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.007224869395623</v>
+        <v>2.007770665415053</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.125201224498302</v>
+        <v>0.08020662389524469</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.400791689956428</v>
+        <v>3.373794929594594</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.322346311246992</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.243788820485532</v>
+        <v>-3.242424330436958</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.024474358739032</v>
+        <v>2.025020154758462</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.1766365578829616</v>
+        <v>0.1316419572799044</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.428328245976769</v>
+        <v>3.401331485614935</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.332352464891734</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.216837596159044</v>
+        <v>-3.21547310611047</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.045261002114369</v>
+        <v>2.045806798133799</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.1915169039106808</v>
+        <v>0.1465223033076235</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.447262607238142</v>
+        <v>3.420265846876308</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.516455597036694</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.35279060421536</v>
+        <v>-3.351426114166786</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.174982931036802</v>
+        <v>2.175528727056232</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.1915169039106808</v>
+        <v>0.1465223033076235</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.631365739383102</v>
+        <v>3.604368979021268</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.508572291939687</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.375198722020232</v>
+        <v>-3.373834231971658</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.158136378817846</v>
+        <v>2.158682174837276</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.1915169039106808</v>
+        <v>0.1465223033076235</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.623482434286095</v>
+        <v>3.596485673924261</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.510626291489324</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.523204489499632</v>
+        <v>-3.521839999451057</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.100988071375724</v>
+        <v>2.101533867395154</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.1047898950471393</v>
+        <v>0.05979529444408205</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.573500228517608</v>
+        <v>3.546503468155774</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.566880009211171</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.501637802172079</v>
+        <v>-3.531280925339587</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.165868464028592</v>
+        <v>2.154011214761589</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.1173007593381451</v>
+        <v>0.1822224119874735</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.637260464814058</v>
+        <v>3.676213456403655</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.569771103756472</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.500351038632522</v>
+        <v>-3.529994161800031</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.169274263989716</v>
+        <v>2.157417014722713</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.1185875228777017</v>
+        <v>0.1835091755270301</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.640923617483093</v>
+        <v>3.67987660907269</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.567882916650247</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.501908092621814</v>
+        <v>-3.531551215789322</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.166763255287774</v>
+        <v>2.154906006020771</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.1185875228777017</v>
+        <v>0.1835091755270301</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.639035430376869</v>
+        <v>3.677988421966465</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.56270314625311</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.509179978145278</v>
+        <v>-3.538823101312787</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.158674730681251</v>
+        <v>2.146817481414248</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.1113156373542369</v>
+        <v>0.1762372900035653</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.629492528665652</v>
+        <v>3.668445520255249</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.561137156463262</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.507338959087027</v>
+        <v>-3.536982082254536</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.157845148514704</v>
+        <v>2.145987899247701</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.1125838640257054</v>
+        <v>0.1775055166750337</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.628687474878685</v>
+        <v>3.667640466468282</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.574210563329181</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.514247664586708</v>
+        <v>-3.543890787754216</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.16815507318075</v>
+        <v>2.156297823913747</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.1125838640257054</v>
+        <v>0.1775055166750337</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.641760881744604</v>
+        <v>3.680713873334201</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.574210563329181</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.515809307401567</v>
+        <v>-3.545452430569076</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.167530416054806</v>
+        <v>2.155673166787803</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.1125838640257054</v>
+        <v>0.1775055166750337</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.641760881744604</v>
+        <v>3.680713873334201</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.572734604456183</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.54371009451104</v>
+        <v>-3.573353217678549</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.154894142338019</v>
+        <v>2.143036893071016</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.07798693988277056</v>
+        <v>0.1429085925320989</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.619526768385845</v>
+        <v>3.658479759975442</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172534</v>
+        <v>3.684909939172533</v>
       </c>
       <c r="C2014" t="n">
         <v>3.569499048433381</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.599938623522838</v>
+        <v>-3.638455127022676</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.129167174710499</v>
+        <v>2.113760573310564</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.02175841087097319</v>
+        <v>0.07780668318797168</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.582554094955965</v>
+        <v>3.616183058346165</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.814702670382983</v>
+        <v>3.766506501048612</v>
       </c>
       <c r="C2015" t="n">
         <v>3.577473969103421</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.706727332862719</v>
+        <v>-3.725576823628631</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.094426611644586</v>
+        <v>2.086886815338221</v>
       </c>
       <c r="F2015" t="n">
-        <v>-0.08503029846890864</v>
+        <v>-0.009315013417982798</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.526455790022076</v>
+        <v>3.571884961052631</v>
       </c>
     </row>
   </sheetData>
